--- a/Project 1/defense_results/analysis_results.xlsx
+++ b/Project 1/defense_results/analysis_results.xlsx
@@ -17,11 +17,13 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="exclusion_cost" sheetId="8" state="visible" r:id="rId8"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="defense_weight_sensitivity" sheetId="9" state="visible" r:id="rId9"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="bootstrap_gmv_defense" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="monthly_returns" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="frontier_full_with_def" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="data_audit" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="security_history" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="periods" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="returns_test" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="question_answer" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="monthly_returns" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="frontier_full_with_def" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="data_audit" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="security_history" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="periods" sheetId="17" state="visible" r:id="rId17"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -51,7 +53,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -64,6 +66,27 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top/>
+      <bottom style="thin"/>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -853,6 +876,236 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:B8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>DEF</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>Pre-invasion annualized mean</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>0.188482706995672</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>Post-invasion annualized mean</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>0.09883805855208924</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Difference (post - pre), annualized</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>-0.0896446484435828</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>Standard error of difference, annualized</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>0.09912376354075705</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>t-statistic</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>-0.9043709120943869</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Degrees of freedom (Welch)</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>81.78186331488877</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>Two-sided p-value</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>0.3684551720365185</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Pre-invasion</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Post-invasion</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Change (post - pre)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>Diversification test</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>Average correlation of DEF with sectors</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>0.5486283832502574</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.3927084394723381</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-0.1559199437779193</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="n"/>
+      <c r="B3" s="1" t="inlineStr">
+        <is>
+          <t>DEF weight in minimum variance portfolio</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>0.05540182866451901</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.2214304253984209</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.1660285967339019</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="n"/>
+      <c r="B4" s="1" t="inlineStr">
+        <is>
+          <t>Extra minimum-variance volatility from excluding DEF</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>0.0002831058937632913</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.005021155056011709</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.004738049162248417</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>Returns test</t>
+        </is>
+      </c>
+      <c r="B5" s="1" t="inlineStr">
+        <is>
+          <t>DEF annualized mean return</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>0.188482706995672</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.09883805855208924</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-0.0896446484435828</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="1" t="inlineStr">
+        <is>
+          <t>DEF weight in mean-variance utility portfolio (γ = 4)</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>0.4025461561604331</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.2221693546039033</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-0.1803768015565298</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="A2:A4"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:I193"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -6871,7 +7124,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -10525,7 +10778,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -10610,7 +10863,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -11084,7 +11337,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -12812,7 +13065,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Utility max (A=4)</t>
+          <t>Mean-variance utility (γ=4)</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
@@ -12906,7 +13159,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Utility max (A=4)</t>
+          <t>Mean-variance utility (γ=4)</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
@@ -13000,7 +13253,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Utility max (A=4)</t>
+          <t>Mean-variance utility (γ=4)</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
@@ -13094,7 +13347,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Utility max (A=4)</t>
+          <t>Mean-variance utility (γ=4)</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
@@ -13188,7 +13441,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Utility max (A=4)</t>
+          <t>Mean-variance utility (γ=4)</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
@@ -13282,7 +13535,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Utility max (A=4)</t>
+          <t>Mean-variance utility (γ=4)</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
@@ -13491,7 +13744,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>A = 2</t>
+          <t>γ = 2</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -13507,7 +13760,7 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>A = 4</t>
+          <t>γ = 4</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
@@ -13523,7 +13776,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>A = 6</t>
+          <t>γ = 6</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -13539,7 +13792,7 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>A = 8</t>
+          <t>γ = 8</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
@@ -13555,7 +13808,7 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>A = 10</t>
+          <t>γ = 10</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">

--- a/Project 1/defense_results/analysis_results.xlsx
+++ b/Project 1/defense_results/analysis_results.xlsx
@@ -1,29 +1,29 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="asset_metrics_full" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="asset_metrics_pre" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="asset_metrics_post" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="correlation_full" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="defense_correlations" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="annual_covariance_full" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="portfolios" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="exclusion_cost" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="defense_weight_sensitivity" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="bootstrap_gmv_defense" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="returns_test" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="question_answer" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="monthly_returns" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="frontier_full_with_def" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="data_audit" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="security_history" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="periods" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="asset_metrics_full" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="asset_metrics_pre" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="asset_metrics_post" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="correlation_full" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="defense_correlations" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="annual_covariance_full" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="portfolios" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="exclusion_cost" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="defense_weight_sensitivity" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="bootstrap_gmv_defense" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="returns_test" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="question_answer" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="monthly_returns" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="frontier_full_with_def" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="data_audit" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="security_history" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="periods" sheetId="17" state="visible" r:id="rId17"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -834,10 +834,10 @@
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>0.04496770866122467</v>
+        <v>0.04496770866122459</v>
       </c>
       <c r="E2" t="n">
-        <v>0.145307845304233</v>
+        <v>0.1453078453042332</v>
       </c>
       <c r="F2" t="n">
         <v>0.68</v>
@@ -853,13 +853,13 @@
         <v>500</v>
       </c>
       <c r="C3" t="n">
-        <v>3.660335397729083e-17</v>
+        <v>2.107181450903737e-17</v>
       </c>
       <c r="D3" t="n">
         <v>0.2166291567547662</v>
       </c>
       <c r="E3" t="n">
-        <v>0.4270913255303988</v>
+        <v>0.4270913255303989</v>
       </c>
       <c r="F3" t="n">
         <v>0.926</v>
@@ -1010,13 +1010,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.5486283832502574</v>
+        <v>0.5486283832502575</v>
       </c>
       <c r="D2" t="n">
         <v>0.3927084394723381</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.1559199437779193</v>
+        <v>-0.1559199437779195</v>
       </c>
     </row>
     <row r="3">
@@ -1027,13 +1027,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.05540182866451901</v>
+        <v>0.05540182866451893</v>
       </c>
       <c r="D3" t="n">
-        <v>0.2214304253984209</v>
+        <v>0.2214304253984211</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1660285967339019</v>
+        <v>0.1660285967339022</v>
       </c>
     </row>
     <row r="4">
@@ -1047,10 +1047,10 @@
         <v>0.0002831058937632913</v>
       </c>
       <c r="D4" t="n">
-        <v>0.005021155056011709</v>
+        <v>0.005021155056011667</v>
       </c>
       <c r="E4" t="n">
-        <v>0.004738049162248417</v>
+        <v>0.004738049162248376</v>
       </c>
     </row>
     <row r="5">
@@ -1082,13 +1082,13 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.4025461561604331</v>
+        <v>0.4025461561604337</v>
       </c>
       <c r="D6" t="n">
-        <v>0.2221693546039033</v>
+        <v>0.2221693546039032</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.1803768015565298</v>
+        <v>-0.1803768015565305</v>
       </c>
     </row>
   </sheetData>
@@ -7240,28 +7240,28 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>0.09710259697751444</v>
+        <v>0.09710259697751432</v>
       </c>
       <c r="B3" s="2" t="n">
-        <v>0.2277568511291737</v>
+        <v>0.2277568511291748</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>2.229126426278046e-16</v>
+        <v>0</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>0.8252721848025786</v>
+        <v>0.8252721848025842</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0</v>
+        <v>4.167136464939772e-18</v>
       </c>
       <c r="F3" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>2.242858538903548e-16</v>
+        <v>1.316345419785818e-16</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>0.174727815197422</v>
+        <v>0.174727815197416</v>
       </c>
       <c r="I3" s="2" t="n">
         <v>0</v>
@@ -7275,34 +7275,34 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>0.09802374248931074</v>
+        <v>0.09802374248931071</v>
       </c>
       <c r="B4" s="2" t="n">
         <v>0.1930617529131541</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>4.57256406274151e-17</v>
+        <v>0</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>0.6505443696051616</v>
+        <v>0.6505443696051622</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>1.313170570158451e-18</v>
+        <v>0</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>0</v>
+        <v>5.494322100631465e-18</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>1.002545226404683e-16</v>
+        <v>4.025111865110741e-17</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>0.3494556303948388</v>
+        <v>0.3494556303948379</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>0</v>
+        <v>1.387778780781446e-16</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>2.42621155963712e-17</v>
+        <v>3.885341036788755e-17</v>
       </c>
       <c r="K4" t="b">
         <v>0</v>
@@ -7310,16 +7310,16 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>0.09894488800110718</v>
+        <v>0.09894488800110712</v>
       </c>
       <c r="B5" s="2" t="n">
-        <v>0.161876088596235</v>
+        <v>0.1618760885962355</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>0</v>
+        <v>1.108788482893477e-16</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>0.4758165544077424</v>
+        <v>0.4758165544077456</v>
       </c>
       <c r="E5" s="2" t="n">
         <v>0</v>
@@ -7328,16 +7328,16 @@
         <v>0</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>1.269520981338025e-16</v>
+        <v>0</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>0.5241834455922583</v>
+        <v>0.5241834455922544</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>0</v>
+        <v>2.706168622523819e-16</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>1.179288761058581e-17</v>
+        <v>0</v>
       </c>
       <c r="K5" t="b">
         <v>0</v>
@@ -7348,31 +7348,31 @@
         <v>0.0998660335129035</v>
       </c>
       <c r="B6" s="2" t="n">
-        <v>0.13662454428186</v>
+        <v>0.1366245442818596</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>0</v>
+        <v>1.304791449717892e-17</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>0.3010887392103265</v>
+        <v>0.3010887392103233</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>1.724959234714576e-17</v>
+        <v>1.110481603489779e-17</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>3.184204494451667e-17</v>
+        <v>9.062111293291953e-17</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>2.638804680404088e-17</v>
+        <v>0</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>0.6989112607896735</v>
+        <v>0.6989112607896767</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>0</v>
+        <v>5.551115123125783e-17</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>1.321466327748923e-16</v>
+        <v>0</v>
       </c>
       <c r="K6" t="b">
         <v>0</v>
@@ -7383,31 +7383,31 @@
         <v>0.1007871790246999</v>
       </c>
       <c r="B7" s="2" t="n">
-        <v>0.121078629662418</v>
+        <v>0.1210786296624181</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>4.941347279054521e-17</v>
+        <v>6.636285367910951e-18</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>0.1263609240129075</v>
+        <v>0.1263609240129097</v>
       </c>
       <c r="E7" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>0</v>
+        <v>1.989281539099085e-18</v>
       </c>
       <c r="G7" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>0.8736390759870927</v>
+        <v>0.8736390759870905</v>
       </c>
       <c r="I7" s="2" t="n">
         <v>0</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>6.641347056427596e-17</v>
+        <v>0</v>
       </c>
       <c r="K7" t="b">
         <v>0</v>
@@ -7421,25 +7421,25 @@
         <v>0.1162834320011623</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>1.243919634516214e-17</v>
+        <v>2.266373330701999e-17</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>0.05355770051053205</v>
+        <v>0.05355770051053174</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>6.995577733517971e-18</v>
+        <v>0</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>0</v>
+        <v>3.546820731340557e-18</v>
       </c>
       <c r="G8" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>0.8643595252730931</v>
+        <v>0.8643595252730918</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>0.08208277421637505</v>
+        <v>0.0820827742163765</v>
       </c>
       <c r="J8" s="2" t="n">
         <v>0</v>
@@ -7456,28 +7456,28 @@
         <v>0.1141351483727779</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>1.018797680429931e-17</v>
+        <v>0</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>0.0338283042389759</v>
+        <v>0.03382830423897654</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>0</v>
+        <v>5.193335980731027e-19</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>5.88300587723684e-18</v>
+        <v>5.928002969625661e-18</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>6.965680639581048e-18</v>
+        <v>0</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>0.7592642839081012</v>
+        <v>0.7592642839081032</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>0.2069074118529229</v>
+        <v>0.2069074118529204</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>1.41699028099773e-17</v>
+        <v>2.834394525777843e-18</v>
       </c>
       <c r="K9" t="b">
         <v>0</v>
@@ -7491,28 +7491,28 @@
         <v>0.1132992351990149</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>0</v>
+        <v>5.85088008315908e-19</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>0.0267618810851756</v>
+        <v>0.02676188108517542</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>0</v>
+        <v>8.574091008581655e-19</v>
       </c>
       <c r="F10" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>3.259405570682519e-18</v>
+        <v>6.056285572868247e-19</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>0.7147499059332615</v>
+        <v>0.714749905933261</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>0.2298277901187272</v>
+        <v>0.2298277901187274</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>0.02866042286283569</v>
+        <v>0.02866042286283615</v>
       </c>
       <c r="K10" t="b">
         <v>0</v>
@@ -7529,25 +7529,25 @@
         <v>0</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>0.02195564499597495</v>
+        <v>0.02195564499597489</v>
       </c>
       <c r="E11" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>5.624229728082778e-19</v>
+        <v>2.847089493958517e-19</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>3.182156291004638e-18</v>
+        <v>2.923640096566624e-18</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>0.6810501073175148</v>
+        <v>0.681050107317515</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>0.2345573042517479</v>
+        <v>0.2345573042517477</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>0.06243694343476232</v>
+        <v>0.06243694343476242</v>
       </c>
       <c r="K11" t="b">
         <v>0</v>
@@ -7558,13 +7558,13 @@
         <v>0.1053929065836819</v>
       </c>
       <c r="B12" s="2" t="n">
-        <v>0.1119651078903085</v>
+        <v>0.1119651078903086</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>0</v>
+        <v>1.209139532205514e-19</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>0.01714991708724638</v>
+        <v>0.01714991708724662</v>
       </c>
       <c r="E12" s="2" t="n">
         <v>0</v>
@@ -7573,16 +7573,16 @@
         <v>0</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>1.174631929436902e-18</v>
+        <v>1.455890817652532e-18</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>0.6473504362674416</v>
+        <v>0.6473504362674432</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>0.2392858237042008</v>
+        <v>0.2392858237042007</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>0.0962138229411111</v>
+        <v>0.09621382294110957</v>
       </c>
       <c r="K12" t="b">
         <v>0</v>
@@ -7593,31 +7593,31 @@
         <v>0.1063140520954783</v>
       </c>
       <c r="B13" s="2" t="n">
-        <v>0.1114482820204132</v>
+        <v>0.1114482820204133</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>0</v>
+        <v>2.498747194400186e-20</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>0.01234386115521104</v>
+        <v>0.01234386115521106</v>
       </c>
       <c r="E13" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>2.361486804196368e-18</v>
+        <v>1.976233745062689e-18</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>0</v>
+        <v>4.773030657777982e-19</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>0.6136510292947182</v>
+        <v>0.6136510292947185</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>0.2440145198021764</v>
+        <v>0.2440145198021765</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>0.1299905897478944</v>
+        <v>0.129990589747894</v>
       </c>
       <c r="K13" t="b">
         <v>0</v>
@@ -7628,31 +7628,31 @@
         <v>0.1072351976072747</v>
       </c>
       <c r="B14" s="2" t="n">
-        <v>0.1110335698632131</v>
+        <v>0.111033569863213</v>
       </c>
       <c r="C14" s="2" t="n">
-        <v>8.363887106464166e-19</v>
+        <v>0</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>0.007538307479885637</v>
+        <v>0.007538307479885565</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>0</v>
+        <v>2.174227696483382e-19</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>7.230097270150865e-19</v>
+        <v>0</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>0</v>
+        <v>1.582734001503864e-18</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>0.579951212690211</v>
+        <v>0.5799512126902107</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>0.2487429525298342</v>
+        <v>0.2487429525298344</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>0.1637675273000692</v>
+        <v>0.1637675273000693</v>
       </c>
       <c r="K14" t="b">
         <v>0</v>
@@ -7666,10 +7666,10 @@
         <v>0.1107111837609897</v>
       </c>
       <c r="C15" s="2" t="n">
-        <v>0.006135358628416578</v>
+        <v>0.006135358628416437</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>0.003366839761846044</v>
+        <v>0.003366839761846085</v>
       </c>
       <c r="E15" s="2" t="n">
         <v>0</v>
@@ -7678,16 +7678,16 @@
         <v>0</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>0</v>
+        <v>6.454391058077769e-19</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>0.5565618843682874</v>
+        <v>0.5565618843682877</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>0.251451887936813</v>
+        <v>0.2514518879368131</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>0.182484029304637</v>
+        <v>0.1824840293046367</v>
       </c>
       <c r="K15" t="b">
         <v>0</v>
@@ -7701,28 +7701,28 @@
         <v>0.1104280120364591</v>
       </c>
       <c r="C16" s="2" t="n">
-        <v>0.01729681281747945</v>
+        <v>0.01729681281747918</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>0</v>
+        <v>1.633926555253545e-18</v>
       </c>
       <c r="E16" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>1.396431742001195e-18</v>
+        <v>0</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>0</v>
+        <v>9.656175598699024e-19</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>0.5412184346017008</v>
+        <v>0.5412184346017014</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>0.2525824737138867</v>
+        <v>0.2525824737138868</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>0.188902278866933</v>
+        <v>0.1889022788669328</v>
       </c>
       <c r="K16" t="b">
         <v>0</v>
@@ -7736,28 +7736,28 @@
         <v>0.1101811834058612</v>
       </c>
       <c r="C17" s="2" t="n">
-        <v>0.02878008169748257</v>
+        <v>0.02878008169748303</v>
       </c>
       <c r="D17" s="2" t="n">
-        <v>2.966659240142665e-19</v>
+        <v>0</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>3.981434735877491e-18</v>
+        <v>1.219727444046192e-19</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>3.007606303087473e-18</v>
+        <v>0</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>0</v>
+        <v>1.070649645329436e-18</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>0.5217336274162692</v>
+        <v>0.5217336274162689</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>0.2544968186238762</v>
+        <v>0.2544968186238761</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>0.1949894722623721</v>
+        <v>0.1949894722623719</v>
       </c>
       <c r="K17" t="b">
         <v>0</v>
@@ -7771,10 +7771,10 @@
         <v>0.1099740044687139</v>
       </c>
       <c r="C18" s="2" t="n">
-        <v>0.04026160261389346</v>
+        <v>0.04026160261389322</v>
       </c>
       <c r="D18" s="2" t="n">
-        <v>0</v>
+        <v>3.472835083742631e-19</v>
       </c>
       <c r="E18" s="2" t="n">
         <v>0</v>
@@ -7783,7 +7783,7 @@
         <v>0</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>0</v>
+        <v>1.063026348804147e-18</v>
       </c>
       <c r="H18" s="2" t="n">
         <v>0.5022408513474832</v>
@@ -7792,7 +7792,7 @@
         <v>0.2564182058289725</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>0.2010793402096509</v>
+        <v>0.2010793402096512</v>
       </c>
       <c r="K18" t="b">
         <v>0</v>
@@ -7806,28 +7806,28 @@
         <v>0.1098066996570172</v>
       </c>
       <c r="C19" s="2" t="n">
-        <v>0.05174444161545532</v>
+        <v>0.05174444161545522</v>
       </c>
       <c r="D19" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>1.412995201848167e-19</v>
+        <v>4.777265822514254e-19</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>8.778102261329954e-20</v>
+        <v>2.564815764286021e-18</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>1.613714445626992e-18</v>
+        <v>9.876404164985142e-19</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>0.4827526890566378</v>
+        <v>0.482752689056638</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>0.2583361572265024</v>
+        <v>0.2583361572265028</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>0.2071667121014044</v>
+        <v>0.2071667121014041</v>
       </c>
       <c r="K19" t="b">
         <v>0</v>
@@ -7841,28 +7841,28 @@
         <v>0.109678540322404</v>
       </c>
       <c r="C20" s="2" t="n">
-        <v>0.06107187495902944</v>
+        <v>0.06107187495902933</v>
       </c>
       <c r="D20" s="2" t="n">
-        <v>3.781248990540869e-18</v>
+        <v>5.993605134771429e-18</v>
       </c>
       <c r="E20" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>5.855566647424098e-19</v>
+        <v>0</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>0.002197935521458924</v>
+        <v>0.002197935521459024</v>
       </c>
       <c r="H20" s="2" t="n">
         <v>0.4654449654800258</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>0.259869211778648</v>
+        <v>0.2598692117786476</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>0.2114160122608379</v>
+        <v>0.2114160122608383</v>
       </c>
       <c r="K20" t="b">
         <v>0</v>
@@ -7876,28 +7876,28 @@
         <v>0.10957484994231</v>
       </c>
       <c r="C21" s="2" t="n">
-        <v>0.06526729798585322</v>
+        <v>0.06526729798585307</v>
       </c>
       <c r="D21" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>2.358616231810077e-19</v>
+        <v>5.759824041329242e-20</v>
       </c>
       <c r="F21" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>0.009640478721340435</v>
+        <v>0.009640478721340245</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>0.4533615236137789</v>
+        <v>0.4533615236137792</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>0.2604783575675375</v>
+        <v>0.2604783575675376</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>0.2112523421114899</v>
+        <v>0.21125234211149</v>
       </c>
       <c r="K21" t="b">
         <v>0</v>
@@ -7911,28 +7911,28 @@
         <v>0.1094904984479527</v>
       </c>
       <c r="C22" s="2" t="n">
-        <v>0.06946311280584751</v>
+        <v>0.06946311280584772</v>
       </c>
       <c r="D22" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>7.435216379809497e-19</v>
+        <v>1.368805242762949e-18</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>0</v>
+        <v>1.741499739554841e-18</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>0.01708276106248051</v>
+        <v>0.0170827610624807</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>0.4412795182643953</v>
+        <v>0.4412795182643955</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>0.2610855564576613</v>
+        <v>0.261085556457661</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>0.2110890514096155</v>
+        <v>0.2110890514096151</v>
       </c>
       <c r="K22" t="b">
         <v>0</v>
@@ -7943,31 +7943,31 @@
         <v>0.1155255072134423</v>
       </c>
       <c r="B23" s="2" t="n">
-        <v>0.1094255305538441</v>
+        <v>0.1094255305538442</v>
       </c>
       <c r="C23" s="2" t="n">
-        <v>0.07365205079573729</v>
+        <v>0.07365205079573704</v>
       </c>
       <c r="D23" s="2" t="n">
-        <v>2.771990714546318e-19</v>
+        <v>1.517036008532452e-18</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>4.926657441219292e-21</v>
+        <v>0</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>1.67460142157509e-18</v>
+        <v>0</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>0.02452707164644399</v>
+        <v>0.02452707164644385</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>0.4291884849767938</v>
+        <v>0.4291884849767942</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>0.2616969873274265</v>
+        <v>0.2616969873274263</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>0.2109354052535984</v>
+        <v>0.2109354052535987</v>
       </c>
       <c r="K23" t="b">
         <v>0</v>
@@ -7981,28 +7981,28 @@
         <v>0.1093799808064924</v>
       </c>
       <c r="C24" s="2" t="n">
-        <v>0.07784468957383618</v>
+        <v>0.07784468957383611</v>
       </c>
       <c r="D24" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>9.618773965425015e-19</v>
+        <v>9.546061315555965e-19</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>0</v>
+        <v>4.726443845678996e-19</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>0.03197021483881322</v>
+        <v>0.03197021483881328</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>0.4171020387683898</v>
+        <v>0.4171020387683896</v>
       </c>
       <c r="I24" s="2" t="n">
         <v>0.2623062614456784</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>0.2107767953732824</v>
+        <v>0.2107767953732826</v>
       </c>
       <c r="K24" t="b">
         <v>0</v>
@@ -8016,28 +8016,28 @@
         <v>0.1093538734686002</v>
       </c>
       <c r="C25" s="2" t="n">
-        <v>0.08203733313773964</v>
+        <v>0.08203733313773971</v>
       </c>
       <c r="D25" s="2" t="n">
-        <v>0</v>
+        <v>1.827388880406428e-17</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>1.574756397948861e-18</v>
+        <v>0</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>2.925973450944501e-18</v>
+        <v>1.01643953670516e-20</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>0.03941336211944144</v>
+        <v>0.0394133621194415</v>
       </c>
       <c r="H25" s="2" t="n">
         <v>0.4050156094552341</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>0.2629155360325779</v>
+        <v>0.2629155360325781</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>0.2106181592550069</v>
+        <v>0.2106181592550065</v>
       </c>
       <c r="K25" t="b">
         <v>0</v>
@@ -8051,25 +8051,25 @@
         <v>0.1093469788600055</v>
       </c>
       <c r="C26" s="2" t="n">
-        <v>0.08556588192474855</v>
+        <v>0.08556588192474845</v>
       </c>
       <c r="D26" s="2" t="n">
-        <v>0</v>
+        <v>1.776312793686993e-17</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>7.118723266119786e-19</v>
+        <v>0</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>1.224101427947435e-18</v>
+        <v>0</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>0.04567755617018877</v>
+        <v>0.04567755617018905</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>0.3948436233141227</v>
+        <v>0.3948436233141226</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>0.2634282965915295</v>
+        <v>0.2634282965915293</v>
       </c>
       <c r="J26" s="2" t="n">
         <v>0.2104846419994106</v>
@@ -8086,10 +8086,10 @@
         <v>0.1093472224661616</v>
       </c>
       <c r="C27" s="2" t="n">
-        <v>0.08622997552522801</v>
+        <v>0.08622997552522807</v>
       </c>
       <c r="D27" s="2" t="n">
-        <v>0</v>
+        <v>4.311397701524389e-18</v>
       </c>
       <c r="E27" s="2" t="n">
         <v>0</v>
@@ -8098,16 +8098,16 @@
         <v>0</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>0.04685651447944759</v>
+        <v>0.04685651447944752</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>0.3929291977862459</v>
+        <v>0.3929291977862457</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>0.2635248007697365</v>
+        <v>0.2635248007697368</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>0.2104595114393419</v>
+        <v>0.2104595114393418</v>
       </c>
       <c r="K27" t="b">
         <v>1</v>
@@ -8121,28 +8121,28 @@
         <v>0.1093600313490333</v>
       </c>
       <c r="C28" s="2" t="n">
-        <v>0.09042261848679778</v>
+        <v>0.09042261848679785</v>
       </c>
       <c r="D28" s="2" t="n">
-        <v>2.793523245105177e-18</v>
+        <v>1.54835637524616e-17</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>6.080636012940202e-19</v>
+        <v>0</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>1.540757923691568e-18</v>
+        <v>0</v>
       </c>
       <c r="G28" s="2" t="n">
         <v>0.05429967120675538</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>0.3808428000732867</v>
+        <v>0.3808428000732871</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>0.2641340619931514</v>
+        <v>0.264134061993151</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>0.2103008482400088</v>
+        <v>0.2103008482400086</v>
       </c>
       <c r="K28" t="b">
         <v>1</v>
@@ -8156,28 +8156,28 @@
         <v>0.1093922932814668</v>
       </c>
       <c r="C29" s="2" t="n">
-        <v>0.09461525835233185</v>
+        <v>0.09461525835233182</v>
       </c>
       <c r="D29" s="2" t="n">
-        <v>0</v>
+        <v>2.797749824780954e-18</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>1.216186949536698e-18</v>
+        <v>0</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>2.527411981171513e-18</v>
+        <v>0</v>
       </c>
       <c r="G29" s="2" t="n">
-        <v>0.06174282354240782</v>
+        <v>0.06174282354240813</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>0.368756384898113</v>
+        <v>0.3687563848981129</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>0.2647433260765337</v>
+        <v>0.2647433260765336</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>0.2101422071306137</v>
+        <v>0.2101422071306135</v>
       </c>
       <c r="K29" t="b">
         <v>1</v>
@@ -8191,28 +8191,28 @@
         <v>0.1094439910603356</v>
       </c>
       <c r="C30" s="2" t="n">
-        <v>0.09880789386597232</v>
+        <v>0.09880789386597237</v>
       </c>
       <c r="D30" s="2" t="n">
-        <v>6.768535921612014e-18</v>
+        <v>2.274283463377796e-19</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>7.711478123334585e-19</v>
+        <v>2.541098841762901e-21</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>0</v>
+        <v>4.701032857261367e-19</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>0.06918596206749543</v>
+        <v>0.06918596206749542</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>0.356669921463194</v>
+        <v>0.3566699214631942</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>0.2653526014994654</v>
+        <v>0.2653526014994653</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>0.2099836211038728</v>
+        <v>0.2099836211038726</v>
       </c>
       <c r="K30" t="b">
         <v>1</v>
@@ -8226,28 +8226,28 @@
         <v>0.1095150971609429</v>
       </c>
       <c r="C31" s="2" t="n">
-        <v>0.1030005278055224</v>
+        <v>0.1030005278055226</v>
       </c>
       <c r="D31" s="2" t="n">
-        <v>1.54159292797051e-18</v>
+        <v>1.616138863361205e-17</v>
       </c>
       <c r="E31" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F31" s="2" t="n">
-        <v>4.322650768900076e-18</v>
+        <v>0</v>
       </c>
       <c r="G31" s="2" t="n">
-        <v>0.07662909141286492</v>
+        <v>0.07662909141286542</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>0.3445834261546328</v>
+        <v>0.3445834261546325</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>0.2659618869492472</v>
+        <v>0.2659618869492476</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>0.2098250676777327</v>
+        <v>0.209825067677732</v>
       </c>
       <c r="K31" t="b">
         <v>1</v>
@@ -8261,7 +8261,7 @@
         <v>0.1096055738101233</v>
       </c>
       <c r="C32" s="2" t="n">
-        <v>0.1071931632450051</v>
+        <v>0.1071931632450049</v>
       </c>
       <c r="D32" s="2" t="n">
         <v>0</v>
@@ -8270,19 +8270,19 @@
         <v>0</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>1.357375420821095e-18</v>
+        <v>0</v>
       </c>
       <c r="G32" s="2" t="n">
         <v>0.08407222317217926</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>0.3324969385437331</v>
+        <v>0.3324969385437327</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>0.2665711729575012</v>
+        <v>0.2665711729575016</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>0.2096665020815814</v>
+        <v>0.2096665020815816</v>
       </c>
       <c r="K32" t="b">
         <v>1</v>
@@ -8296,28 +8296,28 @@
         <v>0.1097153730861891</v>
       </c>
       <c r="C33" s="2" t="n">
-        <v>0.1113858008182984</v>
+        <v>0.1113858008182985</v>
       </c>
       <c r="D33" s="2" t="n">
-        <v>0</v>
+        <v>1.894357422798721e-17</v>
       </c>
       <c r="E33" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>5.564490485453433e-19</v>
+        <v>0</v>
       </c>
       <c r="G33" s="2" t="n">
-        <v>0.09151536088920144</v>
+        <v>0.09151536088920112</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>0.320410471864781</v>
+        <v>0.3204104718647817</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>0.2671804544593492</v>
+        <v>0.2671804544593491</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>0.2095079119683698</v>
+        <v>0.2095079119683696</v>
       </c>
       <c r="K33" t="b">
         <v>1</v>
@@ -8331,10 +8331,10 @@
         <v>0.1098444370451074</v>
       </c>
       <c r="C34" s="2" t="n">
-        <v>0.1155784398096605</v>
+        <v>0.1155784398096604</v>
       </c>
       <c r="D34" s="2" t="n">
-        <v>7.125157406684637e-18</v>
+        <v>1.39876903327207e-17</v>
       </c>
       <c r="E34" s="2" t="n">
         <v>0</v>
@@ -8343,16 +8343,16 @@
         <v>0</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>0.09895850262685182</v>
+        <v>0.09895850262685175</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>0.3083240202212085</v>
+        <v>0.3083240202212082</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>0.2677897316524659</v>
+        <v>0.2677897316524661</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>0.2093493056898132</v>
+        <v>0.2093493056898136</v>
       </c>
       <c r="K34" t="b">
         <v>1</v>
@@ -8372,22 +8372,22 @@
         <v>0</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>6.124341638682814e-18</v>
+        <v>2.672812465060945e-18</v>
       </c>
       <c r="F35" s="2" t="n">
-        <v>8.773405087267641e-18</v>
+        <v>0</v>
       </c>
       <c r="G35" s="2" t="n">
-        <v>0.1064016461225506</v>
+        <v>0.1064016461225509</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>0.2962375753245199</v>
+        <v>0.2962375753245203</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>0.2683990064114244</v>
+        <v>0.2683990064114241</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>0.2091906928722861</v>
+        <v>0.2091906928722857</v>
       </c>
       <c r="K35" t="b">
         <v>1</v>
@@ -8401,28 +8401,28 @@
         <v>0.1101600780580229</v>
       </c>
       <c r="C36" s="2" t="n">
-        <v>0.1239636742420718</v>
+        <v>0.1239636742420719</v>
       </c>
       <c r="D36" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>2.002241403722401e-18</v>
+        <v>0</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>0</v>
+        <v>1.529741502741266e-18</v>
       </c>
       <c r="G36" s="2" t="n">
         <v>0.1138450135583851</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>0.2841517784173822</v>
+        <v>0.2841517784173819</v>
       </c>
       <c r="I36" s="2" t="n">
         <v>0.2690080369098871</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>0.2090314968722737</v>
+        <v>0.2090314968722739</v>
       </c>
       <c r="K36" t="b">
         <v>1</v>
@@ -8442,22 +8442,22 @@
         <v>0</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>7.929509444073994e-19</v>
+        <v>5.79021134831199e-18</v>
       </c>
       <c r="F37" s="2" t="n">
-        <v>3.361332365485249e-18</v>
+        <v>1.272338777982525e-17</v>
       </c>
       <c r="G37" s="2" t="n">
-        <v>0.1212901792910122</v>
+        <v>0.1212901792910117</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>0.2720685065678042</v>
+        <v>0.272068506567804</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>0.2696166165710555</v>
+        <v>0.2696166165710559</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>0.2088697816944956</v>
+        <v>0.2088697816944959</v>
       </c>
       <c r="K37" t="b">
         <v>1</v>
@@ -8468,28 +8468,28 @@
         <v>0.1284215443785919</v>
       </c>
       <c r="B38" s="2" t="n">
-        <v>0.1105518392183673</v>
+        <v>0.1105518392183672</v>
       </c>
       <c r="C38" s="2" t="n">
         <v>0.132345675180275</v>
       </c>
       <c r="D38" s="2" t="n">
-        <v>2.508248191691972e-17</v>
+        <v>2.054213715769289e-17</v>
       </c>
       <c r="E38" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F38" s="2" t="n">
-        <v>0</v>
+        <v>1.023427558520008e-18</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>0.1287336355165928</v>
+        <v>0.1287336355165929</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>0.2599780606363274</v>
+        <v>0.2599780606363271</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>0.2702283306677833</v>
+        <v>0.2702283306677831</v>
       </c>
       <c r="J38" s="2" t="n">
         <v>0.2087142979990217</v>
@@ -8509,25 +8509,25 @@
         <v>0.1365386014549501</v>
       </c>
       <c r="D39" s="2" t="n">
-        <v>1.340423546516761e-17</v>
+        <v>2.293087594806842e-17</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>3.737937158688627e-18</v>
+        <v>0</v>
       </c>
       <c r="F39" s="2" t="n">
-        <v>3.516397107821945e-18</v>
+        <v>0</v>
       </c>
       <c r="G39" s="2" t="n">
-        <v>0.136176572522704</v>
+        <v>0.1361765725227039</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>0.2478918530769881</v>
+        <v>0.2478918530769884</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>0.2708372242599328</v>
+        <v>0.2708372242599325</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>0.208555748685425</v>
+        <v>0.2085557486854251</v>
       </c>
       <c r="K39" t="b">
         <v>1</v>
@@ -8541,25 +8541,25 @@
         <v>0.1110189146915058</v>
       </c>
       <c r="C40" s="2" t="n">
-        <v>0.1407322734884168</v>
+        <v>0.1407322734884165</v>
       </c>
       <c r="D40" s="2" t="n">
-        <v>2.330843169505761e-17</v>
+        <v>0</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>0</v>
+        <v>2.710505431213761e-18</v>
       </c>
       <c r="F40" s="2" t="n">
-        <v>0</v>
+        <v>4.98732999343332e-18</v>
       </c>
       <c r="G40" s="2" t="n">
-        <v>0.1436188974967418</v>
+        <v>0.1436188974967423</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>0.2358053842025342</v>
+        <v>0.2358053842025345</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>0.2714460655078218</v>
+        <v>0.2714460655078211</v>
       </c>
       <c r="J40" s="2" t="n">
         <v>0.2083973793044855</v>
@@ -8576,28 +8576,28 @@
         <v>0.1112804049121456</v>
       </c>
       <c r="C41" s="2" t="n">
-        <v>0.1449250683626374</v>
+        <v>0.144925068362637</v>
       </c>
       <c r="D41" s="2" t="n">
-        <v>2.19830432205906e-17</v>
+        <v>0</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>0</v>
+        <v>2.710505431213761e-19</v>
       </c>
       <c r="F41" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G41" s="2" t="n">
-        <v>0.1510618983574981</v>
+        <v>0.1510618983574984</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>0.2237189320534056</v>
+        <v>0.2237189320534057</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>0.2720552174577932</v>
+        <v>0.2720552174577928</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>0.2082388837686658</v>
+        <v>0.2082388837686661</v>
       </c>
       <c r="K41" t="b">
         <v>1</v>
@@ -8611,28 +8611,28 @@
         <v>0.1115603585181689</v>
       </c>
       <c r="C42" s="2" t="n">
-        <v>0.1491175094735913</v>
+        <v>0.1491175094735914</v>
       </c>
       <c r="D42" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>1.462304045423125e-18</v>
+        <v>6.613633252161577e-18</v>
       </c>
       <c r="F42" s="2" t="n">
-        <v>5.486136353442025e-18</v>
+        <v>7.325140927855189e-18</v>
       </c>
       <c r="G42" s="2" t="n">
-        <v>0.1585051595755728</v>
+        <v>0.158505159575573</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>0.2116324683152658</v>
+        <v>0.2116324683152654</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>0.2726644800461313</v>
+        <v>0.2726644800461314</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>0.2080803825894388</v>
+        <v>0.2080803825894389</v>
       </c>
       <c r="K42" t="b">
         <v>1</v>
@@ -8646,28 +8646,28 @@
         <v>0.1118586368822811</v>
       </c>
       <c r="C43" s="2" t="n">
-        <v>0.1533096217394715</v>
+        <v>0.153309621739471</v>
       </c>
       <c r="D43" s="2" t="n">
-        <v>0</v>
+        <v>4.228388472693467e-18</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>2.908742002469381e-18</v>
+        <v>0</v>
       </c>
       <c r="F43" s="2" t="n">
-        <v>2.839951447918161e-18</v>
+        <v>1.301042606982605e-18</v>
       </c>
       <c r="G43" s="2" t="n">
-        <v>0.1659486761982064</v>
+        <v>0.1659486761982065</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>0.1995460114074293</v>
+        <v>0.1995460114074276</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>0.2732738648416163</v>
+        <v>0.2732738648416169</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>0.2079218258132765</v>
+        <v>0.2079218258132781</v>
       </c>
       <c r="K43" t="b">
         <v>1</v>
@@ -8681,28 +8681,28 @@
         <v>0.1121750938259657</v>
       </c>
       <c r="C44" s="2" t="n">
-        <v>0.1575011901993978</v>
+        <v>0.1575011901993981</v>
       </c>
       <c r="D44" s="2" t="n">
-        <v>0</v>
+        <v>1.431146867680866e-17</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>1.728941165829424e-18</v>
+        <v>2.49366499671666e-18</v>
       </c>
       <c r="F44" s="2" t="n">
-        <v>1.208096734714583e-17</v>
+        <v>9.75781955236954e-19</v>
       </c>
       <c r="G44" s="2" t="n">
-        <v>0.1733926179045095</v>
+        <v>0.1733926179045094</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>0.1874596012690913</v>
+        <v>0.1874596012690914</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>0.2738834128263341</v>
+        <v>0.2738834128263335</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>0.2077631778006673</v>
+        <v>0.2077631778006678</v>
       </c>
       <c r="K44" t="b">
         <v>1</v>
@@ -8725,16 +8725,16 @@
         <v>0</v>
       </c>
       <c r="F45" s="2" t="n">
-        <v>7.495644899774745e-20</v>
+        <v>0</v>
       </c>
       <c r="G45" s="2" t="n">
         <v>0.180833605129308</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>0.1753730994522147</v>
+        <v>0.175373099452214</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>0.2744919630172833</v>
+        <v>0.2744919630172837</v>
       </c>
       <c r="J45" s="2" t="n">
         <v>0.2076045794142138</v>
@@ -8754,10 +8754,10 @@
         <v>0.1658885678590159</v>
       </c>
       <c r="D46" s="2" t="n">
-        <v>2.823027199825825e-17</v>
+        <v>0</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>0</v>
+        <v>2.373879317851631e-18</v>
       </c>
       <c r="F46" s="2" t="n">
         <v>0</v>
@@ -8766,13 +8766,13 @@
         <v>0.1882773542287804</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>0.1632866543380277</v>
+        <v>0.1632866543380273</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>0.2751014556042651</v>
+        <v>0.2751014556042654</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>0.2074459679699109</v>
+        <v>0.2074459679699112</v>
       </c>
       <c r="K46" t="b">
         <v>1</v>
@@ -8786,10 +8786,10 @@
         <v>0.1132319682145252</v>
       </c>
       <c r="C47" s="2" t="n">
-        <v>0.1700827512221682</v>
+        <v>0.1700827512221681</v>
       </c>
       <c r="D47" s="2" t="n">
-        <v>1.140588764473795e-17</v>
+        <v>1.488859176300629e-17</v>
       </c>
       <c r="E47" s="2" t="n">
         <v>0</v>
@@ -8801,13 +8801,13 @@
         <v>0.1957193549116364</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>0.1512001865506704</v>
+        <v>0.1512001865506696</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>0.275710325155443</v>
+        <v>0.2757103251554433</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>0.2072873821600819</v>
+        <v>0.2072873821600825</v>
       </c>
       <c r="K47" t="b">
         <v>1</v>
@@ -8821,28 +8821,28 @@
         <v>0.1136195386530185</v>
       </c>
       <c r="C48" s="2" t="n">
-        <v>0.1742753913654378</v>
+        <v>0.1742753913654377</v>
       </c>
       <c r="D48" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>0</v>
+        <v>5.789615778270952e-18</v>
       </c>
       <c r="F48" s="2" t="n">
-        <v>3.47185349644322e-18</v>
+        <v>1.062102553496048e-17</v>
       </c>
       <c r="G48" s="2" t="n">
-        <v>0.2031624968452371</v>
+        <v>0.203162496845237</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>0.1391137305097979</v>
+        <v>0.1391137305097982</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>0.2763196113002427</v>
+        <v>0.2763196113002426</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>0.2071287699792845</v>
+        <v>0.2071287699792846</v>
       </c>
       <c r="K48" t="b">
         <v>1</v>
@@ -8856,28 +8856,28 @@
         <v>0.1140244556194063</v>
       </c>
       <c r="C49" s="2" t="n">
-        <v>0.1784676293893829</v>
+        <v>0.1784676293893831</v>
       </c>
       <c r="D49" s="2" t="n">
-        <v>0</v>
+        <v>9.475334064460231e-18</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>2.971888763564332e-18</v>
+        <v>0</v>
       </c>
       <c r="F49" s="2" t="n">
-        <v>6.926294966362984e-18</v>
+        <v>2.14299335655338e-19</v>
       </c>
       <c r="G49" s="2" t="n">
         <v>0.2106060919321661</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>0.1270234610231586</v>
+        <v>0.1270234610231581</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>0.2769346339160213</v>
+        <v>0.2769346339160214</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>0.2069681837392711</v>
+        <v>0.2069681837392713</v>
       </c>
       <c r="K49" t="b">
         <v>1</v>
@@ -8891,28 +8891,28 @@
         <v>0.1144465349893637</v>
       </c>
       <c r="C50" s="2" t="n">
-        <v>0.1826611404718393</v>
+        <v>0.1826611404718396</v>
       </c>
       <c r="D50" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>5.318983494844309e-18</v>
+        <v>3.783060900674519e-18</v>
       </c>
       <c r="F50" s="2" t="n">
-        <v>3.735792711855121e-18</v>
+        <v>6.460320288708549e-18</v>
       </c>
       <c r="G50" s="2" t="n">
-        <v>0.2180484645299627</v>
+        <v>0.2180484645299625</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>0.1149404550884048</v>
+        <v>0.1149404550884044</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>0.2775386384462518</v>
+        <v>0.277538638446252</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>0.2068113014635413</v>
+        <v>0.2068113014635416</v>
       </c>
       <c r="K50" t="b">
         <v>1</v>
@@ -8920,34 +8920,34 @@
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>0.140396436031945</v>
+        <v>0.1403964360319451</v>
       </c>
       <c r="B51" s="2" t="n">
         <v>0.1148855876096416</v>
       </c>
       <c r="C51" s="2" t="n">
-        <v>0.1868535390410661</v>
+        <v>0.1868535390410662</v>
       </c>
       <c r="D51" s="2" t="n">
-        <v>1.210082713152576e-17</v>
+        <v>3.206983205335029e-17</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>0</v>
+        <v>1.913023911373837e-18</v>
       </c>
       <c r="F51" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G51" s="2" t="n">
-        <v>0.2254917651876365</v>
+        <v>0.2254917651876364</v>
       </c>
       <c r="H51" s="2" t="n">
         <v>0.1028542750524873</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>0.2781475574430336</v>
+        <v>0.2781475574430334</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>0.2066528632757764</v>
+        <v>0.2066528632757767</v>
       </c>
       <c r="K51" t="b">
         <v>1</v>
@@ -8961,28 +8961,28 @@
         <v>0.1153414196501431</v>
       </c>
       <c r="C52" s="2" t="n">
-        <v>0.1910467584623067</v>
+        <v>0.1910467584623066</v>
       </c>
       <c r="D52" s="2" t="n">
-        <v>6.418847931030393e-18</v>
+        <v>0</v>
       </c>
       <c r="E52" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F52" s="2" t="n">
-        <v>1.003125335842772e-18</v>
+        <v>0</v>
       </c>
       <c r="G52" s="2" t="n">
-        <v>0.2329345781998509</v>
+        <v>0.232934578199851</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>0.09076729122151195</v>
+        <v>0.09076729122151146</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>0.2787577099683721</v>
+        <v>0.2787577099683719</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>0.2064936621479585</v>
+        <v>0.206493662147959</v>
       </c>
       <c r="K52" t="b">
         <v>1</v>
@@ -8996,25 +8996,25 @@
         <v>0.1158138329846072</v>
       </c>
       <c r="C53" s="2" t="n">
-        <v>0.1952397206967951</v>
+        <v>0.195239720696795</v>
       </c>
       <c r="D53" s="2" t="n">
-        <v>4.746965756006355e-17</v>
+        <v>0</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>0</v>
+        <v>8.599078480525657e-18</v>
       </c>
       <c r="F53" s="2" t="n">
-        <v>0</v>
+        <v>1.139682830530661e-17</v>
       </c>
       <c r="G53" s="2" t="n">
-        <v>0.2403776954000592</v>
+        <v>0.2403776954000591</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>0.07868027873365196</v>
+        <v>0.07868027873365249</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>0.2793683393192031</v>
+        <v>0.2793683393192029</v>
       </c>
       <c r="J53" s="2" t="n">
         <v>0.2063339658502905</v>
@@ -9034,25 +9034,25 @@
         <v>0.1994309636344388</v>
       </c>
       <c r="D54" s="2" t="n">
-        <v>3.432250657154552e-19</v>
+        <v>0</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>2.109638101056453e-18</v>
+        <v>7.26415455565288e-18</v>
       </c>
       <c r="F54" s="2" t="n">
-        <v>0</v>
+        <v>1.586492710207305e-17</v>
       </c>
       <c r="G54" s="2" t="n">
         <v>0.2478223889848276</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>0.06659399022008382</v>
+        <v>0.06659399022008343</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>0.2799794574753707</v>
+        <v>0.279979457475371</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>0.2061731996852791</v>
+        <v>0.2061731996852792</v>
       </c>
       <c r="K54" t="b">
         <v>1</v>
@@ -9066,10 +9066,10 @@
         <v>0.1168075917438615</v>
       </c>
       <c r="C55" s="2" t="n">
-        <v>0.2036238652285512</v>
+        <v>0.2036238652285511</v>
       </c>
       <c r="D55" s="2" t="n">
-        <v>0</v>
+        <v>7.698682457594336e-18</v>
       </c>
       <c r="E55" s="2" t="n">
         <v>0</v>
@@ -9078,16 +9078,16 @@
         <v>0</v>
       </c>
       <c r="G55" s="2" t="n">
-        <v>0.2552645059818688</v>
+        <v>0.2552645059818685</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>0.05450863597262209</v>
+        <v>0.05450863597262121</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>0.2805845181543496</v>
+        <v>0.28058451815435</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>0.2060184746626082</v>
+        <v>0.206018474662609</v>
       </c>
       <c r="K55" t="b">
         <v>1</v>
@@ -9101,28 +9101,28 @@
         <v>0.1173285227212339</v>
       </c>
       <c r="C56" s="2" t="n">
-        <v>0.2078164929816406</v>
+        <v>0.2078164929816407</v>
       </c>
       <c r="D56" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>0</v>
+        <v>1.434906899873287e-18</v>
       </c>
       <c r="F56" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G56" s="2" t="n">
-        <v>0.2627076370862579</v>
+        <v>0.2627076370862578</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>0.0424221654449757</v>
+        <v>0.04242216544497576</v>
       </c>
       <c r="I56" s="2" t="n">
         <v>0.2811937629966152</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>0.2058599414905106</v>
+        <v>0.2058599414905104</v>
       </c>
       <c r="K56" t="b">
         <v>1</v>
@@ -9136,28 +9136,28 @@
         <v>0.1178652068091448</v>
       </c>
       <c r="C57" s="2" t="n">
-        <v>0.2120081880581156</v>
+        <v>0.2120081880581155</v>
       </c>
       <c r="D57" s="2" t="n">
-        <v>0</v>
+        <v>4.578213079909493e-17</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>3.453589259944531e-18</v>
+        <v>0</v>
       </c>
       <c r="F57" s="2" t="n">
-        <v>5.368907306913378e-18</v>
+        <v>0</v>
       </c>
       <c r="G57" s="2" t="n">
-        <v>0.270150935162858</v>
+        <v>0.2701509351628578</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>0.03033647979825832</v>
+        <v>0.03033647979825916</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>0.2818005349795565</v>
+        <v>0.2818005349795562</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>0.2057038620012115</v>
+        <v>0.2057038620012112</v>
       </c>
       <c r="K57" t="b">
         <v>1</v>
@@ -9171,28 +9171,28 @@
         <v>0.1184174298201149</v>
       </c>
       <c r="C58" s="2" t="n">
-        <v>0.2162018914381707</v>
+        <v>0.2162018914381704</v>
       </c>
       <c r="D58" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>4.565587507725512e-18</v>
+        <v>3.405072447962287e-19</v>
       </c>
       <c r="F58" s="2" t="n">
-        <v>1.341809610234805e-17</v>
+        <v>0</v>
       </c>
       <c r="G58" s="2" t="n">
-        <v>0.2775937429294341</v>
+        <v>0.277593742929434</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>0.01824918931250637</v>
+        <v>0.01824918931250614</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>0.2824120970108471</v>
+        <v>0.2824120970108474</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>0.2055430793090416</v>
+        <v>0.2055430793090422</v>
       </c>
       <c r="K58" t="b">
         <v>1</v>
@@ -9212,22 +9212,22 @@
         <v>0</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>1.692760689155498e-18</v>
+        <v>0</v>
       </c>
       <c r="F59" s="2" t="n">
-        <v>1.039857386263308e-17</v>
+        <v>0</v>
       </c>
       <c r="G59" s="2" t="n">
-        <v>0.2850367307542349</v>
+        <v>0.285036730754235</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>0.006162639183730225</v>
+        <v>0.006162639183731049</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>0.2830211485103305</v>
+        <v>0.2830211485103303</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>0.2053848859827814</v>
+        <v>0.2053848859827808</v>
       </c>
       <c r="K59" t="b">
         <v>1</v>
@@ -9241,28 +9241,28 @@
         <v>0.1195688849420593</v>
       </c>
       <c r="C60" s="2" t="n">
-        <v>0.2248194891490457</v>
+        <v>0.2248194891490456</v>
       </c>
       <c r="D60" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>5.473489347822608e-18</v>
+        <v>3.354250471127029e-18</v>
       </c>
       <c r="F60" s="2" t="n">
-        <v>5.005814858707256e-18</v>
+        <v>1.852376352350429e-17</v>
       </c>
       <c r="G60" s="2" t="n">
-        <v>0.2937021471878464</v>
+        <v>0.293702147187846</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>0</v>
+        <v>2.950893381644532e-17</v>
       </c>
       <c r="I60" s="2" t="n">
         <v>0.2800860154054124</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>0.2013923482576955</v>
+        <v>0.2013923482576959</v>
       </c>
       <c r="K60" t="b">
         <v>1</v>
@@ -9276,28 +9276,28 @@
         <v>0.1201767449899418</v>
       </c>
       <c r="C61" s="2" t="n">
-        <v>0.2294864475195106</v>
+        <v>0.2294864475195104</v>
       </c>
       <c r="D61" s="2" t="n">
-        <v>0</v>
+        <v>2.775642264857617e-17</v>
       </c>
       <c r="E61" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F61" s="2" t="n">
-        <v>0</v>
+        <v>4.15215550744058e-18</v>
       </c>
       <c r="G61" s="2" t="n">
-        <v>0.3036382499776653</v>
+        <v>0.3036382499776658</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>2.922998155784687e-17</v>
+        <v>0</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>0.2734617274349697</v>
+        <v>0.2734617274349695</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>0.1934135750678546</v>
+        <v>0.1934135750678543</v>
       </c>
       <c r="K61" t="b">
         <v>1</v>
@@ -9311,28 +9311,28 @@
         <v>0.1208095433588196</v>
       </c>
       <c r="C62" s="2" t="n">
-        <v>0.2341531023764462</v>
+        <v>0.2341531023764464</v>
       </c>
       <c r="D62" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>1.180532431066826e-17</v>
+        <v>1.536517766319301e-18</v>
       </c>
       <c r="F62" s="2" t="n">
-        <v>3.2636915993916e-18</v>
+        <v>0</v>
       </c>
       <c r="G62" s="2" t="n">
-        <v>0.3135751164566929</v>
+        <v>0.3135751164566931</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>0</v>
+        <v>1.055021887452594e-17</v>
       </c>
       <c r="I62" s="2" t="n">
         <v>0.2668392571157123</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>0.1854325240511486</v>
+        <v>0.1854325240511481</v>
       </c>
       <c r="K62" t="b">
         <v>1</v>
@@ -9346,10 +9346,10 @@
         <v>0.1214668902909845</v>
       </c>
       <c r="C63" s="2" t="n">
-        <v>0.23881928253571</v>
+        <v>0.2388192825357099</v>
       </c>
       <c r="D63" s="2" t="n">
-        <v>5.888466317462763e-17</v>
+        <v>1.398620802506301e-17</v>
       </c>
       <c r="E63" s="2" t="n">
         <v>0</v>
@@ -9358,16 +9358,16 @@
         <v>0</v>
       </c>
       <c r="G63" s="2" t="n">
-        <v>0.3235121444468337</v>
+        <v>0.323512144446834</v>
       </c>
       <c r="H63" s="2" t="n">
         <v>0</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>0.2602163107835705</v>
+        <v>0.2602163107835709</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>0.1774522622338857</v>
+        <v>0.1774522622338852</v>
       </c>
       <c r="K63" t="b">
         <v>1</v>
@@ -9375,34 +9375,34 @@
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>0.1523713276852983</v>
+        <v>0.1523713276852982</v>
       </c>
       <c r="B64" s="2" t="n">
         <v>0.1221483894594569</v>
       </c>
       <c r="C64" s="2" t="n">
-        <v>0.2434860230859878</v>
+        <v>0.2434860230859876</v>
       </c>
       <c r="D64" s="2" t="n">
-        <v>1.21225688773224e-17</v>
+        <v>1.214306433183765e-17</v>
       </c>
       <c r="E64" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F64" s="2" t="n">
-        <v>0</v>
+        <v>8.673617379884035e-19</v>
       </c>
       <c r="G64" s="2" t="n">
         <v>0.3334486938515002</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>0</v>
+        <v>3.238376363942641e-17</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>0.2535930012836279</v>
+        <v>0.2535930012836274</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>0.1694722817788842</v>
+        <v>0.1694722817788847</v>
       </c>
       <c r="K64" t="b">
         <v>1</v>
@@ -9416,25 +9416,25 @@
         <v>0.1228536389297965</v>
       </c>
       <c r="C65" s="2" t="n">
-        <v>0.2481527326981277</v>
+        <v>0.248152732698128</v>
       </c>
       <c r="D65" s="2" t="n">
-        <v>0</v>
+        <v>2.352718714293545e-17</v>
       </c>
       <c r="E65" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F65" s="2" t="n">
-        <v>6.242961556036581e-18</v>
+        <v>4.77048955893622e-18</v>
       </c>
       <c r="G65" s="2" t="n">
-        <v>0.3433852649790836</v>
+        <v>0.3433852649790834</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>8.808588139378218e-17</v>
+        <v>0</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>0.2469696967354591</v>
+        <v>0.246969696735459</v>
       </c>
       <c r="J65" s="2" t="n">
         <v>0.1614923055873295</v>
@@ -9448,16 +9448,16 @@
         <v>0.1542136187088911</v>
       </c>
       <c r="B66" s="2" t="n">
-        <v>0.123582232093545</v>
+        <v>0.1235822320935449</v>
       </c>
       <c r="C66" s="2" t="n">
-        <v>0.2528194195702518</v>
+        <v>0.2528194195702513</v>
       </c>
       <c r="D66" s="2" t="n">
-        <v>0</v>
+        <v>1.009663273127126e-18</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>0</v>
+        <v>3.903127820947816e-18</v>
       </c>
       <c r="F66" s="2" t="n">
         <v>0</v>
@@ -9469,10 +9469,10 @@
         <v>0</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>0.2403463956880106</v>
+        <v>0.2403463956880104</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>0.1535123327116213</v>
+        <v>0.1535123327116217</v>
       </c>
       <c r="K66" t="b">
         <v>1</v>
@@ -9486,10 +9486,10 @@
         <v>0.1243337585707523</v>
       </c>
       <c r="C67" s="2" t="n">
-        <v>0.2574859592126474</v>
+        <v>0.2574859592126478</v>
       </c>
       <c r="D67" s="2" t="n">
-        <v>2.330574180053757e-17</v>
+        <v>2.276824562219559e-17</v>
       </c>
       <c r="E67" s="2" t="n">
         <v>0</v>
@@ -9498,16 +9498,16 @@
         <v>0</v>
       </c>
       <c r="G67" s="2" t="n">
-        <v>0.3632585416522113</v>
+        <v>0.3632585416522114</v>
       </c>
       <c r="H67" s="2" t="n">
         <v>0</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>0.2337231156191261</v>
+        <v>0.2337231156191258</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>0.1455323835160153</v>
+        <v>0.1455323835160151</v>
       </c>
       <c r="K67" t="b">
         <v>1</v>
@@ -9521,28 +9521,28 @@
         <v>0.1251078050787412</v>
       </c>
       <c r="C68" s="2" t="n">
-        <v>0.2621530706286376</v>
+        <v>0.2621530706286377</v>
       </c>
       <c r="D68" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>6.286725746474622e-18</v>
+        <v>1.863980703727813e-17</v>
       </c>
       <c r="F68" s="2" t="n">
-        <v>1.520872650166378e-17</v>
+        <v>2.681113387944037e-17</v>
       </c>
       <c r="G68" s="2" t="n">
-        <v>0.3731946843604229</v>
+        <v>0.3731946843604227</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>1.087022594298878e-16</v>
+        <v>0</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>0.2270992766938344</v>
+        <v>0.2270992766938341</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>0.1375529683171051</v>
+        <v>0.1375529683171055</v>
       </c>
       <c r="K68" t="b">
         <v>1</v>
@@ -9553,31 +9553,31 @@
         <v>0.1569770552442803</v>
       </c>
       <c r="B69" s="2" t="n">
-        <v>0.1259039562645679</v>
+        <v>0.125903956264568</v>
       </c>
       <c r="C69" s="2" t="n">
-        <v>0.2668195306384423</v>
+        <v>0.2668195306384422</v>
       </c>
       <c r="D69" s="2" t="n">
-        <v>5.258825330769866e-17</v>
+        <v>0</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>0</v>
+        <v>6.396792817664476e-18</v>
       </c>
       <c r="F69" s="2" t="n">
-        <v>0</v>
+        <v>9.974659986866641e-18</v>
       </c>
       <c r="G69" s="2" t="n">
-        <v>0.3831315780890427</v>
+        <v>0.383131578089043</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>4.50932834265589e-19</v>
+        <v>2.474691458698164e-17</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>0.2204764855312477</v>
+        <v>0.2204764855312475</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>0.1295724057412674</v>
+        <v>0.1295724057412673</v>
       </c>
       <c r="K69" t="b">
         <v>1</v>
@@ -9591,13 +9591,13 @@
         <v>0.1267217954998478</v>
       </c>
       <c r="C70" s="2" t="n">
-        <v>0.2714862124680325</v>
+        <v>0.2714862124680326</v>
       </c>
       <c r="D70" s="2" t="n">
-        <v>7.807186550252792e-17</v>
+        <v>0</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>3.678965356949765e-18</v>
+        <v>0</v>
       </c>
       <c r="F70" s="2" t="n">
         <v>0</v>
@@ -9606,13 +9606,13 @@
         <v>0.3930681687099266</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>0</v>
+        <v>5.475220971051797e-17</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>0.2138531853849693</v>
+        <v>0.2138531853849691</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>0.1215924334370716</v>
+        <v>0.1215924334370718</v>
       </c>
       <c r="K70" t="b">
         <v>1</v>
@@ -9626,28 +9626,28 @@
         <v>0.1275609056353729</v>
       </c>
       <c r="C71" s="2" t="n">
-        <v>0.2761528916254467</v>
+        <v>0.2761528916254468</v>
       </c>
       <c r="D71" s="2" t="n">
-        <v>0</v>
+        <v>1.382357769919018e-17</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>9.758523161993298e-18</v>
+        <v>0</v>
       </c>
       <c r="F71" s="2" t="n">
-        <v>4.200287701354042e-18</v>
+        <v>0</v>
       </c>
       <c r="G71" s="2" t="n">
-        <v>0.4030047611926826</v>
+        <v>0.4030047611926824</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>2.46897705518883e-17</v>
+        <v>0</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>0.2072298856202097</v>
+        <v>0.2072298856202093</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>0.1136124615616611</v>
+        <v>0.1136124615616615</v>
       </c>
       <c r="K71" t="b">
         <v>1</v>
@@ -9661,28 +9661,28 @@
         <v>0.1284208697155724</v>
       </c>
       <c r="C72" s="2" t="n">
-        <v>0.280819576225136</v>
+        <v>0.2808195762251364</v>
       </c>
       <c r="D72" s="2" t="n">
-        <v>5.865832671206449e-19</v>
+        <v>5.269222558279552e-17</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>2.090985564883392e-18</v>
+        <v>0</v>
       </c>
       <c r="F72" s="2" t="n">
-        <v>1.261593671557387e-17</v>
+        <v>0</v>
       </c>
       <c r="G72" s="2" t="n">
-        <v>0.4129413498833944</v>
+        <v>0.4129413498833938</v>
       </c>
       <c r="H72" s="2" t="n">
         <v>0</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>0.2006065850782051</v>
+        <v>0.2006065850782046</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>0.1056324888132646</v>
+        <v>0.1056324888132652</v>
       </c>
       <c r="K72" t="b">
         <v>1</v>
@@ -9690,34 +9690,34 @@
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
-        <v>0.1606616372914658</v>
+        <v>0.1606616372914659</v>
       </c>
       <c r="B73" s="2" t="n">
-        <v>0.1293012716513947</v>
+        <v>0.1293012716513948</v>
       </c>
       <c r="C73" s="2" t="n">
-        <v>0.2854862580706434</v>
+        <v>0.2854862580706437</v>
       </c>
       <c r="D73" s="2" t="n">
-        <v>2.286615013744519e-17</v>
+        <v>2.97613496347271e-17</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>1.340937944120186e-17</v>
+        <v>4.472333961502706e-19</v>
       </c>
       <c r="F73" s="2" t="n">
-        <v>7.707386409350045e-18</v>
+        <v>0</v>
       </c>
       <c r="G73" s="2" t="n">
-        <v>0.422877940493221</v>
+        <v>0.4228779404932212</v>
       </c>
       <c r="H73" s="2" t="n">
-        <v>4.156368274390267e-18</v>
+        <v>0</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>0.1939832849297629</v>
+        <v>0.1939832849297625</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>0.09765251650637269</v>
+        <v>0.09765251650637277</v>
       </c>
       <c r="K73" t="b">
         <v>1</v>
@@ -9734,25 +9734,25 @@
         <v>0.2901514530233115</v>
       </c>
       <c r="D74" s="2" t="n">
-        <v>0</v>
+        <v>1.741499739554841e-17</v>
       </c>
       <c r="E74" s="2" t="n">
-        <v>8.299843308630023e-18</v>
+        <v>0</v>
       </c>
       <c r="F74" s="2" t="n">
-        <v>4.205719171947843e-19</v>
+        <v>3.4863876108987e-18</v>
       </c>
       <c r="G74" s="2" t="n">
-        <v>0.4328155536396192</v>
+        <v>0.4328155536396188</v>
       </c>
       <c r="H74" s="2" t="n">
-        <v>1.624341710493032e-17</v>
+        <v>2.344587197999903e-18</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>0.1873601537761474</v>
+        <v>0.1873601537761473</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>0.08967283956092188</v>
+        <v>0.08967283956092252</v>
       </c>
       <c r="K74" t="b">
         <v>1</v>
@@ -9766,28 +9766,28 @@
         <v>0.1311217328514482</v>
       </c>
       <c r="C75" s="2" t="n">
-        <v>0.2948235851502121</v>
+        <v>0.2948235851502119</v>
       </c>
       <c r="D75" s="2" t="n">
-        <v>2.062258737817569e-17</v>
+        <v>3.925150677576428e-17</v>
       </c>
       <c r="E75" s="2" t="n">
-        <v>3.840429556927399e-18</v>
+        <v>0</v>
       </c>
       <c r="F75" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G75" s="2" t="n">
-        <v>0.4427544501817509</v>
+        <v>0.4427544501817506</v>
       </c>
       <c r="H75" s="2" t="n">
-        <v>7.115683951086188e-18</v>
+        <v>0</v>
       </c>
       <c r="I75" s="2" t="n">
         <v>0.1807556866126137</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>0.08166627805542327</v>
+        <v>0.08166627805542377</v>
       </c>
       <c r="K75" t="b">
         <v>1</v>
@@ -9801,28 +9801,28 @@
         <v>0.1320609696625637</v>
       </c>
       <c r="C76" s="2" t="n">
-        <v>0.299486329515482</v>
+        <v>0.2994863295154818</v>
       </c>
       <c r="D76" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E76" s="2" t="n">
-        <v>1.213539288289955e-18</v>
+        <v>0</v>
       </c>
       <c r="F76" s="2" t="n">
-        <v>1.372973448084029e-17</v>
+        <v>0</v>
       </c>
       <c r="G76" s="2" t="n">
-        <v>0.4526876943839748</v>
+        <v>0.4526876943839752</v>
       </c>
       <c r="H76" s="2" t="n">
-        <v>1.257653563166315e-17</v>
+        <v>0</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>0.1741133811491678</v>
+        <v>0.1741133811491676</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>0.07371259495137546</v>
+        <v>0.07371259495137542</v>
       </c>
       <c r="K76" t="b">
         <v>1</v>
@@ -9836,28 +9836,28 @@
         <v>0.1330190006770013</v>
       </c>
       <c r="C77" s="2" t="n">
-        <v>0.3041539093769637</v>
+        <v>0.3041539093769636</v>
       </c>
       <c r="D77" s="2" t="n">
-        <v>2.157110267946039e-18</v>
+        <v>0</v>
       </c>
       <c r="E77" s="2" t="n">
-        <v>1.865854315361376e-18</v>
+        <v>3.74049749507499e-18</v>
       </c>
       <c r="F77" s="2" t="n">
-        <v>7.087700007251719e-18</v>
+        <v>1.620882247865829e-17</v>
       </c>
       <c r="G77" s="2" t="n">
-        <v>0.4626236670974366</v>
+        <v>0.4626236670974364</v>
       </c>
       <c r="H77" s="2" t="n">
-        <v>6.14403546136559e-18</v>
+        <v>2.455717920679668e-17</v>
       </c>
       <c r="I77" s="2" t="n">
         <v>0.1674899778733766</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>0.06573244565222304</v>
+        <v>0.06573244565222346</v>
       </c>
       <c r="K77" t="b">
         <v>1</v>
@@ -9868,31 +9868,31 @@
         <v>0.1652673648504479</v>
       </c>
       <c r="B78" s="2" t="n">
-        <v>0.1339954227358776</v>
+        <v>0.1339954227358775</v>
       </c>
       <c r="C78" s="2" t="n">
-        <v>0.3088200559250501</v>
+        <v>0.3088200559250502</v>
       </c>
       <c r="D78" s="2" t="n">
-        <v>1.044103533058181e-16</v>
+        <v>0</v>
       </c>
       <c r="E78" s="2" t="n">
-        <v>0</v>
+        <v>6.979551485375435e-19</v>
       </c>
       <c r="F78" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G78" s="2" t="n">
-        <v>0.4725609773424344</v>
+        <v>0.4725609773424339</v>
       </c>
       <c r="H78" s="2" t="n">
-        <v>0</v>
+        <v>2.848571801616212e-18</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>0.1608678680072466</v>
+        <v>0.1608678680072468</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>0.05775109872526896</v>
+        <v>0.05775109872526924</v>
       </c>
       <c r="K78" t="b">
         <v>1</v>
@@ -9900,34 +9900,34 @@
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
-        <v>0.1661885103622442</v>
+        <v>0.1661885103622443</v>
       </c>
       <c r="B79" s="2" t="n">
         <v>0.1349898367557779</v>
       </c>
       <c r="C79" s="2" t="n">
-        <v>0.3134863491249772</v>
+        <v>0.3134863491249778</v>
       </c>
       <c r="D79" s="2" t="n">
-        <v>4.134697560075311e-17</v>
+        <v>0</v>
       </c>
       <c r="E79" s="2" t="n">
-        <v>0</v>
+        <v>7.914675859144182e-18</v>
       </c>
       <c r="F79" s="2" t="n">
-        <v>3.010179316035507e-18</v>
+        <v>0</v>
       </c>
       <c r="G79" s="2" t="n">
-        <v>0.4824974841652599</v>
+        <v>0.4824974841652598</v>
       </c>
       <c r="H79" s="2" t="n">
-        <v>0</v>
+        <v>1.067939139898222e-17</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>0.1542434840419084</v>
+        <v>0.1542434840419081</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>0.0497726826678545</v>
+        <v>0.04977268266785441</v>
       </c>
       <c r="K79" t="b">
         <v>1</v>
@@ -9938,31 +9938,31 @@
         <v>0.1671096558740407</v>
       </c>
       <c r="B80" s="2" t="n">
-        <v>0.1360018480784325</v>
+        <v>0.1360018480784326</v>
       </c>
       <c r="C80" s="2" t="n">
-        <v>0.3181530309671691</v>
+        <v>0.3181530309671696</v>
       </c>
       <c r="D80" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E80" s="2" t="n">
-        <v>3.755449614743167e-18</v>
+        <v>1.637145280453112e-17</v>
       </c>
       <c r="F80" s="2" t="n">
-        <v>1.426263817267348e-17</v>
+        <v>2.103352214621879e-17</v>
       </c>
       <c r="G80" s="2" t="n">
-        <v>0.4924340747774061</v>
+        <v>0.492434074777406</v>
       </c>
       <c r="H80" s="2" t="n">
-        <v>4.243892263515043e-17</v>
+        <v>4.849094216441419e-17</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>0.1476201838939701</v>
+        <v>0.1476201838939699</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>0.04179271036145487</v>
+        <v>0.04179271036145454</v>
       </c>
       <c r="K80" t="b">
         <v>1</v>
@@ -9976,28 +9976,28 @@
         <v>0.137031066821808</v>
       </c>
       <c r="C81" s="2" t="n">
-        <v>0.3228197128106895</v>
+        <v>0.3228197128106896</v>
       </c>
       <c r="D81" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E81" s="2" t="n">
-        <v>1.248975761205835e-17</v>
+        <v>1.387778780781446e-17</v>
       </c>
       <c r="F81" s="2" t="n">
-        <v>2.547379128365631e-17</v>
+        <v>7.304812137121086e-18</v>
       </c>
       <c r="G81" s="2" t="n">
-        <v>0.5023706653886369</v>
+        <v>0.5023706653886371</v>
       </c>
       <c r="H81" s="2" t="n">
-        <v>1.911202594211069e-17</v>
+        <v>3.577867169202165e-17</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>0.1409968837458721</v>
+        <v>0.1409968837458716</v>
       </c>
       <c r="J81" s="2" t="n">
-        <v>0.03381273805480157</v>
+        <v>0.03381273805480195</v>
       </c>
       <c r="K81" t="b">
         <v>1</v>
@@ -10011,13 +10011,13 @@
         <v>0.1380771081970969</v>
       </c>
       <c r="C82" s="2" t="n">
-        <v>0.3274863953193665</v>
+        <v>0.3274863953193669</v>
       </c>
       <c r="D82" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E82" s="2" t="n">
-        <v>0</v>
+        <v>1.626303258728257e-18</v>
       </c>
       <c r="F82" s="2" t="n">
         <v>0</v>
@@ -10026,13 +10026,13 @@
         <v>0.512307255541907</v>
       </c>
       <c r="H82" s="2" t="n">
-        <v>1.096774619955739e-17</v>
+        <v>0</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>0.1343735835204656</v>
+        <v>0.134373583520466</v>
       </c>
       <c r="J82" s="2" t="n">
-        <v>0.02583276561826089</v>
+        <v>0.02583276561826022</v>
       </c>
       <c r="K82" t="b">
         <v>1</v>
@@ -10046,28 +10046,28 @@
         <v>0.1391395927914284</v>
       </c>
       <c r="C83" s="2" t="n">
-        <v>0.3321555728848556</v>
+        <v>0.3321555728848559</v>
       </c>
       <c r="D83" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E83" s="2" t="n">
-        <v>4.613900966566013e-18</v>
+        <v>2.602085213965211e-18</v>
       </c>
       <c r="F83" s="2" t="n">
-        <v>3.134471659959496e-18</v>
+        <v>1.366094737331736e-17</v>
       </c>
       <c r="G83" s="2" t="n">
-        <v>0.5222421424082511</v>
+        <v>0.5222421424082507</v>
       </c>
       <c r="H83" s="2" t="n">
-        <v>0</v>
+        <v>4.401860820291148e-17</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>0.1277500400862799</v>
+        <v>0.1277500400862803</v>
       </c>
       <c r="J83" s="2" t="n">
-        <v>0.01785224462061351</v>
+        <v>0.0178522446206131</v>
       </c>
       <c r="K83" t="b">
         <v>1</v>
@@ -10075,34 +10075,34 @@
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
-        <v>0.1707942379212262</v>
+        <v>0.1707942379212263</v>
       </c>
       <c r="B84" s="2" t="n">
         <v>0.1402181468145316</v>
       </c>
       <c r="C84" s="2" t="n">
-        <v>0.3368197583381765</v>
+        <v>0.336819758338177</v>
       </c>
       <c r="D84" s="2" t="n">
-        <v>4.808204437901356e-17</v>
+        <v>1.287490079826537e-17</v>
       </c>
       <c r="E84" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F84" s="2" t="n">
-        <v>0</v>
+        <v>1.474514954580286e-17</v>
       </c>
       <c r="G84" s="2" t="n">
-        <v>0.5321804372244566</v>
+        <v>0.5321804372244565</v>
       </c>
       <c r="H84" s="2" t="n">
-        <v>0</v>
+        <v>1.192622389734055e-17</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>0.1211269833019749</v>
+        <v>0.1211269833019746</v>
       </c>
       <c r="J84" s="2" t="n">
-        <v>0.009872821135392028</v>
+        <v>0.009872821135391834</v>
       </c>
       <c r="K84" t="b">
         <v>1</v>
@@ -10116,10 +10116,10 @@
         <v>0.1413124023232932</v>
       </c>
       <c r="C85" s="2" t="n">
-        <v>0.3414864404012782</v>
+        <v>0.3414864404012783</v>
       </c>
       <c r="D85" s="2" t="n">
-        <v>6.016441438390489e-18</v>
+        <v>5.941427905220564e-17</v>
       </c>
       <c r="E85" s="2" t="n">
         <v>0</v>
@@ -10128,7 +10128,7 @@
         <v>0</v>
       </c>
       <c r="G85" s="2" t="n">
-        <v>0.5421170276846857</v>
+        <v>0.5421170276846856</v>
       </c>
       <c r="H85" s="2" t="n">
         <v>0</v>
@@ -10137,7 +10137,7 @@
         <v>0.1145036831289358</v>
       </c>
       <c r="J85" s="2" t="n">
-        <v>0.001892848785100378</v>
+        <v>0.001892848785100406</v>
       </c>
       <c r="K85" t="b">
         <v>1</v>
@@ -10151,28 +10151,28 @@
         <v>0.1424239405973149</v>
       </c>
       <c r="C86" s="2" t="n">
-        <v>0.3447721674178074</v>
+        <v>0.3447721674178073</v>
       </c>
       <c r="D86" s="2" t="n">
-        <v>7.982911417866441e-18</v>
+        <v>0</v>
       </c>
       <c r="E86" s="2" t="n">
-        <v>0</v>
+        <v>2.561074651617226e-17</v>
       </c>
       <c r="F86" s="2" t="n">
-        <v>0</v>
+        <v>7.266664357713169e-18</v>
       </c>
       <c r="G86" s="2" t="n">
-        <v>0.5516236053857962</v>
+        <v>0.5516236053857964</v>
       </c>
       <c r="H86" s="2" t="n">
-        <v>0</v>
+        <v>2.236249726147364e-17</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>0.1036042271963966</v>
+        <v>0.1036042271963965</v>
       </c>
       <c r="J86" s="2" t="n">
-        <v>0</v>
+        <v>7.306329241996487e-17</v>
       </c>
       <c r="K86" t="b">
         <v>1</v>
@@ -10186,10 +10186,10 @@
         <v>0.1435568724256205</v>
       </c>
       <c r="C87" s="2" t="n">
-        <v>0.3476283583836498</v>
+        <v>0.3476283583836499</v>
       </c>
       <c r="D87" s="2" t="n">
-        <v>7.400819769841363e-17</v>
+        <v>0</v>
       </c>
       <c r="E87" s="2" t="n">
         <v>0</v>
@@ -10198,13 +10198,13 @@
         <v>0</v>
       </c>
       <c r="G87" s="2" t="n">
-        <v>0.5609965510398458</v>
+        <v>0.560996551039846</v>
       </c>
       <c r="H87" s="2" t="n">
-        <v>0</v>
+        <v>1.178904047478623e-17</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>0.09137509057650461</v>
+        <v>0.09137509057650399</v>
       </c>
       <c r="J87" s="2" t="n">
         <v>0</v>
@@ -10224,25 +10224,25 @@
         <v>0.3504857856401951</v>
       </c>
       <c r="D88" s="2" t="n">
-        <v>0</v>
+        <v>2.511125086934852e-17</v>
       </c>
       <c r="E88" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F88" s="2" t="n">
-        <v>0</v>
+        <v>1.169314502968047e-17</v>
       </c>
       <c r="G88" s="2" t="n">
         <v>0.5703685882067143</v>
       </c>
       <c r="H88" s="2" t="n">
-        <v>0</v>
+        <v>8.046593154091896e-18</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>0.0791456261530905</v>
+        <v>0.07914562615309047</v>
       </c>
       <c r="J88" s="2" t="n">
-        <v>6.886481728296377e-17</v>
+        <v>3.58639004567194e-17</v>
       </c>
       <c r="K88" t="b">
         <v>1</v>
@@ -10253,28 +10253,28 @@
         <v>0.1753999654802083</v>
       </c>
       <c r="B89" s="2" t="n">
-        <v>0.1458854639748918</v>
+        <v>0.1458854639748919</v>
       </c>
       <c r="C89" s="2" t="n">
-        <v>0.3533408401308597</v>
+        <v>0.3533408401308603</v>
       </c>
       <c r="D89" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E89" s="2" t="n">
-        <v>3.380663593977521e-18</v>
+        <v>0</v>
       </c>
       <c r="F89" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G89" s="2" t="n">
-        <v>0.5797423689985911</v>
+        <v>0.5797423689985908</v>
       </c>
       <c r="H89" s="2" t="n">
         <v>0</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>0.06691679087054928</v>
+        <v>0.06691679087054897</v>
       </c>
       <c r="J89" s="2" t="n">
         <v>0</v>
@@ -10291,28 +10291,28 @@
         <v>0.1470801305831436</v>
       </c>
       <c r="C90" s="2" t="n">
-        <v>0.3561970810044656</v>
+        <v>0.3561970810044651</v>
       </c>
       <c r="D90" s="2" t="n">
-        <v>0</v>
+        <v>1.301392739710546e-16</v>
       </c>
       <c r="E90" s="2" t="n">
-        <v>4.729367590383481e-18</v>
+        <v>0</v>
       </c>
       <c r="F90" s="2" t="n">
-        <v>8.815454076208484e-18</v>
+        <v>0</v>
       </c>
       <c r="G90" s="2" t="n">
-        <v>0.5891152779779627</v>
+        <v>0.589115277977963</v>
       </c>
       <c r="H90" s="2" t="n">
-        <v>1.639030540766928e-17</v>
+        <v>0</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>0.05468764101757165</v>
+        <v>0.0546876410175719</v>
       </c>
       <c r="J90" s="2" t="n">
-        <v>8.177945328699773e-17</v>
+        <v>0</v>
       </c>
       <c r="K90" t="b">
         <v>1</v>
@@ -10326,28 +10326,28 @@
         <v>0.1482943947293645</v>
       </c>
       <c r="C91" s="2" t="n">
-        <v>0.35905332187807</v>
+        <v>0.3590533218780701</v>
       </c>
       <c r="D91" s="2" t="n">
-        <v>2.555279938416584e-17</v>
+        <v>0</v>
       </c>
       <c r="E91" s="2" t="n">
-        <v>1.465894177107073e-18</v>
+        <v>0</v>
       </c>
       <c r="F91" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G91" s="2" t="n">
-        <v>0.5984881869573354</v>
+        <v>0.5984881869573353</v>
       </c>
       <c r="H91" s="2" t="n">
         <v>0</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>0.04245849116459437</v>
+        <v>0.04245849116459467</v>
       </c>
       <c r="J91" s="2" t="n">
-        <v>0</v>
+        <v>1.434520656820287e-17</v>
       </c>
       <c r="K91" t="b">
         <v>1</v>
@@ -10358,31 +10358,31 @@
         <v>0.1781634020155975</v>
       </c>
       <c r="B92" s="2" t="n">
-        <v>0.149527778979531</v>
+        <v>0.1495277789795309</v>
       </c>
       <c r="C92" s="2" t="n">
-        <v>0.3619095627516751</v>
+        <v>0.3619095627516754</v>
       </c>
       <c r="D92" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E92" s="2" t="n">
-        <v>2.445528355027034e-17</v>
+        <v>1.135282387799376e-17</v>
       </c>
       <c r="F92" s="2" t="n">
-        <v>2.935755962819028e-17</v>
+        <v>2.303486738256641e-17</v>
       </c>
       <c r="G92" s="2" t="n">
-        <v>0.6078610959367083</v>
+        <v>0.6078610959367078</v>
       </c>
       <c r="H92" s="2" t="n">
-        <v>6.039018896780739e-17</v>
+        <v>6.408377981947193e-17</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>0.03022934131161653</v>
+        <v>0.03022934131161684</v>
       </c>
       <c r="J92" s="2" t="n">
-        <v>1.041001105067031e-16</v>
+        <v>0</v>
       </c>
       <c r="K92" t="b">
         <v>1</v>
@@ -10396,10 +10396,10 @@
         <v>0.150779814124979</v>
       </c>
       <c r="C93" s="2" t="n">
-        <v>0.3647658036252802</v>
+        <v>0.3647658036252807</v>
       </c>
       <c r="D93" s="2" t="n">
-        <v>0</v>
+        <v>6.707982786178983e-17</v>
       </c>
       <c r="E93" s="2" t="n">
         <v>0</v>
@@ -10408,16 +10408,16 @@
         <v>0</v>
       </c>
       <c r="G93" s="2" t="n">
-        <v>0.6172340049160802</v>
+        <v>0.6172340049160803</v>
       </c>
       <c r="H93" s="2" t="n">
         <v>0</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>0.0180001914586398</v>
+        <v>0.01800019145863883</v>
       </c>
       <c r="J93" s="2" t="n">
-        <v>3.48792273564862e-17</v>
+        <v>0</v>
       </c>
       <c r="K93" t="b">
         <v>1</v>
@@ -10434,25 +10434,25 @@
         <v>0.3676220444988855</v>
       </c>
       <c r="D94" s="2" t="n">
-        <v>0</v>
+        <v>6.177304293794816e-17</v>
       </c>
       <c r="E94" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F94" s="2" t="n">
-        <v>3.7463659250078e-18</v>
+        <v>2.285057403750985e-17</v>
       </c>
       <c r="G94" s="2" t="n">
-        <v>0.6266069138954528</v>
+        <v>0.6266069138954525</v>
       </c>
       <c r="H94" s="2" t="n">
-        <v>1.993438254894449e-17</v>
+        <v>0</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>0.005771041605661756</v>
+        <v>0.005771041605662022</v>
       </c>
       <c r="J94" s="2" t="n">
-        <v>5.767091161905899e-18</v>
+        <v>6.866390421443588e-17</v>
       </c>
       <c r="K94" t="b">
         <v>1</v>
@@ -10466,25 +10466,25 @@
         <v>0.1533933407371694</v>
       </c>
       <c r="C95" s="2" t="n">
-        <v>0.3461219296656814</v>
+        <v>0.3461219296656823</v>
       </c>
       <c r="D95" s="2" t="n">
-        <v>0</v>
+        <v>9.724472088708689e-17</v>
       </c>
       <c r="E95" s="2" t="n">
-        <v>1.042170493240455e-17</v>
+        <v>0</v>
       </c>
       <c r="F95" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G95" s="2" t="n">
-        <v>0.6538780703343187</v>
+        <v>0.6538780703343178</v>
       </c>
       <c r="H95" s="2" t="n">
-        <v>5.786306530141348e-18</v>
+        <v>0</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>2.34187669256869e-17</v>
+        <v>0</v>
       </c>
       <c r="J95" s="2" t="n">
         <v>0</v>
@@ -10501,19 +10501,19 @@
         <v>0.1551020960988001</v>
       </c>
       <c r="C96" s="2" t="n">
-        <v>0.3028566884574715</v>
+        <v>0.3028566884574723</v>
       </c>
       <c r="D96" s="2" t="n">
-        <v>9.203798868302517e-17</v>
+        <v>9.501395202964955e-17</v>
       </c>
       <c r="E96" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F96" s="2" t="n">
-        <v>0</v>
+        <v>4.459560709618491e-18</v>
       </c>
       <c r="G96" s="2" t="n">
-        <v>0.6971433115425285</v>
+        <v>0.6971433115425278</v>
       </c>
       <c r="H96" s="2" t="n">
         <v>0</v>
@@ -10536,22 +10536,22 @@
         <v>0.1572075015092637</v>
       </c>
       <c r="C97" s="2" t="n">
-        <v>0.2595914472492631</v>
+        <v>0.2595914472492641</v>
       </c>
       <c r="D97" s="2" t="n">
-        <v>9.700628646235238e-17</v>
+        <v>3.931963786712453e-17</v>
       </c>
       <c r="E97" s="2" t="n">
-        <v>0</v>
+        <v>2.955450376348882e-18</v>
       </c>
       <c r="F97" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G97" s="2" t="n">
-        <v>0.7404085527507374</v>
+        <v>0.7404085527507366</v>
       </c>
       <c r="H97" s="2" t="n">
-        <v>3.148860173991073e-17</v>
+        <v>0</v>
       </c>
       <c r="I97" s="2" t="n">
         <v>0</v>
@@ -10568,31 +10568,31 @@
         <v>0.1836902750863759</v>
       </c>
       <c r="B98" s="2" t="n">
-        <v>0.1596938694256625</v>
+        <v>0.1596938694256624</v>
       </c>
       <c r="C98" s="2" t="n">
-        <v>0.2163262060410502</v>
+        <v>0.2163262060410523</v>
       </c>
       <c r="D98" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E98" s="2" t="n">
-        <v>1.454523653604266e-17</v>
+        <v>1.445563145357763e-17</v>
       </c>
       <c r="F98" s="2" t="n">
-        <v>5.177801548928603e-18</v>
+        <v>0</v>
       </c>
       <c r="G98" s="2" t="n">
-        <v>0.7836737939589496</v>
+        <v>0.7836737939589478</v>
       </c>
       <c r="H98" s="2" t="n">
-        <v>0</v>
+        <v>1.077121916593676e-17</v>
       </c>
       <c r="I98" s="2" t="n">
         <v>0</v>
       </c>
       <c r="J98" s="2" t="n">
-        <v>5.00588792281615e-17</v>
+        <v>2.701905488489614e-17</v>
       </c>
       <c r="K98" t="b">
         <v>1</v>
@@ -10603,22 +10603,22 @@
         <v>0.1846114205981723</v>
       </c>
       <c r="B99" s="2" t="n">
-        <v>0.1625437184830826</v>
+        <v>0.1625437184830825</v>
       </c>
       <c r="C99" s="2" t="n">
-        <v>0.1730609648328408</v>
+        <v>0.1730609648328418</v>
       </c>
       <c r="D99" s="2" t="n">
-        <v>2.807849537186837e-17</v>
+        <v>9.107298248878237e-18</v>
       </c>
       <c r="E99" s="2" t="n">
-        <v>0</v>
+        <v>7.589415207398531e-18</v>
       </c>
       <c r="F99" s="2" t="n">
-        <v>5.858980446428797e-18</v>
+        <v>8.239936510889834e-18</v>
       </c>
       <c r="G99" s="2" t="n">
-        <v>0.8269390351671592</v>
+        <v>0.8269390351671583</v>
       </c>
       <c r="H99" s="2" t="n">
         <v>0</v>
@@ -10627,7 +10627,7 @@
         <v>0</v>
       </c>
       <c r="J99" s="2" t="n">
-        <v>0</v>
+        <v>3.642919299551295e-17</v>
       </c>
       <c r="K99" t="b">
         <v>1</v>
@@ -10641,28 +10641,28 @@
         <v>0.1657382997055487</v>
       </c>
       <c r="C100" s="2" t="n">
-        <v>0.1297957236246315</v>
+        <v>0.1297957236246318</v>
       </c>
       <c r="D100" s="2" t="n">
-        <v>0</v>
+        <v>2.127081013121506e-17</v>
       </c>
       <c r="E100" s="2" t="n">
-        <v>2.526165384682099e-17</v>
+        <v>7.6442388118952e-18</v>
       </c>
       <c r="F100" s="2" t="n">
-        <v>5.597057620635927e-18</v>
+        <v>0</v>
       </c>
       <c r="G100" s="2" t="n">
-        <v>0.8702042763753685</v>
+        <v>0.8702042763753682</v>
       </c>
       <c r="H100" s="2" t="n">
-        <v>1.459045502661779e-17</v>
+        <v>9.482251959541034e-18</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>2.081668171172169e-17</v>
+        <v>0</v>
       </c>
       <c r="J100" s="2" t="n">
-        <v>8.42117931504023e-17</v>
+        <v>4.191489331437508e-18</v>
       </c>
       <c r="K100" t="b">
         <v>1</v>
@@ -10673,13 +10673,13 @@
         <v>0.1864537116217651</v>
       </c>
       <c r="B101" s="2" t="n">
-        <v>0.1692580947697234</v>
+        <v>0.1692580947697235</v>
       </c>
       <c r="C101" s="2" t="n">
-        <v>0.08653048241641952</v>
+        <v>0.08653048241641931</v>
       </c>
       <c r="D101" s="2" t="n">
-        <v>4.182706391663632e-17</v>
+        <v>1.192622389734055e-17</v>
       </c>
       <c r="E101" s="2" t="n">
         <v>0</v>
@@ -10688,13 +10688,13 @@
         <v>0</v>
       </c>
       <c r="G101" s="2" t="n">
-        <v>0.9134695175835804</v>
+        <v>0.9134695175835806</v>
       </c>
       <c r="H101" s="2" t="n">
         <v>0</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>0</v>
+        <v>1.908195823574488e-17</v>
       </c>
       <c r="J101" s="2" t="n">
         <v>0</v>
@@ -10705,34 +10705,34 @@
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
-        <v>0.1873748571335615</v>
+        <v>0.1873748571335614</v>
       </c>
       <c r="B102" s="2" t="n">
-        <v>0.1730832643142563</v>
+        <v>0.1730832643142562</v>
       </c>
       <c r="C102" s="2" t="n">
-        <v>0.04326524120820983</v>
+        <v>0.04326524120820995</v>
       </c>
       <c r="D102" s="2" t="n">
-        <v>7.715161106974284e-17</v>
+        <v>0</v>
       </c>
       <c r="E102" s="2" t="n">
-        <v>7.735295547998643e-18</v>
+        <v>3.68426563102041e-17</v>
       </c>
       <c r="F102" s="2" t="n">
-        <v>3.635394108379463e-18</v>
+        <v>1.339742606285927e-17</v>
       </c>
       <c r="G102" s="2" t="n">
-        <v>0.9567347587917902</v>
+        <v>0.9567347587917899</v>
       </c>
       <c r="H102" s="2" t="n">
-        <v>0</v>
+        <v>3.509098823367522e-17</v>
       </c>
       <c r="I102" s="2" t="n">
-        <v>0</v>
+        <v>9.974659986866641e-18</v>
       </c>
       <c r="J102" s="2" t="n">
-        <v>0</v>
+        <v>4.362271860682831e-17</v>
       </c>
       <c r="K102" t="b">
         <v>1</v>
@@ -12157,13 +12157,13 @@
         <v>0.6154051621353303</v>
       </c>
       <c r="E2" t="n">
-        <v>0.7080158486523555</v>
+        <v>0.7080158486523553</v>
       </c>
       <c r="F2" t="n">
         <v>0.4457140877612871</v>
       </c>
       <c r="G2" t="n">
-        <v>0.4957871609401717</v>
+        <v>0.4957871609401718</v>
       </c>
       <c r="H2" t="n">
         <v>0.2875761766931065</v>
@@ -12188,19 +12188,19 @@
         <v>0.7019845897229843</v>
       </c>
       <c r="E3" t="n">
-        <v>0.6727182928307738</v>
+        <v>0.6727182928307739</v>
       </c>
       <c r="F3" t="n">
-        <v>0.4479860119557348</v>
+        <v>0.447986011955735</v>
       </c>
       <c r="G3" t="n">
         <v>0.4179338773472103</v>
       </c>
       <c r="H3" t="n">
-        <v>0.2154842554349414</v>
+        <v>0.2154842554349415</v>
       </c>
       <c r="I3" t="n">
-        <v>0.4611928159408281</v>
+        <v>0.4611928159408279</v>
       </c>
     </row>
     <row r="4">
@@ -12222,7 +12222,7 @@
         <v>0.8703787734388615</v>
       </c>
       <c r="F4" t="n">
-        <v>0.6415182470774795</v>
+        <v>0.6415182470774797</v>
       </c>
       <c r="G4" t="n">
         <v>0.5602009897339925</v>
@@ -12231,7 +12231,7 @@
         <v>0.2990536675378052</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6304140854381329</v>
+        <v>0.630414085438133</v>
       </c>
     </row>
     <row r="5">
@@ -12241,10 +12241,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.7080158486523555</v>
+        <v>0.7080158486523553</v>
       </c>
       <c r="C5" t="n">
-        <v>0.6727182928307738</v>
+        <v>0.6727182928307739</v>
       </c>
       <c r="D5" t="n">
         <v>0.8703787734388615</v>
@@ -12253,16 +12253,16 @@
         <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7451471429847806</v>
+        <v>0.7451471429847808</v>
       </c>
       <c r="G5" t="n">
         <v>0.6592595738247619</v>
       </c>
       <c r="H5" t="n">
-        <v>0.4107400072088258</v>
+        <v>0.4107400072088257</v>
       </c>
       <c r="I5" t="n">
-        <v>0.6689423984404478</v>
+        <v>0.6689423984404477</v>
       </c>
     </row>
     <row r="6">
@@ -12275,13 +12275,13 @@
         <v>0.4457140877612871</v>
       </c>
       <c r="C6" t="n">
-        <v>0.4479860119557348</v>
+        <v>0.447986011955735</v>
       </c>
       <c r="D6" t="n">
-        <v>0.6415182470774795</v>
+        <v>0.6415182470774797</v>
       </c>
       <c r="E6" t="n">
-        <v>0.7451471429847806</v>
+        <v>0.7451471429847808</v>
       </c>
       <c r="F6" t="n">
         <v>1</v>
@@ -12290,7 +12290,7 @@
         <v>0.5265685538144041</v>
       </c>
       <c r="H6" t="n">
-        <v>0.3306651094032382</v>
+        <v>0.3306651094032383</v>
       </c>
       <c r="I6" t="n">
         <v>0.5531937350398379</v>
@@ -12303,7 +12303,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.4957871609401717</v>
+        <v>0.4957871609401718</v>
       </c>
       <c r="C7" t="n">
         <v>0.4179338773472103</v>
@@ -12324,7 +12324,7 @@
         <v>0.6255080489684137</v>
       </c>
       <c r="I7" t="n">
-        <v>0.6850436303922661</v>
+        <v>0.6850436303922663</v>
       </c>
     </row>
     <row r="8">
@@ -12337,16 +12337,16 @@
         <v>0.2875761766931065</v>
       </c>
       <c r="C8" t="n">
-        <v>0.2154842554349414</v>
+        <v>0.2154842554349415</v>
       </c>
       <c r="D8" t="n">
         <v>0.2990536675378052</v>
       </c>
       <c r="E8" t="n">
-        <v>0.4107400072088258</v>
+        <v>0.4107400072088257</v>
       </c>
       <c r="F8" t="n">
-        <v>0.3306651094032382</v>
+        <v>0.3306651094032383</v>
       </c>
       <c r="G8" t="n">
         <v>0.6255080489684137</v>
@@ -12355,7 +12355,7 @@
         <v>1</v>
       </c>
       <c r="I8" t="n">
-        <v>0.4104610785140765</v>
+        <v>0.4104610785140766</v>
       </c>
     </row>
     <row r="9">
@@ -12368,22 +12368,22 @@
         <v>0.5204386167756581</v>
       </c>
       <c r="C9" t="n">
-        <v>0.4611928159408281</v>
+        <v>0.4611928159408279</v>
       </c>
       <c r="D9" t="n">
-        <v>0.6304140854381329</v>
+        <v>0.630414085438133</v>
       </c>
       <c r="E9" t="n">
-        <v>0.6689423984404478</v>
+        <v>0.6689423984404477</v>
       </c>
       <c r="F9" t="n">
         <v>0.5531937350398379</v>
       </c>
       <c r="G9" t="n">
-        <v>0.6850436303922661</v>
+        <v>0.6850436303922663</v>
       </c>
       <c r="H9" t="n">
-        <v>0.4104610785140765</v>
+        <v>0.4104610785140766</v>
       </c>
       <c r="I9" t="n">
         <v>1</v>
@@ -12447,13 +12447,13 @@
         <v>0.4902260525509582</v>
       </c>
       <c r="C2" t="n">
-        <v>0.5007454006413341</v>
+        <v>0.500745400641334</v>
       </c>
       <c r="D2" t="n">
         <v>0.4609393448218127</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.0398060558195214</v>
+        <v>-0.03980605581952129</v>
       </c>
     </row>
     <row r="3">
@@ -12482,7 +12482,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.7080158486523555</v>
+        <v>0.7080158486523553</v>
       </c>
       <c r="C4" t="n">
         <v>0.7614833758022684</v>
@@ -12520,16 +12520,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.4957871609401717</v>
+        <v>0.4957871609401718</v>
       </c>
       <c r="C6" t="n">
-        <v>0.5187401319918179</v>
+        <v>0.518740131991818</v>
       </c>
       <c r="D6" t="n">
-        <v>0.4120295869101725</v>
+        <v>0.4120295869101724</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.1067105450816454</v>
+        <v>-0.1067105450816456</v>
       </c>
     </row>
     <row r="7">
@@ -12561,10 +12561,10 @@
         <v>0.5204386167756581</v>
       </c>
       <c r="C8" t="n">
-        <v>0.5716776228704172</v>
+        <v>0.5716776228704171</v>
       </c>
       <c r="D8" t="n">
-        <v>0.3472883864356235</v>
+        <v>0.3472883864356234</v>
       </c>
       <c r="E8" t="n">
         <v>-0.2243892364347937</v>
@@ -12577,16 +12577,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.5090233007869811</v>
+        <v>0.509023300786981</v>
       </c>
       <c r="C9" t="n">
-        <v>0.5486283832502574</v>
+        <v>0.5486283832502575</v>
       </c>
       <c r="D9" t="n">
         <v>0.3927084394723381</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.1559199437779193</v>
+        <v>-0.1559199437779195</v>
       </c>
     </row>
   </sheetData>
@@ -12686,7 +12686,7 @@
         <v>0.01038787912675922</v>
       </c>
       <c r="H2" t="n">
-        <v>0.007172550081213879</v>
+        <v>0.007172550081213882</v>
       </c>
       <c r="I2" t="n">
         <v>0.01252286124322956</v>
@@ -12705,7 +12705,7 @@
         <v>0.07000489645434713</v>
       </c>
       <c r="D3" t="n">
-        <v>0.03452163019589029</v>
+        <v>0.03452163019589028</v>
       </c>
       <c r="E3" t="n">
         <v>0.03135659096199024</v>
@@ -12733,13 +12733,13 @@
         <v>0.02028152029713371</v>
       </c>
       <c r="C4" t="n">
-        <v>0.03452163019589029</v>
+        <v>0.03452163019589028</v>
       </c>
       <c r="D4" t="n">
         <v>0.03454609934243165</v>
       </c>
       <c r="E4" t="n">
-        <v>0.02849962820785289</v>
+        <v>0.0284996282078529</v>
       </c>
       <c r="F4" t="n">
         <v>0.02112796236936711</v>
@@ -12767,7 +12767,7 @@
         <v>0.03135659096199024</v>
       </c>
       <c r="D5" t="n">
-        <v>0.02849962820785289</v>
+        <v>0.0284996282078529</v>
       </c>
       <c r="E5" t="n">
         <v>0.03103578890532283</v>
@@ -12810,7 +12810,7 @@
         <v>0.01102543569925791</v>
       </c>
       <c r="H6" t="n">
-        <v>0.008241728147407286</v>
+        <v>0.008241728147407288</v>
       </c>
       <c r="I6" t="n">
         <v>0.01330211006359534</v>
@@ -12854,7 +12854,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.007172550081213879</v>
+        <v>0.007172550081213882</v>
       </c>
       <c r="C8" t="n">
         <v>0.00801974525574441</v>
@@ -12866,7 +12866,7 @@
         <v>0.01017839315344844</v>
       </c>
       <c r="F8" t="n">
-        <v>0.008241728147407286</v>
+        <v>0.008241728147407288</v>
       </c>
       <c r="G8" t="n">
         <v>0.0103969384342186</v>
@@ -13028,28 +13028,28 @@
         <v>0.1093469788601253</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>0.08556527673367774</v>
+        <v>0.08556527673367778</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>0</v>
+        <v>8.429036616364356e-18</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>3.687864785652252e-18</v>
+        <v>1.179323972462162e-17</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>1.962937338412056e-18</v>
+        <v>0</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>0.04567811908672142</v>
+        <v>0.04567811908672137</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>0.3948433721197893</v>
+        <v>0.3948433721197898</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>0.2634291742973692</v>
+        <v>0.2634291742973693</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>0.2104840577624423</v>
+        <v>0.2104840577624419</v>
       </c>
     </row>
     <row r="3">
@@ -13075,25 +13075,25 @@
         <v>0.1533775093404843</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>0.3465774705782325</v>
+        <v>0.3465774705782329</v>
       </c>
       <c r="G3" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>1.808712818820481e-17</v>
+        <v>1.074064360563279e-17</v>
       </c>
       <c r="I3" s="2" t="n">
         <v>0</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>0.6534225294217673</v>
+        <v>0.653422529421767</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>6.133598722773533e-17</v>
+        <v>8.139034572895418e-17</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>4.305584546556521e-16</v>
+        <v>1.919535265408507e-16</v>
       </c>
       <c r="M3" s="2" t="n">
         <v>0</v>
@@ -13125,25 +13125,25 @@
         <v>0</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>0</v>
+        <v>8.838788804598624e-19</v>
       </c>
       <c r="H4" s="2" t="n">
         <v>0</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>0</v>
+        <v>1.586492710207305e-18</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>0.06212631032178039</v>
+        <v>0.06212631032178031</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>0.4300000516322494</v>
+        <v>0.4300000516322492</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>0.2636692920157067</v>
+        <v>0.2636692920157068</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>0.2442043460302636</v>
+        <v>0.2442043460302637</v>
       </c>
     </row>
     <row r="5">
@@ -13175,22 +13175,22 @@
         <v>0</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>0</v>
+        <v>1.680513367352532e-18</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>6.675563066487998e-18</v>
+        <v>9.540979117872439e-18</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>0.8692115045337074</v>
+        <v>0.8692115045337073</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>0</v>
+        <v>1.734723475976807e-17</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>0.04516639008307553</v>
+        <v>0.04516639008307429</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>0.0856221053832171</v>
+        <v>0.08562210538321836</v>
       </c>
     </row>
     <row r="6">
@@ -13216,28 +13216,28 @@
         <v>0.1067563288585438</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>0.05540182866451901</v>
+        <v>0.05540182866451893</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>0</v>
+        <v>2.168404344971009e-19</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>9.17123909487703e-19</v>
+        <v>0</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>4.18614284042478e-18</v>
+        <v>0</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>0.05609019744355018</v>
+        <v>0.05609019744355079</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>0.3175974304376356</v>
+        <v>0.3175974304376353</v>
       </c>
       <c r="L6" s="2" t="n">
         <v>0.34342078196175</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>0.2274897614925453</v>
+        <v>0.2274897614925449</v>
       </c>
     </row>
     <row r="7">
@@ -13263,22 +13263,22 @@
         <v>0.1504476024987286</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>0.4025461561604331</v>
+        <v>0.4025461561604337</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>9.925202306393247e-17</v>
+        <v>6.496474504117939e-17</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>1.393070427474296e-16</v>
+        <v>5.345599695110914e-17</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>2.220460394304046e-16</v>
+        <v>1.163729879948893e-16</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>0.5974538438395668</v>
+        <v>0.5974538438395665</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>1.01776876116429e-17</v>
+        <v>0</v>
       </c>
       <c r="L7" s="2" t="n">
         <v>0</v>
@@ -13316,22 +13316,22 @@
         <v>0</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>1.168989046786929e-18</v>
+        <v>0</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>0</v>
+        <v>2.901934877293233e-18</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>0.07361026433028865</v>
+        <v>0.07361026433028842</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>0.3363305860138766</v>
+        <v>0.3363305860138776</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>0.340281021157545</v>
+        <v>0.3402810211575445</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>0.2497781284982896</v>
+        <v>0.2497781284982894</v>
       </c>
     </row>
     <row r="9">
@@ -13354,31 +13354,31 @@
         <v>0.1810966956098033</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>0.1541715894857802</v>
+        <v>0.1541715894857803</v>
       </c>
       <c r="F9" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>1.733882198130903e-17</v>
+        <v>0</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>7.308949913470337e-17</v>
+        <v>0</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>9.924419912522088e-18</v>
+        <v>0</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>0.8863307991279515</v>
+        <v>0.8863307991279518</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>0</v>
+        <v>3.903127820947816e-18</v>
       </c>
       <c r="L9" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>0.1136692008720486</v>
+        <v>0.1136692008720484</v>
       </c>
     </row>
     <row r="10">
@@ -13401,31 +13401,31 @@
         <v>0.07496781225164267</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>0.1113583569727966</v>
+        <v>0.1113583569727967</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>0.2214304253984209</v>
+        <v>0.2214304253984211</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>9.154179701933422e-18</v>
+        <v>0</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>5.514161490226473e-18</v>
+        <v>0</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>2.322281108715372e-18</v>
+        <v>0</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>0.08120951631889428</v>
+        <v>0.08120951631889435</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>0.4927219905189312</v>
+        <v>0.4927219905189315</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>0.01043557493966056</v>
+        <v>0.0104355749396604</v>
       </c>
       <c r="M10" s="2" t="n">
-        <v>0.1942024928240929</v>
+        <v>0.1942024928240928</v>
       </c>
     </row>
     <row r="11">
@@ -13451,28 +13451,28 @@
         <v>0.1721636278425112</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>0.2221693546039033</v>
+        <v>0.2221693546039032</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>0.07993134246149998</v>
+        <v>0.07993134246150027</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>6.74815586966716e-18</v>
+        <v>4.959530626478106e-18</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>1.280732249299352e-17</v>
+        <v>3.60494444964577e-17</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>0.6978993029345968</v>
+        <v>0.6978993029345967</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>2.735985220860997e-17</v>
+        <v>6.277428668144968e-18</v>
       </c>
       <c r="L11" s="2" t="n">
-        <v>3.318994919662097e-18</v>
+        <v>0</v>
       </c>
       <c r="M11" s="2" t="n">
-        <v>1.929796067553098e-17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -13501,22 +13501,22 @@
         <v>0</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>0</v>
+        <v>3.228889594933393e-18</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>1.307170043255201e-17</v>
+        <v>1.140106347004288e-18</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>8.303802788328632e-19</v>
+        <v>0</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>0.08165132750285278</v>
+        <v>0.08165132750285288</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>0.6003671464488617</v>
+        <v>0.6003671464488619</v>
       </c>
       <c r="L12" s="2" t="n">
-        <v>0.07475257078037478</v>
+        <v>0.07475257078037457</v>
       </c>
       <c r="M12" s="2" t="n">
         <v>0.2432289552679107</v>
@@ -13542,31 +13542,31 @@
         <v>0.176267970179717</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>0.186388865173497</v>
+        <v>0.1863888651734969</v>
       </c>
       <c r="F13" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>0.1576130232278464</v>
+        <v>0.1576130232278462</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>1.244569617657793e-17</v>
+        <v>0</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>0.01304206278550461</v>
+        <v>0.01304206278550549</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>0.7348352533246162</v>
+        <v>0.7348352533246157</v>
       </c>
       <c r="K13" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L13" s="2" t="n">
-        <v>0.09450966066203263</v>
+        <v>0.09450966066203245</v>
       </c>
       <c r="M13" s="2" t="n">
-        <v>2.582074524351535e-17</v>
+        <v>4.348680846087594e-17</v>
       </c>
     </row>
   </sheetData>
@@ -13636,7 +13636,7 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>0.08556527673367774</v>
+        <v>0.08556527673367778</v>
       </c>
       <c r="C2" s="2" t="n">
         <v>0.1093469788601253</v>
@@ -13645,13 +13645,13 @@
         <v>0.1100594843273342</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>0.0007125054672088849</v>
+        <v>0.000712505467208871</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>0.006354975146787118</v>
+        <v>0.00635497514678711</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>0.01119820727887488</v>
+        <v>0.01119820727887491</v>
       </c>
     </row>
     <row r="3">
@@ -13661,7 +13661,7 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>0.05540182866451901</v>
+        <v>0.05540182866451893</v>
       </c>
       <c r="C3" s="2" t="n">
         <v>0.1067563288585438</v>
@@ -13673,7 +13673,7 @@
         <v>0.0002831058937632913</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>0.006082846491066296</v>
+        <v>0.006082846491066305</v>
       </c>
       <c r="G3" s="2" t="n">
         <v>0.008079144654214665</v>
@@ -13686,22 +13686,22 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>0.2214304253984209</v>
+        <v>0.2214304253984211</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>0.1113583569727966</v>
+        <v>0.1113583569727967</v>
       </c>
       <c r="D4" s="2" t="n">
         <v>0.1163795120288083</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0.005021155056011709</v>
+        <v>0.005021155056011667</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>0.007012519926916038</v>
+        <v>0.007012519926916028</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>0.03368074571068379</v>
+        <v>0.03368074571068376</v>
       </c>
     </row>
   </sheetData>
@@ -13748,13 +13748,13 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>0.1937588930478941</v>
+        <v>0.1937588930478912</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>0.427936014551821</v>
+        <v>0.4279360145518201</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>3.735259020504507e-17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -13764,13 +13764,13 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>0.3465774705782325</v>
+        <v>0.3465774705782329</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>0.4025461561604331</v>
+        <v>0.4025461561604337</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>0.2221693546039033</v>
+        <v>0.2221693546039032</v>
       </c>
     </row>
     <row r="4">
@@ -13780,13 +13780,13 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>0.3384510282616056</v>
+        <v>0.3384510282616053</v>
       </c>
       <c r="C4" s="2" t="n">
         <v>0.3391483660024529</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>0.3159012209564501</v>
+        <v>0.31590122095645</v>
       </c>
     </row>
     <row r="5">
@@ -13796,13 +13796,13 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>0.2854919704249195</v>
+        <v>0.2854919704249194</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>0.274398870332317</v>
+        <v>0.2743988703323169</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>0.3288283943947342</v>
+        <v>0.3288283943947343</v>
       </c>
     </row>
     <row r="6">
@@ -13815,10 +13815,10 @@
         <v>0.2537136369278277</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>0.2355487583306577</v>
+        <v>0.2355487583306576</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>0.327632154804668</v>
+        <v>0.3276321548046678</v>
       </c>
     </row>
     <row r="7">
@@ -13828,13 +13828,13 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>0.08556527673367774</v>
+        <v>0.08556527673367778</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>0.05540182866451901</v>
+        <v>0.05540182866451893</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>0.2214304253984209</v>
+        <v>0.2214304253984211</v>
       </c>
     </row>
   </sheetData>

--- a/Project 1/defense_results/analysis_results.xlsx
+++ b/Project 1/defense_results/analysis_results.xlsx
@@ -1,25 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="asset_stats_full" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="asset_stats_pre" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="asset_stats_post" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="correlation_matrix_full" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="defense_correlations" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="covariance_matrix_full" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="portfolio_weights" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="exclusion_cost" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="defense_weight_sensitivity" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="bootstrap_min_var_defense" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="returns_test" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="economic_conclusion" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="efficient_frontier_full" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="asset_stats_full" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="asset_stats_pre" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="asset_stats_post" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="correlation_matrix_full" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="defense_correlations" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="covariance_matrix_full" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="portfolio_weights" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="exclusion_cost" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="defense_weight_sensitivity" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="bootstrap_min_var_defense" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="returns_test" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="economic_conclusion" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="efficient_frontier_full" sheetId="13" state="visible" r:id="rId13"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -810,10 +810,10 @@
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>0.04496770866122467</v>
+        <v>0.04496770866122459</v>
       </c>
       <c r="E2" t="n">
-        <v>0.145307845304233</v>
+        <v>0.1453078453042332</v>
       </c>
       <c r="F2" t="n">
         <v>0.68</v>
@@ -829,13 +829,13 @@
         <v>500</v>
       </c>
       <c r="C3" t="n">
-        <v>3.660335397729083e-17</v>
+        <v>2.107181450903737e-17</v>
       </c>
       <c r="D3" t="n">
         <v>0.2166291567547662</v>
       </c>
       <c r="E3" t="n">
-        <v>0.4270913255303988</v>
+        <v>0.4270913255303989</v>
       </c>
       <c r="F3" t="n">
         <v>0.926</v>
@@ -975,13 +975,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.5486283832502574</v>
+        <v>0.5486283832502575</v>
       </c>
       <c r="D2" t="n">
         <v>0.3927084394723381</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.1559199437779193</v>
+        <v>-0.1559199437779195</v>
       </c>
     </row>
     <row r="3">
@@ -992,13 +992,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.05540182866451901</v>
+        <v>0.05540182866451893</v>
       </c>
       <c r="D3" t="n">
-        <v>0.2214304253984209</v>
+        <v>0.2214304253984211</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1660285967339019</v>
+        <v>0.1660285967339022</v>
       </c>
     </row>
     <row r="4">
@@ -1009,13 +1009,13 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.0002831058937633052</v>
+        <v>0.0002831058937632913</v>
       </c>
       <c r="D4" t="n">
-        <v>0.005021155056011695</v>
+        <v>0.005021155056011667</v>
       </c>
       <c r="E4" t="n">
-        <v>0.004738049162248389</v>
+        <v>0.004738049162248376</v>
       </c>
     </row>
     <row r="5">
@@ -1047,13 +1047,13 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.4025461561604331</v>
+        <v>0.4025461561604337</v>
       </c>
       <c r="D6" t="n">
-        <v>0.2221693546039033</v>
+        <v>0.2221693546039032</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.1803768015565298</v>
+        <v>-0.1803768015565305</v>
       </c>
     </row>
   </sheetData>
@@ -1131,16 +1131,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.09618145146571942</v>
+        <v>0.09618145146571878</v>
       </c>
       <c r="C2" t="n">
-        <v>0.2645843843735795</v>
+        <v>0.2645843843735805</v>
       </c>
       <c r="D2" t="n">
-        <v>1.137978600240785e-15</v>
+        <v>3.413935800722356e-15</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9999999999999876</v>
+        <v>0.999999999999993</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
@@ -1149,13 +1149,13 @@
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>3.108624468950438e-15</v>
+        <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>1.451616604697392e-14</v>
+        <v>8.187894806610529e-15</v>
       </c>
       <c r="J2" t="n">
-        <v>4.496403249731884e-15</v>
+        <v>1.498801083243961e-15</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
@@ -1166,34 +1166,34 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>0.09711190147763402</v>
+        <v>0.09711190147763374</v>
       </c>
       <c r="C3" t="n">
-        <v>0.2273940412051917</v>
+        <v>0.2273940412051913</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>0.8235072573763325</v>
+        <v>0.8235072573763311</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>5.551115123125783e-17</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>1.720845688168993e-15</v>
+        <v>4.579669976578771e-16</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1764927426236673</v>
+        <v>0.1764927426236688</v>
       </c>
       <c r="J3" t="n">
-        <v>1.540434446667405e-15</v>
+        <v>1.318389841742373e-15</v>
       </c>
       <c r="K3" t="n">
-        <v>4.85722573273506e-16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -1201,31 +1201,31 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>0.09804235148954925</v>
+        <v>0.09804235148954919</v>
       </c>
       <c r="C4" t="n">
-        <v>0.1923909432388075</v>
+        <v>0.1923909432388076</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>0.6470145147526758</v>
+        <v>0.6470145147526769</v>
       </c>
       <c r="F4" t="n">
-        <v>4.440892098500626e-16</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>6.661338147750939e-16</v>
+        <v>1.942890293094024e-16</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>3.469446951953614e-16</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3529854852473244</v>
+        <v>0.3529854852473232</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>3.05311331771918e-16</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
@@ -1236,31 +1236,31 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>0.09897280150146456</v>
+        <v>0.09897280150146458</v>
       </c>
       <c r="C5" t="n">
-        <v>0.1610079862876861</v>
+        <v>0.1610079862876859</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>0.4705217721290353</v>
+        <v>0.4705217721290342</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>2.368435745707945e-17</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>8.717875744392267e-17</v>
+        <v>4.079250134621409e-17</v>
       </c>
       <c r="I5" t="n">
-        <v>0.5294782278709648</v>
+        <v>0.5294782278709658</v>
       </c>
       <c r="J5" t="n">
-        <v>5.204170427930421e-17</v>
+        <v>1.179611963664229e-16</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
@@ -1271,34 +1271,34 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>0.0999032515133801</v>
+        <v>0.09990325151338013</v>
       </c>
       <c r="C6" t="n">
-        <v>0.1357790108960865</v>
+        <v>0.1357790108960859</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>0.2940290295053831</v>
+        <v>0.2940290295053777</v>
       </c>
       <c r="F6" t="n">
-        <v>1.36185190347453e-16</v>
+        <v>6.892493574968853e-17</v>
       </c>
       <c r="G6" t="n">
-        <v>2.607934249801045e-19</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>1.143787035188694e-17</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>0.7059709704946169</v>
+        <v>0.7059709704946222</v>
       </c>
       <c r="J6" t="n">
-        <v>4.163336342344337e-17</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>1.265285448363179e-17</v>
+        <v>1.294622775371346e-16</v>
       </c>
     </row>
     <row r="7">
@@ -1312,25 +1312,25 @@
         <v>0.1206290988726618</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>2.104756316113397e-17</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1175362868817243</v>
+        <v>0.1175362868817235</v>
       </c>
       <c r="F7" t="n">
-        <v>1.486026504242479e-17</v>
+        <v>1.485525434196194e-17</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>2.023881901708053e-17</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>0.8824637131182758</v>
+        <v>0.8824637131182764</v>
       </c>
       <c r="J7" t="n">
-        <v>4.163336342344337e-17</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
@@ -1347,25 +1347,25 @@
         <v>0.1160975746495587</v>
       </c>
       <c r="D8" t="n">
-        <v>1.619361812672808e-17</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>0.05236197952437702</v>
+        <v>0.05236197952437716</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>4.552503251496558e-18</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>8.988347145731723e-18</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>0.8579901167055155</v>
+        <v>0.8579901167055159</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0896479037701074</v>
+        <v>0.08964790377010706</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
@@ -1385,25 +1385,25 @@
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>0.03243329642179553</v>
+        <v>0.03243329642179543</v>
       </c>
       <c r="F9" t="n">
-        <v>2.283671742205936e-18</v>
+        <v>7.51630268626449e-19</v>
       </c>
       <c r="G9" t="n">
-        <v>6.785618142388495e-18</v>
+        <v>8.673617379884035e-19</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>0.7518333072459269</v>
+        <v>0.751833307245928</v>
       </c>
       <c r="J9" t="n">
-        <v>0.2157333963322776</v>
+        <v>0.2157333963322766</v>
       </c>
       <c r="K9" t="n">
-        <v>5.454805508981572e-18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -1420,25 +1420,25 @@
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>0.02637427479091802</v>
+        <v>0.02637427479091794</v>
       </c>
       <c r="F10" t="n">
-        <v>9.085017107437435e-19</v>
+        <v>2.588532686809142e-18</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>9.537590986083422e-19</v>
       </c>
       <c r="H10" t="n">
-        <v>1.70215571007729e-18</v>
+        <v>2.31239994600424e-18</v>
       </c>
       <c r="I10" t="n">
-        <v>0.7120264257898332</v>
+        <v>0.7120264257898328</v>
       </c>
       <c r="J10" t="n">
-        <v>0.2302090700117014</v>
+        <v>0.2302090700117016</v>
       </c>
       <c r="K10" t="n">
-        <v>0.03139022940754746</v>
+        <v>0.03139022940754761</v>
       </c>
     </row>
     <row r="11">
@@ -1452,28 +1452,28 @@
         <v>0.1125223819902301</v>
       </c>
       <c r="D11" t="n">
-        <v>4.685388816446753e-18</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>0.02151704454332665</v>
+        <v>0.02151704454332637</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>3.319748087794017e-18</v>
+        <v>3.808260130855334e-18</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>0.6779879247762909</v>
+        <v>0.6779879247762913</v>
       </c>
       <c r="J11" t="n">
-        <v>0.2349880368880829</v>
+        <v>0.2349880368880825</v>
       </c>
       <c r="K11" t="n">
-        <v>0.06550699379229966</v>
+        <v>0.06550699379229985</v>
       </c>
     </row>
     <row r="12">
@@ -1487,28 +1487,28 @@
         <v>0.1119083053836945</v>
       </c>
       <c r="D12" t="n">
-        <v>9.621059161970661e-18</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>0.01666421755553578</v>
+        <v>0.01666421755553583</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>3.469446951953614e-18</v>
       </c>
       <c r="G12" t="n">
-        <v>4.720064661475746e-18</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>4.485886488658775e-18</v>
       </c>
       <c r="I12" t="n">
-        <v>0.6439466574751572</v>
+        <v>0.6439466574751569</v>
       </c>
       <c r="J12" t="n">
-        <v>0.2397635865287553</v>
+        <v>0.2397635865287556</v>
       </c>
       <c r="K12" t="n">
-        <v>0.09962553844055169</v>
+        <v>0.09962553844055166</v>
       </c>
     </row>
     <row r="13">
@@ -1522,28 +1522,28 @@
         <v>0.1113971369552268</v>
       </c>
       <c r="D13" t="n">
-        <v>1.515594160736692e-18</v>
+        <v>1.642396884726088e-18</v>
       </c>
       <c r="E13" t="n">
-        <v>0.01181045764170472</v>
+        <v>0.01181045764170473</v>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>6.481919628863533e-19</v>
       </c>
       <c r="G13" t="n">
-        <v>1.010413080290299e-18</v>
+        <v>4.54009659728305e-19</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>0.6099063989094544</v>
+        <v>0.6099063989094541</v>
       </c>
       <c r="J13" t="n">
         <v>0.244539292380594</v>
       </c>
       <c r="K13" t="n">
-        <v>0.1337438510682469</v>
+        <v>0.1337438510682471</v>
       </c>
     </row>
     <row r="14">
@@ -1557,28 +1557,28 @@
         <v>0.1109902985508705</v>
       </c>
       <c r="D14" t="n">
-        <v>8.329294059862377e-19</v>
+        <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>0.006955778246507852</v>
+        <v>0.006955778246507883</v>
       </c>
       <c r="F14" t="n">
-        <v>1.450779274231137e-18</v>
+        <v>0</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>3.784945711997093e-19</v>
+        <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>0.5758664171335486</v>
+        <v>0.5758664171335499</v>
       </c>
       <c r="J14" t="n">
-        <v>0.2493161160151899</v>
+        <v>0.2493161160151896</v>
       </c>
       <c r="K14" t="n">
-        <v>0.1678616886047535</v>
+        <v>0.1678616886047527</v>
       </c>
     </row>
     <row r="15">
@@ -1592,28 +1592,28 @@
         <v>0.1106721683798148</v>
       </c>
       <c r="D15" t="n">
-        <v>0.007597357360251461</v>
+        <v>0.007597357360251376</v>
       </c>
       <c r="E15" t="n">
-        <v>0.002887592546588841</v>
+        <v>0.002887592546588894</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>6.901921999726022e-19</v>
+        <v>1.728794245346027e-18</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>0.5545928110886682</v>
+        <v>0.5545928110886686</v>
       </c>
       <c r="J15" t="n">
         <v>0.2515914422490584</v>
       </c>
       <c r="K15" t="n">
-        <v>0.183330796755433</v>
+        <v>0.1833307967554327</v>
       </c>
     </row>
     <row r="16">
@@ -1621,22 +1621,22 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0.1092077516325357</v>
+        <v>0.1092077516325356</v>
       </c>
       <c r="C16" t="n">
         <v>0.1103907094646385</v>
       </c>
       <c r="D16" t="n">
-        <v>0.01892067258822476</v>
+        <v>0.01892067258822462</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>1.829190606784532e-19</v>
+        <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>2.361712179643743e-19</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -1645,10 +1645,10 @@
         <v>0.5384624601749175</v>
       </c>
       <c r="J16" t="n">
-        <v>0.2528538470237848</v>
+        <v>0.2528538470237847</v>
       </c>
       <c r="K16" t="n">
-        <v>0.189763020213073</v>
+        <v>0.1897630202130731</v>
       </c>
     </row>
     <row r="17">
@@ -1662,28 +1662,28 @@
         <v>0.1101472379998125</v>
       </c>
       <c r="D17" t="n">
-        <v>0.03051938344104291</v>
+        <v>0.03051938344104311</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>1.520713106583527e-18</v>
+        <v>1.417933153703699e-18</v>
       </c>
       <c r="G17" t="n">
-        <v>5.371211999578603e-19</v>
+        <v>1.660184576618429e-18</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>0.5187784391361221</v>
+        <v>0.5187784391361218</v>
       </c>
       <c r="J17" t="n">
-        <v>0.2547895957559917</v>
+        <v>0.2547895957559921</v>
       </c>
       <c r="K17" t="n">
-        <v>0.1959125816668433</v>
+        <v>0.1959125816668431</v>
       </c>
     </row>
     <row r="18">
@@ -1697,28 +1697,28 @@
         <v>0.1099442586094209</v>
       </c>
       <c r="D18" t="n">
-        <v>0.04211775014185026</v>
+        <v>0.0421177501418505</v>
       </c>
       <c r="E18" t="n">
-        <v>1.481729812207616e-18</v>
+        <v>1.836367429647323e-18</v>
       </c>
       <c r="F18" t="n">
-        <v>4.159518616780226e-18</v>
+        <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>1.963635362516022e-18</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>8.4692801866007e-19</v>
+        <v>1.948175778684891e-19</v>
       </c>
       <c r="I18" t="n">
-        <v>0.4990921468251596</v>
+        <v>0.4990921468251598</v>
       </c>
       <c r="J18" t="n">
         <v>0.2567276745515377</v>
       </c>
       <c r="K18" t="n">
-        <v>0.2020624284814523</v>
+        <v>0.2020624284814521</v>
       </c>
     </row>
     <row r="19">
@@ -1732,28 +1732,28 @@
         <v>0.1097819958959985</v>
       </c>
       <c r="D19" t="n">
-        <v>0.05371712659096846</v>
+        <v>0.05371712659096856</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>0</v>
+        <v>2.381856647679093e-18</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>1.112080731247794e-18</v>
+        <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>0.4794085901519546</v>
+        <v>0.4794085901519539</v>
       </c>
       <c r="J19" t="n">
-        <v>0.2586641945070268</v>
+        <v>0.2586641945070273</v>
       </c>
       <c r="K19" t="n">
-        <v>0.20821008875005</v>
+        <v>0.2082100887500502</v>
       </c>
     </row>
     <row r="20">
@@ -1767,25 +1767,25 @@
         <v>0.1096582514327414</v>
       </c>
       <c r="D20" t="n">
-        <v>0.06183631525396524</v>
+        <v>0.06183631525396507</v>
       </c>
       <c r="E20" t="n">
-        <v>2.443039666293663e-18</v>
+        <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>9.528249835286282e-18</v>
+        <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>7.364104443428887e-18</v>
       </c>
       <c r="H20" t="n">
-        <v>0.003551301472866447</v>
+        <v>0.003551301472866376</v>
       </c>
       <c r="I20" t="n">
-        <v>0.4632524206283112</v>
+        <v>0.4632524206283116</v>
       </c>
       <c r="J20" t="n">
-        <v>0.2599779900446708</v>
+        <v>0.2599779900446709</v>
       </c>
       <c r="K20" t="n">
         <v>0.2113819726001862</v>
@@ -1799,31 +1799,31 @@
         <v>0.1138600016921134</v>
       </c>
       <c r="C21" t="n">
-        <v>0.1095571601554472</v>
+        <v>0.1095571601554473</v>
       </c>
       <c r="D21" t="n">
         <v>0.06607196770974259</v>
       </c>
       <c r="E21" t="n">
-        <v>5.838423338942785e-18</v>
+        <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>1.242766740211509e-17</v>
       </c>
       <c r="G21" t="n">
-        <v>6.580625779217787e-18</v>
+        <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>0.0110690323207517</v>
+        <v>0.01106903232075163</v>
       </c>
       <c r="I21" t="n">
-        <v>0.451042637571679</v>
+        <v>0.4510426375716799</v>
       </c>
       <c r="J21" t="n">
-        <v>0.2605945774037351</v>
+        <v>0.2605945774037348</v>
       </c>
       <c r="K21" t="n">
-        <v>0.2112217849940916</v>
+        <v>0.2112217849940912</v>
       </c>
     </row>
     <row r="22">
@@ -1837,19 +1837,19 @@
         <v>0.1094758099593584</v>
       </c>
       <c r="D22" t="n">
-        <v>0.0703087378386089</v>
+        <v>0.07030873783860873</v>
       </c>
       <c r="E22" t="n">
-        <v>0</v>
+        <v>7.630072788866737e-18</v>
       </c>
       <c r="F22" t="n">
-        <v>0</v>
+        <v>6.532318089225164e-18</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>3.743885626864007e-18</v>
       </c>
       <c r="H22" t="n">
-        <v>0.01858674246437618</v>
+        <v>0.01858674246437601</v>
       </c>
       <c r="I22" t="n">
         <v>0.4388349386179975</v>
@@ -1858,7 +1858,7 @@
         <v>0.261210640930829</v>
       </c>
       <c r="K22" t="n">
-        <v>0.2110589401481884</v>
+        <v>0.2110589401481888</v>
       </c>
     </row>
     <row r="23">
@@ -1866,34 +1866,34 @@
         <v>21</v>
       </c>
       <c r="B23" t="n">
-        <v>0.1157209017159445</v>
+        <v>0.1157209017159446</v>
       </c>
       <c r="C23" t="n">
-        <v>0.1094142448752292</v>
+        <v>0.1094142448752293</v>
       </c>
       <c r="D23" t="n">
-        <v>0.07454224331347185</v>
+        <v>0.07454224331347173</v>
       </c>
       <c r="E23" t="n">
-        <v>3.981576214845981e-18</v>
+        <v>0</v>
       </c>
       <c r="F23" t="n">
         <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>2.853145779531385e-17</v>
       </c>
       <c r="H23" t="n">
-        <v>0.02610597444911851</v>
+        <v>0.02610597444911859</v>
       </c>
       <c r="I23" t="n">
-        <v>0.4266272606485539</v>
+        <v>0.4266272606485547</v>
       </c>
       <c r="J23" t="n">
         <v>0.2618247233959889</v>
       </c>
       <c r="K23" t="n">
-        <v>0.2108997981928667</v>
+        <v>0.2108997981928662</v>
       </c>
     </row>
     <row r="24">
@@ -1907,25 +1907,25 @@
         <v>0.1093724983151886</v>
       </c>
       <c r="D24" t="n">
-        <v>0.07877653755066487</v>
+        <v>0.07877653755066479</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>1.614798509896962e-17</v>
+        <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>1.903073605027831e-17</v>
+        <v>5.757664107313744e-17</v>
       </c>
       <c r="H24" t="n">
-        <v>0.03362415596972386</v>
+        <v>0.03362415596972366</v>
       </c>
       <c r="I24" t="n">
-        <v>0.4144162389246496</v>
+        <v>0.4144162389246497</v>
       </c>
       <c r="J24" t="n">
-        <v>0.2624415761140788</v>
+        <v>0.262441576114079</v>
       </c>
       <c r="K24" t="n">
         <v>0.2107414914408828</v>
@@ -1942,7 +1942,7 @@
         <v>0.1093505929778188</v>
       </c>
       <c r="D25" t="n">
-        <v>0.08301247502926264</v>
+        <v>0.08301247502926272</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>
@@ -1951,19 +1951,19 @@
         <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>4.920935926580451e-18</v>
+        <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>0.04114203851843528</v>
+        <v>0.04114203851843538</v>
       </c>
       <c r="I25" t="n">
-        <v>0.4022087354469262</v>
+        <v>0.4022087354469259</v>
       </c>
       <c r="J25" t="n">
-        <v>0.2630561857461575</v>
+        <v>0.2630561857461576</v>
       </c>
       <c r="K25" t="n">
-        <v>0.2105805652592186</v>
+        <v>0.2105805652592184</v>
       </c>
     </row>
     <row r="26">
@@ -1977,28 +1977,28 @@
         <v>0.109348540786506</v>
       </c>
       <c r="D26" t="n">
-        <v>0.08724693709647677</v>
+        <v>0.08724693709647681</v>
       </c>
       <c r="E26" t="n">
-        <v>0</v>
+        <v>5.202476362035913e-18</v>
       </c>
       <c r="F26" t="n">
-        <v>0</v>
+        <v>4.666304506423941e-18</v>
       </c>
       <c r="G26" t="n">
-        <v>2.822483087856566e-17</v>
+        <v>2.401338405465941e-18</v>
       </c>
       <c r="H26" t="n">
-        <v>0.04866090037213219</v>
+        <v>0.04866090037213228</v>
       </c>
       <c r="I26" t="n">
-        <v>0.3900007837785772</v>
+        <v>0.3900007837785778</v>
       </c>
       <c r="J26" t="n">
-        <v>0.2636714516649238</v>
+        <v>0.2636714516649237</v>
       </c>
       <c r="K26" t="n">
-        <v>0.21041992708789</v>
+        <v>0.2104199270878896</v>
       </c>
     </row>
     <row r="27">
@@ -2012,7 +2012,7 @@
         <v>0.1093663428602169</v>
       </c>
       <c r="D27" t="n">
-        <v>0.0914795240864421</v>
+        <v>0.09147952408644214</v>
       </c>
       <c r="E27" t="n">
         <v>0</v>
@@ -2021,19 +2021,19 @@
         <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>3.038410159292888e-17</v>
+        <v>1.940721888749053e-17</v>
       </c>
       <c r="H27" t="n">
-        <v>0.05618166824281052</v>
+        <v>0.05618166824281071</v>
       </c>
       <c r="I27" t="n">
-        <v>0.3777942892145605</v>
+        <v>0.3777942892145602</v>
       </c>
       <c r="J27" t="n">
-        <v>0.2642869540733484</v>
+        <v>0.2642869540733483</v>
       </c>
       <c r="K27" t="n">
-        <v>0.2102575643828386</v>
+        <v>0.2102575643828387</v>
       </c>
     </row>
     <row r="28">
@@ -2041,34 +2041,34 @@
         <v>26</v>
       </c>
       <c r="B28" t="n">
-        <v>0.1203731517755224</v>
+        <v>0.1203731517755223</v>
       </c>
       <c r="C28" t="n">
         <v>0.1094039895035435</v>
       </c>
       <c r="D28" t="n">
-        <v>0.09571609666840401</v>
+        <v>0.09571609666840386</v>
       </c>
       <c r="E28" t="n">
-        <v>3.919703372313374e-18</v>
+        <v>6.372228862194101e-18</v>
       </c>
       <c r="F28" t="n">
-        <v>0</v>
+        <v>4.255493527005605e-18</v>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
+        <v>1.750668871208869e-17</v>
       </c>
       <c r="H28" t="n">
-        <v>0.06369787966537116</v>
+        <v>0.06369787966537133</v>
       </c>
       <c r="I28" t="n">
-        <v>0.3655825118449844</v>
+        <v>0.3655825118449852</v>
       </c>
       <c r="J28" t="n">
-        <v>0.2649032672557623</v>
+        <v>0.2649032672557619</v>
       </c>
       <c r="K28" t="n">
-        <v>0.2101002445654782</v>
+        <v>0.2101002445654777</v>
       </c>
     </row>
     <row r="29">
@@ -2082,25 +2082,25 @@
         <v>0.1094614602463602</v>
       </c>
       <c r="D29" t="n">
-        <v>0.09994920257131835</v>
+        <v>0.09994920257131831</v>
       </c>
       <c r="E29" t="n">
-        <v>0</v>
+        <v>2.168404344971009e-19</v>
       </c>
       <c r="F29" t="n">
         <v>0</v>
       </c>
       <c r="G29" t="n">
-        <v>1.118461330449008e-17</v>
+        <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>0.07121866549901006</v>
+        <v>0.07121866549900994</v>
       </c>
       <c r="I29" t="n">
-        <v>0.3533776975197445</v>
+        <v>0.353377697519745</v>
       </c>
       <c r="J29" t="n">
-        <v>0.2655176576569458</v>
+        <v>0.2655176576569452</v>
       </c>
       <c r="K29" t="n">
         <v>0.2099367767529814</v>
@@ -2117,7 +2117,7 @@
         <v>0.1095387238814366</v>
       </c>
       <c r="D30" t="n">
-        <v>0.1041842242043013</v>
+        <v>0.1041842242043015</v>
       </c>
       <c r="E30" t="n">
         <v>0</v>
@@ -2126,19 +2126,19 @@
         <v>0</v>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>6.331740687315346e-17</v>
       </c>
       <c r="H30" t="n">
-        <v>0.07873692275940002</v>
+        <v>0.07873692275940024</v>
       </c>
       <c r="I30" t="n">
-        <v>0.3411690630484674</v>
+        <v>0.3411690630484681</v>
       </c>
       <c r="J30" t="n">
-        <v>0.2661330711326146</v>
+        <v>0.2661330711326142</v>
       </c>
       <c r="K30" t="n">
-        <v>0.2097767188552166</v>
+        <v>0.2097767188552159</v>
       </c>
     </row>
     <row r="31">
@@ -2152,28 +2152,28 @@
         <v>0.1096357385644733</v>
       </c>
       <c r="D31" t="n">
-        <v>0.1084192405986546</v>
+        <v>0.1084192405986545</v>
       </c>
       <c r="E31" t="n">
-        <v>7.76904143832144e-18</v>
+        <v>1.084202172485504e-19</v>
       </c>
       <c r="F31" t="n">
-        <v>1.379972684437317e-17</v>
+        <v>0</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>0.08625518402379111</v>
+        <v>0.08625518402379109</v>
       </c>
       <c r="I31" t="n">
-        <v>0.3289604304340353</v>
+        <v>0.3289604304340351</v>
       </c>
       <c r="J31" t="n">
-        <v>0.2667484839987776</v>
+        <v>0.2667484839987777</v>
       </c>
       <c r="K31" t="n">
-        <v>0.2096166609447415</v>
+        <v>0.2096166609447418</v>
       </c>
     </row>
     <row r="32">
@@ -2187,25 +2187,25 @@
         <v>0.1097524519192115</v>
       </c>
       <c r="D32" t="n">
-        <v>0.1126542443354555</v>
+        <v>0.1126542443354554</v>
       </c>
       <c r="E32" t="n">
-        <v>2.880546822844913e-18</v>
+        <v>1.517883041479706e-18</v>
       </c>
       <c r="F32" t="n">
-        <v>1.922771304397248e-18</v>
+        <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>2.135878279796444e-17</v>
       </c>
       <c r="H32" t="n">
-        <v>0.09377345653335868</v>
+        <v>0.09377345653335885</v>
       </c>
       <c r="I32" t="n">
-        <v>0.3167518092904546</v>
+        <v>0.3167518092904545</v>
       </c>
       <c r="J32" t="n">
-        <v>0.2673638910558487</v>
+        <v>0.2673638910558486</v>
       </c>
       <c r="K32" t="n">
         <v>0.2094565987848826</v>
@@ -2222,13 +2222,13 @@
         <v>0.1098888011795569</v>
       </c>
       <c r="D33" t="n">
-        <v>0.1168892221663364</v>
+        <v>0.1168892221663367</v>
       </c>
       <c r="E33" t="n">
         <v>0</v>
       </c>
       <c r="F33" t="n">
-        <v>1.748048285914617e-17</v>
+        <v>3.572446158339737e-17</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -2237,13 +2237,13 @@
         <v>0.101291753116991</v>
       </c>
       <c r="I33" t="n">
-        <v>0.3045432157202151</v>
+        <v>0.3045432157202156</v>
       </c>
       <c r="J33" t="n">
-        <v>0.2679792841225115</v>
+        <v>0.2679792841225117</v>
       </c>
       <c r="K33" t="n">
-        <v>0.2092965248739458</v>
+        <v>0.2092965248739452</v>
       </c>
     </row>
     <row r="34">
@@ -2257,25 +2257,25 @@
         <v>0.1100447133568239</v>
       </c>
       <c r="D34" t="n">
-        <v>0.1211241538075818</v>
+        <v>0.1211241538075816</v>
       </c>
       <c r="E34" t="n">
-        <v>1.592452184109451e-18</v>
+        <v>0</v>
       </c>
       <c r="F34" t="n">
-        <v>0</v>
+        <v>9.215718466126788e-19</v>
       </c>
       <c r="G34" t="n">
-        <v>0</v>
+        <v>8.673617379884035e-19</v>
       </c>
       <c r="H34" t="n">
-        <v>0.1088100925187921</v>
+        <v>0.108810092518792</v>
       </c>
       <c r="I34" t="n">
-        <v>0.2923346709060302</v>
+        <v>0.2923346709060304</v>
       </c>
       <c r="J34" t="n">
-        <v>0.2685946524524331</v>
+        <v>0.2685946524524332</v>
       </c>
       <c r="K34" t="n">
         <v>0.2091364303151629</v>
@@ -2292,28 +2292,28 @@
         <v>0.1102201054327244</v>
       </c>
       <c r="D35" t="n">
-        <v>0.125359015143681</v>
+        <v>0.1253590151436812</v>
       </c>
       <c r="E35" t="n">
         <v>0</v>
       </c>
       <c r="F35" t="n">
-        <v>2.607281344439963e-17</v>
+        <v>0</v>
       </c>
       <c r="G35" t="n">
-        <v>2.600529012239415e-17</v>
+        <v>2.059984127722458e-18</v>
       </c>
       <c r="H35" t="n">
         <v>0.1163285008413075</v>
       </c>
       <c r="I35" t="n">
-        <v>0.2801261983968407</v>
+        <v>0.2801261983968398</v>
       </c>
       <c r="J35" t="n">
-        <v>0.2692099977323207</v>
+        <v>0.2692099977323208</v>
       </c>
       <c r="K35" t="n">
-        <v>0.2089762878858501</v>
+        <v>0.2089762878858507</v>
       </c>
     </row>
     <row r="36">
@@ -2327,28 +2327,28 @@
         <v>0.1104148845764814</v>
       </c>
       <c r="D36" t="n">
-        <v>0.1295941574797573</v>
+        <v>0.1295941574797572</v>
       </c>
       <c r="E36" t="n">
-        <v>4.011069267878784e-18</v>
+        <v>2.276824562219559e-18</v>
       </c>
       <c r="F36" t="n">
-        <v>5.881108334329405e-17</v>
+        <v>3.71881345162528e-17</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>0.1238465819068818</v>
+        <v>0.1238465819068817</v>
       </c>
       <c r="I36" t="n">
-        <v>0.2679172444457518</v>
+        <v>0.2679172444457517</v>
       </c>
       <c r="J36" t="n">
-        <v>0.2698255272829214</v>
+        <v>0.2698255272829215</v>
       </c>
       <c r="K36" t="n">
-        <v>0.2088164888846876</v>
+        <v>0.2088164888846879</v>
       </c>
     </row>
     <row r="37">
@@ -2362,13 +2362,13 @@
         <v>0.1106289483861336</v>
       </c>
       <c r="D37" t="n">
-        <v>0.1338303390067653</v>
+        <v>0.1338303390067652</v>
       </c>
       <c r="E37" t="n">
-        <v>0</v>
+        <v>1.244121992927116e-17</v>
       </c>
       <c r="F37" t="n">
-        <v>2.57371484310836e-17</v>
+        <v>0</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
@@ -2377,13 +2377,13 @@
         <v>0.131363579891667</v>
       </c>
       <c r="I37" t="n">
-        <v>0.2557068529450158</v>
+        <v>0.2557068529450163</v>
       </c>
       <c r="J37" t="n">
-        <v>0.2704416862383893</v>
+        <v>0.2704416862383888</v>
       </c>
       <c r="K37" t="n">
-        <v>0.2086575419181625</v>
+        <v>0.2086575419181627</v>
       </c>
     </row>
     <row r="38">
@@ -2397,28 +2397,28 @@
         <v>0.1108621851539934</v>
       </c>
       <c r="D38" t="n">
-        <v>0.1380637002718754</v>
+        <v>0.1380637002718751</v>
       </c>
       <c r="E38" t="n">
-        <v>4.555049768151387e-19</v>
+        <v>0</v>
       </c>
       <c r="F38" t="n">
         <v>0</v>
       </c>
       <c r="G38" t="n">
-        <v>0</v>
+        <v>5.366800753803247e-18</v>
       </c>
       <c r="H38" t="n">
         <v>0.1388833316719817</v>
       </c>
       <c r="I38" t="n">
-        <v>0.2434995289491955</v>
+        <v>0.2434995289491967</v>
       </c>
       <c r="J38" t="n">
-        <v>0.2710566610429038</v>
+        <v>0.2710566610429031</v>
       </c>
       <c r="K38" t="n">
-        <v>0.2084967780640437</v>
+        <v>0.2084967780640436</v>
       </c>
     </row>
     <row r="39">
@@ -2432,28 +2432,28 @@
         <v>0.1111144741400833</v>
       </c>
       <c r="D39" t="n">
-        <v>0.1423010805438031</v>
+        <v>0.1423010805438029</v>
       </c>
       <c r="E39" t="n">
-        <v>3.408366948323002e-18</v>
+        <v>8.688863972934613e-18</v>
       </c>
       <c r="F39" t="n">
-        <v>5.32628290525947e-17</v>
+        <v>0</v>
       </c>
       <c r="G39" t="n">
-        <v>2.510191027443192e-19</v>
+        <v>7.600426635712837e-18</v>
       </c>
       <c r="H39" t="n">
-        <v>0.1463991822031944</v>
+        <v>0.1463991822031946</v>
       </c>
       <c r="I39" t="n">
-        <v>0.2312879476810557</v>
+        <v>0.2312879476810566</v>
       </c>
       <c r="J39" t="n">
-        <v>0.2716732441013335</v>
+        <v>0.2716732441013333</v>
       </c>
       <c r="K39" t="n">
-        <v>0.2083385454706134</v>
+        <v>0.2083385454706127</v>
       </c>
     </row>
     <row r="40">
@@ -2470,10 +2470,10 @@
         <v>0.1465362109069696</v>
       </c>
       <c r="E40" t="n">
-        <v>0</v>
+        <v>1.420135522084621e-17</v>
       </c>
       <c r="F40" t="n">
-        <v>9.772529086089086e-19</v>
+        <v>0</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
@@ -2482,13 +2482,13 @@
         <v>0.1539174632541163</v>
       </c>
       <c r="I40" t="n">
-        <v>0.2190796339151477</v>
+        <v>0.2190796339151473</v>
       </c>
       <c r="J40" t="n">
-        <v>0.2722885310560004</v>
+        <v>0.2722885310560005</v>
       </c>
       <c r="K40" t="n">
-        <v>0.2081781608677659</v>
+        <v>0.2081781608677662</v>
       </c>
     </row>
     <row r="41">
@@ -2502,13 +2502,13 @@
         <v>0.1116756825305589</v>
       </c>
       <c r="D41" t="n">
-        <v>0.1507715766059159</v>
+        <v>0.1507715766059158</v>
       </c>
       <c r="E41" t="n">
         <v>0</v>
       </c>
       <c r="F41" t="n">
-        <v>0</v>
+        <v>4.411347589300396e-18</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
@@ -2517,13 +2517,13 @@
         <v>0.1614355004458819</v>
       </c>
       <c r="I41" t="n">
-        <v>0.2068707892430923</v>
+        <v>0.2068707892430913</v>
       </c>
       <c r="J41" t="n">
         <v>0.2729042409894557</v>
       </c>
       <c r="K41" t="n">
-        <v>0.2080178927156543</v>
+        <v>0.2080178927156553</v>
       </c>
     </row>
     <row r="42">
@@ -2543,22 +2543,22 @@
         <v>0</v>
       </c>
       <c r="F42" t="n">
-        <v>1.34901486198464e-17</v>
+        <v>2.546519852625329e-17</v>
       </c>
       <c r="G42" t="n">
-        <v>3.259276631780997e-17</v>
+        <v>1.897353801849633e-17</v>
       </c>
       <c r="H42" t="n">
         <v>0.1689539160386832</v>
       </c>
       <c r="I42" t="n">
-        <v>0.1946624075711548</v>
+        <v>0.1946624075711542</v>
       </c>
       <c r="J42" t="n">
-        <v>0.2735193597480547</v>
+        <v>0.2735193597480549</v>
       </c>
       <c r="K42" t="n">
-        <v>0.2078579396942373</v>
+        <v>0.2078579396942378</v>
       </c>
     </row>
     <row r="43">
@@ -2566,34 +2566,34 @@
         <v>41</v>
       </c>
       <c r="B43" t="n">
-        <v>0.1343299019542556</v>
+        <v>0.1343299019542557</v>
       </c>
       <c r="C43" t="n">
         <v>0.112311439028643</v>
       </c>
       <c r="D43" t="n">
-        <v>0.1592415862897674</v>
+        <v>0.1592415862897673</v>
       </c>
       <c r="E43" t="n">
         <v>0</v>
       </c>
       <c r="F43" t="n">
-        <v>2.324777338621368e-17</v>
+        <v>0</v>
       </c>
       <c r="G43" t="n">
-        <v>1.777000460654567e-17</v>
+        <v>1.544988095791844e-17</v>
       </c>
       <c r="H43" t="n">
-        <v>0.1764719441571624</v>
+        <v>0.1764719441571621</v>
       </c>
       <c r="I43" t="n">
         <v>0.1824534728601895</v>
       </c>
       <c r="J43" t="n">
-        <v>0.2741348337693598</v>
+        <v>0.2741348337693593</v>
       </c>
       <c r="K43" t="n">
-        <v>0.2076981629235209</v>
+        <v>0.2076981629235219</v>
       </c>
     </row>
     <row r="44">
@@ -2607,28 +2607,28 @@
         <v>0.1126568841959628</v>
       </c>
       <c r="D44" t="n">
-        <v>0.1634767238060609</v>
+        <v>0.1634767238060605</v>
       </c>
       <c r="E44" t="n">
-        <v>0</v>
+        <v>1.268177728629138e-17</v>
       </c>
       <c r="F44" t="n">
-        <v>5.183154426886679e-17</v>
+        <v>0</v>
       </c>
       <c r="G44" t="n">
-        <v>2.686441605935111e-17</v>
+        <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>0.1839900750365567</v>
+        <v>0.183990075036557</v>
       </c>
       <c r="I44" t="n">
-        <v>0.1702446180624727</v>
+        <v>0.1702446180624731</v>
       </c>
       <c r="J44" t="n">
-        <v>0.2747503800644077</v>
+        <v>0.2747503800644073</v>
       </c>
       <c r="K44" t="n">
-        <v>0.2075382030305019</v>
+        <v>0.2075382030305022</v>
       </c>
     </row>
     <row r="45">
@@ -2642,28 +2642,28 @@
         <v>0.1130204856099471</v>
       </c>
       <c r="D45" t="n">
-        <v>0.1677119655646171</v>
+        <v>0.167711965564617</v>
       </c>
       <c r="E45" t="n">
-        <v>9.497407319962234e-18</v>
+        <v>0</v>
       </c>
       <c r="F45" t="n">
-        <v>0</v>
+        <v>7.860465750519907e-18</v>
       </c>
       <c r="G45" t="n">
-        <v>1.264557763088912e-17</v>
+        <v>8.802366387866689e-18</v>
       </c>
       <c r="H45" t="n">
-        <v>0.1915080848635886</v>
+        <v>0.1915080848635885</v>
       </c>
       <c r="I45" t="n">
-        <v>0.1580356400686876</v>
+        <v>0.1580356400686878</v>
       </c>
       <c r="J45" t="n">
-        <v>0.2753659214081264</v>
+        <v>0.2753659214081263</v>
       </c>
       <c r="K45" t="n">
-        <v>0.2073783880949802</v>
+        <v>0.2073783880949805</v>
       </c>
     </row>
     <row r="46">
@@ -2671,16 +2671,16 @@
         <v>44</v>
       </c>
       <c r="B46" t="n">
-        <v>0.1371212519900024</v>
+        <v>0.1371212519900023</v>
       </c>
       <c r="C46" t="n">
         <v>0.1134020686275457</v>
       </c>
       <c r="D46" t="n">
-        <v>0.1719474230378664</v>
+        <v>0.1719474230378662</v>
       </c>
       <c r="E46" t="n">
-        <v>1.903156758174174e-17</v>
+        <v>1.740144486839235e-17</v>
       </c>
       <c r="F46" t="n">
         <v>0</v>
@@ -2689,16 +2689,16 @@
         <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>0.1990258542769376</v>
+        <v>0.1990258542769377</v>
       </c>
       <c r="I46" t="n">
-        <v>0.1458264791156027</v>
+        <v>0.145826479115602</v>
       </c>
       <c r="J46" t="n">
         <v>0.275981388216452</v>
       </c>
       <c r="K46" t="n">
-        <v>0.2072188553531414</v>
+        <v>0.207218855353142</v>
       </c>
     </row>
     <row r="47">
@@ -2715,7 +2715,7 @@
         <v>0.176182410943627</v>
       </c>
       <c r="E47" t="n">
-        <v>1.581540309722026e-17</v>
+        <v>0</v>
       </c>
       <c r="F47" t="n">
         <v>0</v>
@@ -2724,16 +2724,16 @@
         <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>0.2065441417283881</v>
+        <v>0.2065441417283879</v>
       </c>
       <c r="I47" t="n">
         <v>0.1336176679352684</v>
       </c>
       <c r="J47" t="n">
-        <v>0.2765970654118447</v>
+        <v>0.2765970654118449</v>
       </c>
       <c r="K47" t="n">
-        <v>0.2070587139808718</v>
+        <v>0.207058713980872</v>
       </c>
     </row>
     <row r="48">
@@ -2741,31 +2741,31 @@
         <v>46</v>
       </c>
       <c r="B48" t="n">
-        <v>0.1389821520138335</v>
+        <v>0.1389821520138334</v>
       </c>
       <c r="C48" t="n">
         <v>0.1142184501027817</v>
       </c>
       <c r="D48" t="n">
-        <v>0.1804156041046157</v>
+        <v>0.1804156041046156</v>
       </c>
       <c r="E48" t="n">
-        <v>1.655288967646643e-18</v>
+        <v>0</v>
       </c>
       <c r="F48" t="n">
-        <v>0</v>
+        <v>3.601584091725285e-18</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>0.214064023954264</v>
+        <v>0.2140640239542639</v>
       </c>
       <c r="I48" t="n">
-        <v>0.1214099476677634</v>
+        <v>0.1214099476677637</v>
       </c>
       <c r="J48" t="n">
-        <v>0.2772126393884525</v>
+        <v>0.2772126393884526</v>
       </c>
       <c r="K48" t="n">
         <v>0.2068977848849043</v>
@@ -2782,28 +2782,28 @@
         <v>0.1146528696430554</v>
       </c>
       <c r="D49" t="n">
-        <v>0.1846515059977886</v>
+        <v>0.1846515059977887</v>
       </c>
       <c r="E49" t="n">
-        <v>4.521062112439381e-18</v>
+        <v>1.152197742326343e-17</v>
       </c>
       <c r="F49" t="n">
-        <v>0</v>
+        <v>9.78746570552344e-18</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>0.221581952546833</v>
+        <v>0.2215819525468329</v>
       </c>
       <c r="I49" t="n">
-        <v>0.1092025271550564</v>
+        <v>0.1092025271550561</v>
       </c>
       <c r="J49" t="n">
-        <v>0.2778272109156683</v>
+        <v>0.2778272109156684</v>
       </c>
       <c r="K49" t="n">
-        <v>0.2067368033846537</v>
+        <v>0.2067368033846539</v>
       </c>
     </row>
     <row r="50">
@@ -2817,28 +2817,28 @@
         <v>0.115104513734655</v>
       </c>
       <c r="D50" t="n">
-        <v>0.1888888543180824</v>
+        <v>0.1888888543180823</v>
       </c>
       <c r="E50" t="n">
-        <v>0</v>
+        <v>1.09910995235718e-17</v>
       </c>
       <c r="F50" t="n">
-        <v>1.548090339180946e-17</v>
+        <v>1.095044194210359e-17</v>
       </c>
       <c r="G50" t="n">
-        <v>1.231479323559166e-17</v>
+        <v>0</v>
       </c>
       <c r="H50" t="n">
-        <v>0.2290973308875007</v>
+        <v>0.2290973308875006</v>
       </c>
       <c r="I50" t="n">
-        <v>0.0969901574620038</v>
+        <v>0.09699015746200433</v>
       </c>
       <c r="J50" t="n">
-        <v>0.2784432690368244</v>
+        <v>0.2784432690368243</v>
       </c>
       <c r="K50" t="n">
-        <v>0.2065803882955887</v>
+        <v>0.2065803882955885</v>
       </c>
     </row>
     <row r="51">
@@ -2852,28 +2852,28 @@
         <v>0.1155731804400865</v>
       </c>
       <c r="D51" t="n">
-        <v>0.1931238906945895</v>
+        <v>0.1931238906945897</v>
       </c>
       <c r="E51" t="n">
-        <v>0</v>
+        <v>8.673617379884035e-19</v>
       </c>
       <c r="F51" t="n">
-        <v>0</v>
+        <v>2.049142105997603e-17</v>
       </c>
       <c r="G51" t="n">
-        <v>0</v>
+        <v>9.75781955236954e-18</v>
       </c>
       <c r="H51" t="n">
-        <v>0.2366155422025429</v>
+        <v>0.236615542202543</v>
       </c>
       <c r="I51" t="n">
-        <v>0.08478125724787772</v>
+        <v>0.08478125724787718</v>
       </c>
       <c r="J51" t="n">
-        <v>0.2790589228073777</v>
+        <v>0.2790589228073778</v>
       </c>
       <c r="K51" t="n">
-        <v>0.2064203870476123</v>
+        <v>0.2064203870476122</v>
       </c>
     </row>
     <row r="52">
@@ -2881,34 +2881,34 @@
         <v>50</v>
       </c>
       <c r="B52" t="n">
-        <v>0.1427039520614957</v>
+        <v>0.1427039520614956</v>
       </c>
       <c r="C52" t="n">
         <v>0.116058663537498</v>
       </c>
       <c r="D52" t="n">
-        <v>0.1973563464604336</v>
+        <v>0.1973563464604331</v>
       </c>
       <c r="E52" t="n">
         <v>0</v>
       </c>
       <c r="F52" t="n">
-        <v>4.965849005561314e-17</v>
+        <v>0</v>
       </c>
       <c r="G52" t="n">
-        <v>7.413663717277386e-17</v>
+        <v>0</v>
       </c>
       <c r="H52" t="n">
-        <v>0.2441370343675414</v>
+        <v>0.2441370343675409</v>
       </c>
       <c r="I52" t="n">
-        <v>0.07257678981411608</v>
+        <v>0.07257678981411653</v>
       </c>
       <c r="J52" t="n">
-        <v>0.2796737539994139</v>
+        <v>0.2796737539994141</v>
       </c>
       <c r="K52" t="n">
-        <v>0.2062560753584949</v>
+        <v>0.2062560753584955</v>
       </c>
     </row>
     <row r="53">
@@ -2919,31 +2919,31 @@
         <v>0.1436344020734112</v>
       </c>
       <c r="C53" t="n">
-        <v>0.1165607529076992</v>
+        <v>0.1165607529076993</v>
       </c>
       <c r="D53" t="n">
-        <v>0.2015913774124759</v>
+        <v>0.2015913774124762</v>
       </c>
       <c r="E53" t="n">
-        <v>7.793232705014005e-18</v>
+        <v>5.885608433996506e-18</v>
       </c>
       <c r="F53" t="n">
-        <v>2.69851789248078e-17</v>
+        <v>1.572982534698598e-17</v>
       </c>
       <c r="G53" t="n">
-        <v>7.225700437853446e-18</v>
+        <v>8.94339737358453e-18</v>
       </c>
       <c r="H53" t="n">
-        <v>0.2516553078092906</v>
+        <v>0.2516553078092911</v>
       </c>
       <c r="I53" t="n">
-        <v>0.0603682026810215</v>
+        <v>0.06036820268102133</v>
       </c>
       <c r="J53" t="n">
-        <v>0.28028917540242</v>
+        <v>0.2802891754024199</v>
       </c>
       <c r="K53" t="n">
-        <v>0.2060959366947919</v>
+        <v>0.2060959366947915</v>
       </c>
     </row>
     <row r="54">
@@ -2951,7 +2951,7 @@
         <v>52</v>
       </c>
       <c r="B54" t="n">
-        <v>0.1445648520853268</v>
+        <v>0.1445648520853267</v>
       </c>
       <c r="C54" t="n">
         <v>0.1170792349027234</v>
@@ -2960,22 +2960,22 @@
         <v>0.205826473089182</v>
       </c>
       <c r="E54" t="n">
-        <v>1.524213611377932e-18</v>
+        <v>1.901377208349091e-18</v>
       </c>
       <c r="F54" t="n">
-        <v>0</v>
+        <v>7.922934430379912e-18</v>
       </c>
       <c r="G54" t="n">
-        <v>0</v>
+        <v>4.824064392850054e-18</v>
       </c>
       <c r="H54" t="n">
-        <v>0.2591735107359337</v>
+        <v>0.2591735107359335</v>
       </c>
       <c r="I54" t="n">
-        <v>0.04815960054247579</v>
+        <v>0.04815960054247592</v>
       </c>
       <c r="J54" t="n">
-        <v>0.2809045260551215</v>
+        <v>0.2809045260551214</v>
       </c>
       <c r="K54" t="n">
         <v>0.2059358895772871</v>
@@ -2992,7 +2992,7 @@
         <v>0.1176138927304629</v>
       </c>
       <c r="D55" t="n">
-        <v>0.2100623542505944</v>
+        <v>0.2100623542505942</v>
       </c>
       <c r="E55" t="n">
         <v>0</v>
@@ -3001,19 +3001,19 @@
         <v>0</v>
       </c>
       <c r="G55" t="n">
-        <v>0</v>
+        <v>1.874865077100031e-17</v>
       </c>
       <c r="H55" t="n">
-        <v>0.2666909543941109</v>
+        <v>0.2666909543941107</v>
       </c>
       <c r="I55" t="n">
-        <v>0.03595155885060996</v>
+        <v>0.03595155885061052</v>
       </c>
       <c r="J55" t="n">
         <v>0.2815183305234866</v>
       </c>
       <c r="K55" t="n">
-        <v>0.2057768019811981</v>
+        <v>0.2057768019811979</v>
       </c>
     </row>
     <row r="56">
@@ -3021,16 +3021,16 @@
         <v>54</v>
       </c>
       <c r="B56" t="n">
-        <v>0.1464257521091578</v>
+        <v>0.1464257521091579</v>
       </c>
       <c r="C56" t="n">
         <v>0.1181645068176946</v>
       </c>
       <c r="D56" t="n">
-        <v>0.2142957301350956</v>
+        <v>0.2142957301350958</v>
       </c>
       <c r="E56" t="n">
-        <v>6.227786396123461e-18</v>
+        <v>0</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -3039,16 +3039,16 @@
         <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>0.2742107865542008</v>
+        <v>0.274210786554201</v>
       </c>
       <c r="I56" t="n">
-        <v>0.0237425032469068</v>
+        <v>0.02374250324690682</v>
       </c>
       <c r="J56" t="n">
         <v>0.2821359206169048</v>
       </c>
       <c r="K56" t="n">
-        <v>0.2056150594468921</v>
+        <v>0.2056150594468917</v>
       </c>
     </row>
     <row r="57">
@@ -3062,10 +3062,10 @@
         <v>0.1187308551751066</v>
       </c>
       <c r="D57" t="n">
-        <v>0.2185301504743868</v>
+        <v>0.2185301504743865</v>
       </c>
       <c r="E57" t="n">
-        <v>2.630484887257343e-18</v>
+        <v>9.796783067943238e-18</v>
       </c>
       <c r="F57" t="n">
         <v>0</v>
@@ -3074,16 +3074,16 @@
         <v>0</v>
       </c>
       <c r="H57" t="n">
-        <v>0.2817289316912542</v>
+        <v>0.2817289316912543</v>
       </c>
       <c r="I57" t="n">
-        <v>0.01153197796818708</v>
+        <v>0.01153197796818594</v>
       </c>
       <c r="J57" t="n">
-        <v>0.2827522537770827</v>
+        <v>0.2827522537770829</v>
       </c>
       <c r="K57" t="n">
-        <v>0.2054566860890894</v>
+        <v>0.2054566860890903</v>
       </c>
     </row>
     <row r="58">
@@ -3097,28 +3097,28 @@
         <v>0.1193127300817046</v>
       </c>
       <c r="D58" t="n">
-        <v>0.2227930383300677</v>
+        <v>0.2227930383300678</v>
       </c>
       <c r="E58" t="n">
-        <v>6.205441862207055e-18</v>
+        <v>7.516438025036653e-18</v>
       </c>
       <c r="F58" t="n">
         <v>0</v>
       </c>
       <c r="G58" t="n">
-        <v>5.362633189316847e-17</v>
+        <v>0</v>
       </c>
       <c r="H58" t="n">
         <v>0.2893858199440145</v>
       </c>
       <c r="I58" t="n">
-        <v>0</v>
+        <v>5.430858943928333e-17</v>
       </c>
       <c r="J58" t="n">
         <v>0.2829624375304455</v>
       </c>
       <c r="K58" t="n">
-        <v>0.2048587041954723</v>
+        <v>0.2048587041954722</v>
       </c>
     </row>
     <row r="59">
@@ -3126,34 +3126,34 @@
         <v>57</v>
       </c>
       <c r="B59" t="n">
-        <v>0.1492171021449046</v>
+        <v>0.1492171021449045</v>
       </c>
       <c r="C59" t="n">
         <v>0.1199157968984054</v>
       </c>
       <c r="D59" t="n">
-        <v>0.2275054946207085</v>
+        <v>0.2275054946207086</v>
       </c>
       <c r="E59" t="n">
-        <v>2.947876020777785e-19</v>
+        <v>0</v>
       </c>
       <c r="F59" t="n">
         <v>0</v>
       </c>
       <c r="G59" t="n">
-        <v>8.24259153293851e-17</v>
+        <v>1.094790084326183e-16</v>
       </c>
       <c r="H59" t="n">
         <v>0.2994236183221585</v>
       </c>
       <c r="I59" t="n">
-        <v>0</v>
+        <v>1.180763928472495e-18</v>
       </c>
       <c r="J59" t="n">
-        <v>0.2762720700494155</v>
+        <v>0.2762720700494157</v>
       </c>
       <c r="K59" t="n">
-        <v>0.1967988170077175</v>
+        <v>0.196798817007717</v>
       </c>
     </row>
     <row r="60">
@@ -3167,28 +3167,28 @@
         <v>0.1205444748112922</v>
       </c>
       <c r="D60" t="n">
-        <v>0.232220134587693</v>
+        <v>0.2322201345876931</v>
       </c>
       <c r="E60" t="n">
-        <v>0</v>
+        <v>8.185726402265558e-18</v>
       </c>
       <c r="F60" t="n">
-        <v>1.729447834419584e-18</v>
+        <v>1.192622389734055e-17</v>
       </c>
       <c r="G60" t="n">
-        <v>0</v>
+        <v>1.122149248522497e-16</v>
       </c>
       <c r="H60" t="n">
-        <v>0.3094602464242078</v>
+        <v>0.3094602464242082</v>
       </c>
       <c r="I60" t="n">
-        <v>4.785342015458158e-17</v>
+        <v>0</v>
       </c>
       <c r="J60" t="n">
-        <v>0.2695825193274731</v>
+        <v>0.269582519327473</v>
       </c>
       <c r="K60" t="n">
-        <v>0.1887370996606262</v>
+        <v>0.1887370996606256</v>
       </c>
     </row>
     <row r="61">
@@ -3208,22 +3208,22 @@
         <v>0</v>
       </c>
       <c r="F61" t="n">
-        <v>6.80845433949207e-18</v>
+        <v>0</v>
       </c>
       <c r="G61" t="n">
-        <v>5.314613964480223e-17</v>
+        <v>0</v>
       </c>
       <c r="H61" t="n">
-        <v>0.3194967225871695</v>
+        <v>0.3194967225871693</v>
       </c>
       <c r="I61" t="n">
-        <v>9.895973495374203e-18</v>
+        <v>0</v>
       </c>
       <c r="J61" t="n">
-        <v>0.262891693639939</v>
+        <v>0.2628916936399393</v>
       </c>
       <c r="K61" t="n">
-        <v>0.1806771845855214</v>
+        <v>0.1806771845855215</v>
       </c>
     </row>
     <row r="62">
@@ -3237,28 +3237,28 @@
         <v>0.1218770624767823</v>
       </c>
       <c r="D62" t="n">
-        <v>0.2416451303911126</v>
+        <v>0.2416451303911129</v>
       </c>
       <c r="E62" t="n">
-        <v>1.117760467911274e-17</v>
+        <v>0</v>
       </c>
       <c r="F62" t="n">
-        <v>4.020905650965934e-17</v>
+        <v>0</v>
       </c>
       <c r="G62" t="n">
-        <v>6.418032086415028e-17</v>
+        <v>0</v>
       </c>
       <c r="H62" t="n">
-        <v>0.3295355825265709</v>
+        <v>0.3295355825265711</v>
       </c>
       <c r="I62" t="n">
-        <v>0</v>
+        <v>1.908873449932291e-17</v>
       </c>
       <c r="J62" t="n">
-        <v>0.2562011212899727</v>
+        <v>0.2562011212899723</v>
       </c>
       <c r="K62" t="n">
-        <v>0.1726181657923438</v>
+        <v>0.1726181657923436</v>
       </c>
     </row>
     <row r="63">
@@ -3269,31 +3269,31 @@
         <v>0.1529389021925668</v>
       </c>
       <c r="C63" t="n">
-        <v>0.1225801543739193</v>
+        <v>0.1225801543739194</v>
       </c>
       <c r="D63" t="n">
         <v>0.246359721514181</v>
       </c>
       <c r="E63" t="n">
-        <v>3.402504379401495e-18</v>
+        <v>5.131325594466551e-18</v>
       </c>
       <c r="F63" t="n">
-        <v>4.669535921096329e-19</v>
+        <v>0</v>
       </c>
       <c r="G63" t="n">
-        <v>4.733327988276164e-17</v>
+        <v>0</v>
       </c>
       <c r="H63" t="n">
-        <v>0.3395720811859981</v>
+        <v>0.3395720811859984</v>
       </c>
       <c r="I63" t="n">
-        <v>0</v>
+        <v>2.403794801012979e-17</v>
       </c>
       <c r="J63" t="n">
-        <v>0.2495110522783279</v>
+        <v>0.2495110522783273</v>
       </c>
       <c r="K63" t="n">
-        <v>0.164557145021493</v>
+        <v>0.1645571450214933</v>
       </c>
     </row>
     <row r="64">
@@ -3301,34 +3301,34 @@
         <v>62</v>
       </c>
       <c r="B64" t="n">
-        <v>0.1538693522044823</v>
+        <v>0.1538693522044824</v>
       </c>
       <c r="C64" t="n">
         <v>0.1233072236751285</v>
       </c>
       <c r="D64" t="n">
-        <v>0.2510745966731365</v>
+        <v>0.2510745966731364</v>
       </c>
       <c r="E64" t="n">
-        <v>2.792576346834128e-18</v>
+        <v>0</v>
       </c>
       <c r="F64" t="n">
-        <v>0</v>
+        <v>2.112711928689039e-18</v>
       </c>
       <c r="G64" t="n">
-        <v>0</v>
+        <v>1.078484700091538e-17</v>
       </c>
       <c r="H64" t="n">
-        <v>0.3496077840250476</v>
+        <v>0.3496077840250478</v>
       </c>
       <c r="I64" t="n">
-        <v>0</v>
+        <v>1.951733317063359e-17</v>
       </c>
       <c r="J64" t="n">
-        <v>0.2428190215495199</v>
+        <v>0.2428190215495206</v>
       </c>
       <c r="K64" t="n">
-        <v>0.1564985977522961</v>
+        <v>0.1564985977522954</v>
       </c>
     </row>
     <row r="65">
@@ -3339,22 +3339,22 @@
         <v>0.1547998022163979</v>
       </c>
       <c r="C65" t="n">
-        <v>0.1240578488038154</v>
+        <v>0.1240578488038153</v>
       </c>
       <c r="D65" t="n">
-        <v>0.255789110154714</v>
+        <v>0.2557891101547138</v>
       </c>
       <c r="E65" t="n">
-        <v>0</v>
+        <v>8.040460251811446e-19</v>
       </c>
       <c r="F65" t="n">
-        <v>1.031344376976084e-19</v>
+        <v>1.67034897198548e-18</v>
       </c>
       <c r="G65" t="n">
-        <v>7.232287028992505e-18</v>
+        <v>2.40989343823321e-17</v>
       </c>
       <c r="H65" t="n">
-        <v>0.3596452927253833</v>
+        <v>0.3596452927253829</v>
       </c>
       <c r="I65" t="n">
         <v>0</v>
@@ -3363,7 +3363,7 @@
         <v>0.2361320351706779</v>
       </c>
       <c r="K65" t="n">
-        <v>0.1484335619492249</v>
+        <v>0.1484335619492255</v>
       </c>
     </row>
     <row r="66">
@@ -3371,34 +3371,34 @@
         <v>64</v>
       </c>
       <c r="B66" t="n">
-        <v>0.1557302522283134</v>
+        <v>0.1557302522283135</v>
       </c>
       <c r="C66" t="n">
         <v>0.1248316048321178</v>
       </c>
       <c r="D66" t="n">
-        <v>0.260503011984329</v>
+        <v>0.2605030119843286</v>
       </c>
       <c r="E66" t="n">
-        <v>0</v>
+        <v>2.430561042146215e-18</v>
       </c>
       <c r="F66" t="n">
-        <v>0</v>
+        <v>3.278652780584583e-17</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
       </c>
       <c r="H66" t="n">
-        <v>0.3696820513523676</v>
+        <v>0.3696820513523678</v>
       </c>
       <c r="I66" t="n">
-        <v>3.319357951842996e-17</v>
+        <v>2.393715108940653e-18</v>
       </c>
       <c r="J66" t="n">
-        <v>0.2294413567048988</v>
+        <v>0.2294413567048975</v>
       </c>
       <c r="K66" t="n">
-        <v>0.1403735799584047</v>
+        <v>0.140373579958406</v>
       </c>
     </row>
     <row r="67">
@@ -3412,28 +3412,28 @@
         <v>0.1256280643636656</v>
       </c>
       <c r="D67" t="n">
-        <v>0.2652167410065614</v>
+        <v>0.2652167410065616</v>
       </c>
       <c r="E67" t="n">
         <v>0</v>
       </c>
       <c r="F67" t="n">
-        <v>4.417115125613196e-17</v>
+        <v>2.268460111865423e-17</v>
       </c>
       <c r="G67" t="n">
-        <v>1.201582659517029e-18</v>
+        <v>7.915184078912535e-17</v>
       </c>
       <c r="H67" t="n">
-        <v>0.3797196581029111</v>
+        <v>0.3797196581029113</v>
       </c>
       <c r="I67" t="n">
         <v>0</v>
       </c>
       <c r="J67" t="n">
-        <v>0.2227530411466946</v>
+        <v>0.2227530411466948</v>
       </c>
       <c r="K67" t="n">
-        <v>0.1323105597438329</v>
+        <v>0.1323105597438322</v>
       </c>
     </row>
     <row r="68">
@@ -3441,34 +3441,34 @@
         <v>66</v>
       </c>
       <c r="B68" t="n">
-        <v>0.1575911522521446</v>
+        <v>0.1575911522521445</v>
       </c>
       <c r="C68" t="n">
         <v>0.1264467983854028</v>
       </c>
       <c r="D68" t="n">
-        <v>0.269930744073329</v>
+        <v>0.2699307440733291</v>
       </c>
       <c r="E68" t="n">
-        <v>4.260910115368682e-18</v>
+        <v>0</v>
       </c>
       <c r="F68" t="n">
-        <v>0</v>
+        <v>3.247524319772987e-18</v>
       </c>
       <c r="G68" t="n">
-        <v>3.33705062282933e-17</v>
+        <v>2.124019818534884e-17</v>
       </c>
       <c r="H68" t="n">
-        <v>0.3897559262617009</v>
+        <v>0.3897559262617005</v>
       </c>
       <c r="I68" t="n">
-        <v>3.62631228637168e-19</v>
+        <v>2.467406975351777e-17</v>
       </c>
       <c r="J68" t="n">
-        <v>0.2160609989471325</v>
+        <v>0.2160609989471322</v>
       </c>
       <c r="K68" t="n">
-        <v>0.1242523307178377</v>
+        <v>0.1242523307178381</v>
       </c>
     </row>
     <row r="69">
@@ -3482,28 +3482,28 @@
         <v>0.1272873770793497</v>
       </c>
       <c r="D69" t="n">
-        <v>0.2746448454493584</v>
+        <v>0.2746448454493583</v>
       </c>
       <c r="E69" t="n">
-        <v>0</v>
+        <v>7.407091365502043e-18</v>
       </c>
       <c r="F69" t="n">
-        <v>0</v>
+        <v>2.260349771395463e-17</v>
       </c>
       <c r="G69" t="n">
-        <v>4.805973150074228e-17</v>
+        <v>2.611656686269184e-17</v>
       </c>
       <c r="H69" t="n">
-        <v>0.3997927315598032</v>
+        <v>0.3997927315598027</v>
       </c>
       <c r="I69" t="n">
         <v>0</v>
       </c>
       <c r="J69" t="n">
-        <v>0.2093708886894985</v>
+        <v>0.2093708886894987</v>
       </c>
       <c r="K69" t="n">
-        <v>0.1161915343013399</v>
+        <v>0.1161915343013403</v>
       </c>
     </row>
     <row r="70">
@@ -3517,28 +3517,28 @@
         <v>0.1281493705849405</v>
       </c>
       <c r="D70" t="n">
-        <v>0.2793610445456643</v>
+        <v>0.2793610445456648</v>
       </c>
       <c r="E70" t="n">
-        <v>2.638475133723929e-18</v>
+        <v>0</v>
       </c>
       <c r="F70" t="n">
-        <v>1.456235013580053e-17</v>
+        <v>0</v>
       </c>
       <c r="G70" t="n">
-        <v>6.662230066924944e-17</v>
+        <v>3.218725199566341e-18</v>
       </c>
       <c r="H70" t="n">
-        <v>0.4098280013070008</v>
+        <v>0.4098280013070011</v>
       </c>
       <c r="I70" t="n">
         <v>0</v>
       </c>
       <c r="J70" t="n">
-        <v>0.2026802413602783</v>
+        <v>0.2026802413602779</v>
       </c>
       <c r="K70" t="n">
-        <v>0.1081307127870567</v>
+        <v>0.1081307127870563</v>
       </c>
     </row>
     <row r="71">
@@ -3552,28 +3552,28 @@
         <v>0.1290323497191879</v>
       </c>
       <c r="D71" t="n">
-        <v>0.2840720000039574</v>
+        <v>0.2840720000039575</v>
       </c>
       <c r="E71" t="n">
-        <v>7.512614829390322e-18</v>
+        <v>1.626303258728257e-18</v>
       </c>
       <c r="F71" t="n">
-        <v>0</v>
+        <v>1.263095530945613e-17</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
       </c>
       <c r="H71" t="n">
-        <v>0.4198670116785901</v>
+        <v>0.4198670116785896</v>
       </c>
       <c r="I71" t="n">
-        <v>5.830261552342879e-17</v>
+        <v>2.501796513010301e-17</v>
       </c>
       <c r="J71" t="n">
-        <v>0.1959906224020468</v>
+        <v>0.1959906224020469</v>
       </c>
       <c r="K71" t="n">
-        <v>0.1000703659154056</v>
+        <v>0.1000703659154061</v>
       </c>
     </row>
     <row r="72">
@@ -3587,28 +3587,28 @@
         <v>0.1299358866632284</v>
       </c>
       <c r="D72" t="n">
-        <v>0.288789441708875</v>
+        <v>0.2887894417088749</v>
       </c>
       <c r="E72" t="n">
-        <v>0</v>
+        <v>3.172985420414609e-18</v>
       </c>
       <c r="F72" t="n">
-        <v>1.129000150817619e-17</v>
+        <v>0</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
       </c>
       <c r="H72" t="n">
-        <v>0.4299021144999146</v>
+        <v>0.4299021144999143</v>
       </c>
       <c r="I72" t="n">
-        <v>2.653645650248509e-17</v>
+        <v>0</v>
       </c>
       <c r="J72" t="n">
-        <v>0.1893020432272291</v>
+        <v>0.1893020432272292</v>
       </c>
       <c r="K72" t="n">
-        <v>0.09200640056398132</v>
+        <v>0.0920064005639819</v>
       </c>
     </row>
     <row r="73">
@@ -3622,28 +3622,28 @@
         <v>0.1308595555810358</v>
       </c>
       <c r="D73" t="n">
-        <v>0.2935028833055866</v>
+        <v>0.2935028833055867</v>
       </c>
       <c r="E73" t="n">
-        <v>6.560652797164864e-19</v>
+        <v>0</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
       </c>
       <c r="G73" t="n">
-        <v>7.149753272312759e-18</v>
+        <v>0</v>
       </c>
       <c r="H73" t="n">
         <v>0.4399386598303607</v>
       </c>
       <c r="I73" t="n">
-        <v>0</v>
+        <v>2.108095599126503e-17</v>
       </c>
       <c r="J73" t="n">
         <v>0.1826097147697116</v>
       </c>
       <c r="K73" t="n">
-        <v>0.08394874209434104</v>
+        <v>0.08394874209434093</v>
       </c>
     </row>
     <row r="74">
@@ -3657,28 +3657,28 @@
         <v>0.131802933223146</v>
       </c>
       <c r="D74" t="n">
-        <v>0.2982135673994667</v>
+        <v>0.2982135673994669</v>
       </c>
       <c r="E74" t="n">
-        <v>2.174984426639665e-18</v>
+        <v>0</v>
       </c>
       <c r="F74" t="n">
-        <v>0</v>
+        <v>4.607859233063394e-17</v>
       </c>
       <c r="G74" t="n">
-        <v>1.140240050428875e-16</v>
+        <v>0</v>
       </c>
       <c r="H74" t="n">
-        <v>0.4499777397402257</v>
+        <v>0.4499777397402258</v>
       </c>
       <c r="I74" t="n">
-        <v>9.068382649415687e-18</v>
+        <v>5.204170427930421e-18</v>
       </c>
       <c r="J74" t="n">
         <v>0.1759197504661432</v>
       </c>
       <c r="K74" t="n">
-        <v>0.07588894239416444</v>
+        <v>0.07588894239416412</v>
       </c>
     </row>
     <row r="75">
@@ -3695,16 +3695,16 @@
         <v>0.3029273801136371</v>
       </c>
       <c r="E75" t="n">
-        <v>2.577821002115419e-17</v>
+        <v>0</v>
       </c>
       <c r="F75" t="n">
-        <v>4.904647737371336e-18</v>
+        <v>2.039655336988355e-17</v>
       </c>
       <c r="G75" t="n">
-        <v>1.07843862855837e-16</v>
+        <v>0</v>
       </c>
       <c r="H75" t="n">
-        <v>0.4600147103076733</v>
+        <v>0.4600147103076734</v>
       </c>
       <c r="I75" t="n">
         <v>0</v>
@@ -3713,7 +3713,7 @@
         <v>0.1692295662018989</v>
       </c>
       <c r="K75" t="n">
-        <v>0.06782834337679072</v>
+        <v>0.06782834337679093</v>
       </c>
     </row>
     <row r="76">
@@ -3724,31 +3724,31 @@
         <v>0.165034752347469</v>
       </c>
       <c r="C76" t="n">
-        <v>0.1337471378091763</v>
+        <v>0.1337471378091762</v>
       </c>
       <c r="D76" t="n">
-        <v>0.3076410495482266</v>
+        <v>0.3076410495482267</v>
       </c>
       <c r="E76" t="n">
-        <v>0</v>
+        <v>4.891403512156771e-18</v>
       </c>
       <c r="F76" t="n">
-        <v>2.033431404521256e-17</v>
+        <v>0</v>
       </c>
       <c r="G76" t="n">
-        <v>0</v>
+        <v>8.430095407548424e-17</v>
       </c>
       <c r="H76" t="n">
-        <v>0.4700519052671646</v>
+        <v>0.4700519052671648</v>
       </c>
       <c r="I76" t="n">
         <v>0</v>
       </c>
       <c r="J76" t="n">
-        <v>0.1625398026195303</v>
+        <v>0.1625398026195298</v>
       </c>
       <c r="K76" t="n">
-        <v>0.05976724256507886</v>
+        <v>0.05976724256507852</v>
       </c>
     </row>
     <row r="77">
@@ -3759,31 +3759,31 @@
         <v>0.1659652023593846</v>
       </c>
       <c r="C77" t="n">
-        <v>0.1347471358450272</v>
+        <v>0.1347471358450273</v>
       </c>
       <c r="D77" t="n">
-        <v>0.3123551853934004</v>
+        <v>0.3123551853934005</v>
       </c>
       <c r="E77" t="n">
         <v>0</v>
       </c>
       <c r="F77" t="n">
-        <v>1.444556074080157e-17</v>
+        <v>0</v>
       </c>
       <c r="G77" t="n">
-        <v>3.936409715008779e-17</v>
+        <v>1.589454149149142e-16</v>
       </c>
       <c r="H77" t="n">
-        <v>0.4800884672864853</v>
+        <v>0.4800884672864855</v>
       </c>
       <c r="I77" t="n">
-        <v>0</v>
+        <v>1.256859250871453e-17</v>
       </c>
       <c r="J77" t="n">
-        <v>0.155848982928469</v>
+        <v>0.1558489829284689</v>
       </c>
       <c r="K77" t="n">
-        <v>0.05170736439164521</v>
+        <v>0.05170736439164506</v>
       </c>
     </row>
     <row r="78">
@@ -3791,19 +3791,19 @@
         <v>76</v>
       </c>
       <c r="B78" t="n">
-        <v>0.1668956523713001</v>
+        <v>0.1668956523713002</v>
       </c>
       <c r="C78" t="n">
         <v>0.1357651856712508</v>
       </c>
       <c r="D78" t="n">
-        <v>0.3170683131058449</v>
+        <v>0.3170683131058452</v>
       </c>
       <c r="E78" t="n">
         <v>0</v>
       </c>
       <c r="F78" t="n">
-        <v>0</v>
+        <v>8.348356728138384e-18</v>
       </c>
       <c r="G78" t="n">
         <v>0</v>
@@ -3815,10 +3815,10 @@
         <v>0</v>
       </c>
       <c r="J78" t="n">
-        <v>0.1491602100272193</v>
+        <v>0.1491602100272195</v>
       </c>
       <c r="K78" t="n">
-        <v>0.04364515291570071</v>
+        <v>0.04364515291570032</v>
       </c>
     </row>
     <row r="79">
@@ -3826,34 +3826,34 @@
         <v>77</v>
       </c>
       <c r="B79" t="n">
-        <v>0.1678261023832157</v>
+        <v>0.1678261023832156</v>
       </c>
       <c r="C79" t="n">
         <v>0.1368008842724182</v>
       </c>
       <c r="D79" t="n">
-        <v>0.3217825291721423</v>
+        <v>0.3217825291721422</v>
       </c>
       <c r="E79" t="n">
-        <v>0</v>
+        <v>3.310840032580246e-18</v>
       </c>
       <c r="F79" t="n">
-        <v>4.367545354571948e-18</v>
+        <v>0</v>
       </c>
       <c r="G79" t="n">
-        <v>0</v>
+        <v>2.08456290626941e-16</v>
       </c>
       <c r="H79" t="n">
-        <v>0.5001627441423804</v>
+        <v>0.5001627441423803</v>
       </c>
       <c r="I79" t="n">
-        <v>0</v>
+        <v>4.040347158403013e-17</v>
       </c>
       <c r="J79" t="n">
-        <v>0.1424691027704053</v>
+        <v>0.1424691027704048</v>
       </c>
       <c r="K79" t="n">
-        <v>0.03558562391507227</v>
+        <v>0.03558562391507235</v>
       </c>
     </row>
     <row r="80">
@@ -3861,34 +3861,34 @@
         <v>78</v>
       </c>
       <c r="B80" t="n">
-        <v>0.1687565523951313</v>
+        <v>0.1687565523951312</v>
       </c>
       <c r="C80" t="n">
         <v>0.1378538338648085</v>
       </c>
       <c r="D80" t="n">
-        <v>0.3264948035544621</v>
+        <v>0.326494803554462</v>
       </c>
       <c r="E80" t="n">
-        <v>3.729403678364401e-18</v>
+        <v>8.890457814381136e-18</v>
       </c>
       <c r="F80" t="n">
-        <v>2.883701709109285e-17</v>
+        <v>0</v>
       </c>
       <c r="G80" t="n">
         <v>0</v>
       </c>
       <c r="H80" t="n">
-        <v>0.5102018391649796</v>
+        <v>0.5102018391649795</v>
       </c>
       <c r="I80" t="n">
-        <v>0</v>
+        <v>1.658829323902822e-17</v>
       </c>
       <c r="J80" t="n">
-        <v>0.1357825202669001</v>
+        <v>0.1357825202668996</v>
       </c>
       <c r="K80" t="n">
-        <v>0.02752083701365842</v>
+        <v>0.02752083701365886</v>
       </c>
     </row>
     <row r="81">
@@ -3902,28 +3902,28 @@
         <v>0.1389236421914008</v>
       </c>
       <c r="D81" t="n">
-        <v>0.3312086820211195</v>
+        <v>0.3312086820211199</v>
       </c>
       <c r="E81" t="n">
-        <v>0</v>
+        <v>5.041540102057596e-18</v>
       </c>
       <c r="F81" t="n">
-        <v>1.771758387113645e-17</v>
+        <v>2.423191855505102e-17</v>
       </c>
       <c r="G81" t="n">
-        <v>9.879040791650232e-17</v>
+        <v>0</v>
       </c>
       <c r="H81" t="n">
-        <v>0.5202387154544178</v>
+        <v>0.5202387154544182</v>
       </c>
       <c r="I81" t="n">
-        <v>6.340359850155975e-19</v>
+        <v>0</v>
       </c>
       <c r="J81" t="n">
-        <v>0.1290921708944299</v>
+        <v>0.1290921708944295</v>
       </c>
       <c r="K81" t="n">
-        <v>0.01946043163003287</v>
+        <v>0.01946043163003248</v>
       </c>
     </row>
     <row r="82">
@@ -3940,13 +3940,13 @@
         <v>0.3359225658354925</v>
       </c>
       <c r="E82" t="n">
-        <v>0</v>
+        <v>2.168404344971009e-19</v>
       </c>
       <c r="F82" t="n">
-        <v>4.59431642826374e-17</v>
+        <v>5.664956351236761e-17</v>
       </c>
       <c r="G82" t="n">
-        <v>0</v>
+        <v>5.139118297581291e-17</v>
       </c>
       <c r="H82" t="n">
         <v>0.5302755872894397</v>
@@ -3955,10 +3955,10 @@
         <v>0</v>
       </c>
       <c r="J82" t="n">
-        <v>0.1224018184182415</v>
+        <v>0.1224018184182411</v>
       </c>
       <c r="K82" t="n">
-        <v>0.01140002845682636</v>
+        <v>0.01140002845682662</v>
       </c>
     </row>
     <row r="83">
@@ -3969,31 +3969,31 @@
         <v>0.1715479024308779</v>
       </c>
       <c r="C83" t="n">
-        <v>0.1411122952950665</v>
+        <v>0.1411122952950666</v>
       </c>
       <c r="D83" t="n">
-        <v>0.3406363853510341</v>
+        <v>0.3406363853510344</v>
       </c>
       <c r="E83" t="n">
-        <v>6.58209922598095e-18</v>
+        <v>1.187201378871627e-17</v>
       </c>
       <c r="F83" t="n">
         <v>0</v>
       </c>
       <c r="G83" t="n">
-        <v>0</v>
+        <v>3.96113263717579e-16</v>
       </c>
       <c r="H83" t="n">
-        <v>0.5403125519777476</v>
+        <v>0.5403125519777481</v>
       </c>
       <c r="I83" t="n">
-        <v>2.792473476636997e-17</v>
+        <v>7.643625316022806e-18</v>
       </c>
       <c r="J83" t="n">
-        <v>0.1157116295193559</v>
+        <v>0.1157116295193551</v>
       </c>
       <c r="K83" t="n">
-        <v>0.003339433151862461</v>
+        <v>0.003339433151862015</v>
       </c>
     </row>
     <row r="84">
@@ -4001,31 +4001,31 @@
         <v>82</v>
       </c>
       <c r="B84" t="n">
-        <v>0.1724783524427938</v>
+        <v>0.1724783524427935</v>
       </c>
       <c r="C84" t="n">
-        <v>0.1422315538563064</v>
+        <v>0.1422315538563063</v>
       </c>
       <c r="D84" t="n">
-        <v>0.344281651905487</v>
+        <v>0.3442816519054865</v>
       </c>
       <c r="E84" t="n">
         <v>0</v>
       </c>
       <c r="F84" t="n">
-        <v>3.418014418713872e-17</v>
+        <v>1.247141363830304e-18</v>
       </c>
       <c r="G84" t="n">
         <v>0</v>
       </c>
       <c r="H84" t="n">
-        <v>0.5500141526397733</v>
+        <v>0.5500141526397732</v>
       </c>
       <c r="I84" t="n">
         <v>0</v>
       </c>
       <c r="J84" t="n">
-        <v>0.1057041954547423</v>
+        <v>0.1057041954547414</v>
       </c>
       <c r="K84" t="n">
         <v>0</v>
@@ -4036,34 +4036,34 @@
         <v>83</v>
       </c>
       <c r="B85" t="n">
-        <v>0.1734088024547089</v>
+        <v>0.173408802454709</v>
       </c>
       <c r="C85" t="n">
         <v>0.1433723312516441</v>
       </c>
       <c r="D85" t="n">
-        <v>0.3471667436970063</v>
+        <v>0.3471667436970067</v>
       </c>
       <c r="E85" t="n">
-        <v>1.15219509801284e-18</v>
+        <v>4.532957905114619e-18</v>
       </c>
       <c r="F85" t="n">
-        <v>1.029946227891073e-17</v>
+        <v>0</v>
       </c>
       <c r="G85" t="n">
-        <v>0</v>
+        <v>5.145070490977803e-17</v>
       </c>
       <c r="H85" t="n">
-        <v>0.5594817374674217</v>
+        <v>0.5594817374674215</v>
       </c>
       <c r="I85" t="n">
-        <v>0</v>
+        <v>3.482186394177172e-17</v>
       </c>
       <c r="J85" t="n">
-        <v>0.09335151883557206</v>
+        <v>0.09335151883557199</v>
       </c>
       <c r="K85" t="n">
-        <v>6.863381402401034e-17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="86">
@@ -4071,34 +4071,34 @@
         <v>84</v>
       </c>
       <c r="B86" t="n">
-        <v>0.1743392524666246</v>
+        <v>0.1743392524666245</v>
       </c>
       <c r="C86" t="n">
-        <v>0.1445346957377134</v>
+        <v>0.1445346957377133</v>
       </c>
       <c r="D86" t="n">
-        <v>0.3500518354885268</v>
+        <v>0.3500518354885271</v>
       </c>
       <c r="E86" t="n">
-        <v>0</v>
+        <v>2.897520293252017e-18</v>
       </c>
       <c r="F86" t="n">
-        <v>4.490989119128606e-17</v>
+        <v>2.696379737811254e-17</v>
       </c>
       <c r="G86" t="n">
         <v>0</v>
       </c>
       <c r="H86" t="n">
-        <v>0.568949322295071</v>
+        <v>0.5689493222950708</v>
       </c>
       <c r="I86" t="n">
         <v>0</v>
       </c>
       <c r="J86" t="n">
-        <v>0.0809988422164023</v>
+        <v>0.08099884221640202</v>
       </c>
       <c r="K86" t="n">
-        <v>1.603376686148855e-16</v>
+        <v>2.506752119864016e-17</v>
       </c>
     </row>
     <row r="87">
@@ -4112,28 +4112,28 @@
         <v>0.1457181307276686</v>
       </c>
       <c r="D87" t="n">
-        <v>0.3529369272800465</v>
+        <v>0.3529369272800468</v>
       </c>
       <c r="E87" t="n">
         <v>0</v>
       </c>
       <c r="F87" t="n">
-        <v>7.64893096791958e-18</v>
+        <v>0</v>
       </c>
       <c r="G87" t="n">
-        <v>3.343904641159823e-17</v>
+        <v>0</v>
       </c>
       <c r="H87" t="n">
-        <v>0.5784169071227202</v>
+        <v>0.5784169071227199</v>
       </c>
       <c r="I87" t="n">
-        <v>2.752167748574527e-18</v>
+        <v>4.071860936916861e-17</v>
       </c>
       <c r="J87" t="n">
-        <v>0.06864616559723323</v>
+        <v>0.06864616559723359</v>
       </c>
       <c r="K87" t="n">
-        <v>1.270343255459157e-16</v>
+        <v>3.762550204082207e-17</v>
       </c>
     </row>
     <row r="88">
@@ -4147,28 +4147,28 @@
         <v>0.146922127063451</v>
       </c>
       <c r="D88" t="n">
-        <v>0.3558220190715671</v>
+        <v>0.3558220190715681</v>
       </c>
       <c r="E88" t="n">
         <v>0</v>
       </c>
       <c r="F88" t="n">
-        <v>9.138738272570216e-18</v>
+        <v>1.359951295404682e-17</v>
       </c>
       <c r="G88" t="n">
         <v>0</v>
       </c>
       <c r="H88" t="n">
-        <v>0.5878844919503688</v>
+        <v>0.587884491950368</v>
       </c>
       <c r="I88" t="n">
-        <v>2.233976003309086e-18</v>
+        <v>1.395362045191525e-18</v>
       </c>
       <c r="J88" t="n">
-        <v>0.05629348897806399</v>
+        <v>0.05629348897806389</v>
       </c>
       <c r="K88" t="n">
-        <v>5.169078950216265e-17</v>
+        <v>5.331318794373618e-17</v>
       </c>
     </row>
     <row r="89">
@@ -4182,28 +4182,28 @@
         <v>0.1481461834346134</v>
       </c>
       <c r="D89" t="n">
-        <v>0.3587071108630878</v>
+        <v>0.3587071108630879</v>
       </c>
       <c r="E89" t="n">
-        <v>6.3768663520532e-18</v>
+        <v>5.925050526720061e-18</v>
       </c>
       <c r="F89" t="n">
-        <v>2.049075068773434e-17</v>
+        <v>0</v>
       </c>
       <c r="G89" t="n">
-        <v>0</v>
+        <v>2.422202547867661e-16</v>
       </c>
       <c r="H89" t="n">
-        <v>0.5973520767780178</v>
+        <v>0.5973520767780177</v>
       </c>
       <c r="I89" t="n">
         <v>0</v>
       </c>
       <c r="J89" t="n">
-        <v>0.0439408123588943</v>
+        <v>0.04394081235889439</v>
       </c>
       <c r="K89" t="n">
-        <v>8.828544324853152e-17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="90">
@@ -4214,31 +4214,31 @@
         <v>0.1780610525142868</v>
       </c>
       <c r="C90" t="n">
-        <v>0.149389806743786</v>
+        <v>0.1493898067437861</v>
       </c>
       <c r="D90" t="n">
-        <v>0.3615922026546084</v>
+        <v>0.3615922026546079</v>
       </c>
       <c r="E90" t="n">
         <v>0</v>
       </c>
       <c r="F90" t="n">
-        <v>7.947017998939817e-18</v>
+        <v>0</v>
       </c>
       <c r="G90" t="n">
         <v>0</v>
       </c>
       <c r="H90" t="n">
-        <v>0.606819661605666</v>
+        <v>0.6068196616056667</v>
       </c>
       <c r="I90" t="n">
-        <v>0</v>
+        <v>1.036469142266536e-17</v>
       </c>
       <c r="J90" t="n">
-        <v>0.03158813573972561</v>
+        <v>0.03158813573972553</v>
       </c>
       <c r="K90" t="n">
-        <v>9.123517202817045e-17</v>
+        <v>3.639578810372109e-17</v>
       </c>
     </row>
     <row r="91">
@@ -4252,13 +4252,13 @@
         <v>0.1506525124216644</v>
       </c>
       <c r="D91" t="n">
-        <v>0.3644772944461282</v>
+        <v>0.3644772944461281</v>
       </c>
       <c r="E91" t="n">
-        <v>9.044046298930614e-18</v>
+        <v>3.193466569295272e-18</v>
       </c>
       <c r="F91" t="n">
-        <v>1.259890843555951e-17</v>
+        <v>1.974461576171706e-17</v>
       </c>
       <c r="G91" t="n">
         <v>0</v>
@@ -4267,13 +4267,13 @@
         <v>0.6162872464333153</v>
       </c>
       <c r="I91" t="n">
-        <v>1.745726442015692e-18</v>
+        <v>7.873326467738941e-18</v>
       </c>
       <c r="J91" t="n">
-        <v>0.01923545912055639</v>
+        <v>0.01923545912055648</v>
       </c>
       <c r="K91" t="n">
-        <v>1.230212202088242e-16</v>
+        <v>7.032309278471697e-17</v>
       </c>
     </row>
     <row r="92">
@@ -4287,28 +4287,28 @@
         <v>0.1519338246944507</v>
       </c>
       <c r="D92" t="n">
-        <v>0.3673623862376483</v>
+        <v>0.367362386237648</v>
       </c>
       <c r="E92" t="n">
-        <v>7.53634588478355e-19</v>
+        <v>0</v>
       </c>
       <c r="F92" t="n">
-        <v>0</v>
+        <v>4.026427235001806e-18</v>
       </c>
       <c r="G92" t="n">
-        <v>0</v>
+        <v>1.137529897724012e-17</v>
       </c>
       <c r="H92" t="n">
-        <v>0.6257548312609642</v>
+        <v>0.6257548312609644</v>
       </c>
       <c r="I92" t="n">
-        <v>1.143462602340564e-17</v>
+        <v>0</v>
       </c>
       <c r="J92" t="n">
-        <v>0.006882782501387561</v>
+        <v>0.006882782501387678</v>
       </c>
       <c r="K92" t="n">
-        <v>0</v>
+        <v>4.03062224388885e-17</v>
       </c>
     </row>
     <row r="93">
@@ -4325,10 +4325,10 @@
         <v>0.3496181107734166</v>
       </c>
       <c r="E93" t="n">
-        <v>3.191891195797325e-16</v>
+        <v>2.775557561562891e-17</v>
       </c>
       <c r="F93" t="n">
-        <v>0</v>
+        <v>1.52655665885959e-16</v>
       </c>
       <c r="G93" t="n">
         <v>0</v>
@@ -4340,7 +4340,7 @@
         <v>0</v>
       </c>
       <c r="J93" t="n">
-        <v>0</v>
+        <v>5.551115123125783e-17</v>
       </c>
       <c r="K93" t="n">
         <v>0</v>
@@ -4357,22 +4357,22 @@
         <v>0.1549680724784727</v>
       </c>
       <c r="D94" t="n">
-        <v>0.3059158469267394</v>
+        <v>0.3059158469267389</v>
       </c>
       <c r="E94" t="n">
-        <v>5.551115123125783e-17</v>
+        <v>0</v>
       </c>
       <c r="F94" t="n">
-        <v>1.110223024625157e-16</v>
+        <v>1.387778780781446e-16</v>
       </c>
       <c r="G94" t="n">
         <v>0</v>
       </c>
       <c r="H94" t="n">
-        <v>0.6940841530732609</v>
+        <v>0.6940841530732612</v>
       </c>
       <c r="I94" t="n">
-        <v>0</v>
+        <v>3.05311331771918e-16</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -4386,31 +4386,31 @@
         <v>93</v>
       </c>
       <c r="B95" t="n">
-        <v>0.1827133025738648</v>
+        <v>0.1827133025738646</v>
       </c>
       <c r="C95" t="n">
-        <v>0.1570688888171535</v>
+        <v>0.1570688888171533</v>
       </c>
       <c r="D95" t="n">
-        <v>0.262213583080063</v>
+        <v>0.2622135830800638</v>
       </c>
       <c r="E95" t="n">
-        <v>7.077671781985373e-16</v>
+        <v>1.249000902703301e-16</v>
       </c>
       <c r="F95" t="n">
-        <v>1.942890293094024e-16</v>
+        <v>0</v>
       </c>
       <c r="G95" t="n">
         <v>0</v>
       </c>
       <c r="H95" t="n">
-        <v>0.7377864169199376</v>
+        <v>0.7377864169199367</v>
       </c>
       <c r="I95" t="n">
         <v>0</v>
       </c>
       <c r="J95" t="n">
-        <v>0</v>
+        <v>8.326672684688674e-17</v>
       </c>
       <c r="K95" t="n">
         <v>0</v>
@@ -4421,34 +4421,34 @@
         <v>94</v>
       </c>
       <c r="B96" t="n">
-        <v>0.1836437525857802</v>
+        <v>0.1836437525857801</v>
       </c>
       <c r="C96" t="n">
         <v>0.159559427217667</v>
       </c>
       <c r="D96" t="n">
-        <v>0.2185113192333858</v>
+        <v>0.2185113192333857</v>
       </c>
       <c r="E96" t="n">
+        <v>0</v>
+      </c>
+      <c r="F96" t="n">
+        <v>6.938893903907228e-17</v>
+      </c>
+      <c r="G96" t="n">
         <v>1.249000902703301e-16</v>
       </c>
-      <c r="F96" t="n">
-        <v>0</v>
-      </c>
-      <c r="G96" t="n">
-        <v>1.52655665885959e-16</v>
-      </c>
       <c r="H96" t="n">
-        <v>0.7814886807666142</v>
+        <v>0.7814886807666143</v>
       </c>
       <c r="I96" t="n">
-        <v>0</v>
+        <v>1.665334536937735e-16</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
       </c>
       <c r="K96" t="n">
-        <v>3.608224830031759e-16</v>
+        <v>2.775557561562891e-16</v>
       </c>
     </row>
     <row r="97">
@@ -4456,34 +4456,34 @@
         <v>95</v>
       </c>
       <c r="B97" t="n">
-        <v>0.1845742025976958</v>
+        <v>0.1845742025976957</v>
       </c>
       <c r="C97" t="n">
-        <v>0.1624217609405134</v>
+        <v>0.1624217609405133</v>
       </c>
       <c r="D97" t="n">
-        <v>0.1748090553867105</v>
+        <v>0.1748090553867091</v>
       </c>
       <c r="E97" t="n">
-        <v>3.747002708109903e-16</v>
+        <v>0</v>
       </c>
       <c r="F97" t="n">
         <v>0</v>
       </c>
       <c r="G97" t="n">
-        <v>0</v>
+        <v>9.71445146547012e-17</v>
       </c>
       <c r="H97" t="n">
-        <v>0.8251909446132905</v>
+        <v>0.8251909446132909</v>
       </c>
       <c r="I97" t="n">
-        <v>4.163336342344337e-17</v>
+        <v>0</v>
       </c>
       <c r="J97" t="n">
-        <v>0</v>
+        <v>6.938893903907228e-17</v>
       </c>
       <c r="K97" t="n">
-        <v>0</v>
+        <v>2.220446049250313e-16</v>
       </c>
     </row>
     <row r="98">
@@ -4491,34 +4491,34 @@
         <v>96</v>
       </c>
       <c r="B98" t="n">
-        <v>0.1855046526096114</v>
+        <v>0.1855046526096113</v>
       </c>
       <c r="C98" t="n">
-        <v>0.1656366163419708</v>
+        <v>0.1656366163419706</v>
       </c>
       <c r="D98" t="n">
-        <v>0.1311067915400316</v>
+        <v>0.1311067915400318</v>
       </c>
       <c r="E98" t="n">
-        <v>6.38378239159465e-16</v>
+        <v>4.163336342344337e-16</v>
       </c>
       <c r="F98" t="n">
-        <v>4.996003610813204e-16</v>
+        <v>0</v>
       </c>
       <c r="G98" t="n">
         <v>0</v>
       </c>
       <c r="H98" t="n">
-        <v>0.868893208459969</v>
+        <v>0.8688932084599684</v>
       </c>
       <c r="I98" t="n">
         <v>0</v>
       </c>
       <c r="J98" t="n">
-        <v>0</v>
+        <v>1.387778780781446e-17</v>
       </c>
       <c r="K98" t="n">
-        <v>0</v>
+        <v>6.938893903907228e-17</v>
       </c>
     </row>
     <row r="99">
@@ -4526,31 +4526,31 @@
         <v>97</v>
       </c>
       <c r="B99" t="n">
-        <v>0.1864351026215272</v>
+        <v>0.186435102621527</v>
       </c>
       <c r="C99" t="n">
         <v>0.1691838986210855</v>
       </c>
       <c r="D99" t="n">
-        <v>0.08740452769335638</v>
+        <v>0.08740452769335397</v>
       </c>
       <c r="E99" t="n">
-        <v>1.137978600240785e-15</v>
+        <v>6.800116025829084e-16</v>
       </c>
       <c r="F99" t="n">
-        <v>0</v>
+        <v>4.85722573273506e-16</v>
       </c>
       <c r="G99" t="n">
         <v>0</v>
       </c>
       <c r="H99" t="n">
-        <v>0.9125954723066453</v>
+        <v>0.9125954723066466</v>
       </c>
       <c r="I99" t="n">
         <v>0</v>
       </c>
       <c r="J99" t="n">
-        <v>3.747002708109903e-16</v>
+        <v>0</v>
       </c>
       <c r="K99" t="n">
         <v>0</v>
@@ -4561,25 +4561,25 @@
         <v>98</v>
       </c>
       <c r="B100" t="n">
-        <v>0.1873655526334424</v>
+        <v>0.1873655526334425</v>
       </c>
       <c r="C100" t="n">
-        <v>0.173043165323727</v>
+        <v>0.1730431653237273</v>
       </c>
       <c r="D100" t="n">
-        <v>0.04370226384667768</v>
+        <v>0.04370226384667629</v>
       </c>
       <c r="E100" t="n">
-        <v>8.326672684688674e-17</v>
+        <v>8.187894806610529e-16</v>
       </c>
       <c r="F100" t="n">
-        <v>0</v>
+        <v>3.469446951953614e-16</v>
       </c>
       <c r="G100" t="n">
-        <v>9.71445146547012e-17</v>
+        <v>0</v>
       </c>
       <c r="H100" t="n">
-        <v>0.9562977361533227</v>
+        <v>0.956297736153324</v>
       </c>
       <c r="I100" t="n">
         <v>0</v>
@@ -4588,7 +4588,7 @@
         <v>0</v>
       </c>
       <c r="K100" t="n">
-        <v>2.081668171172169e-16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="101">
@@ -4596,31 +4596,31 @@
         <v>99</v>
       </c>
       <c r="B101" t="n">
-        <v>0.188296002645358</v>
+        <v>0.1882960026453581</v>
       </c>
       <c r="C101" t="n">
-        <v>0.1771940326621987</v>
+        <v>0.1771940326621989</v>
       </c>
       <c r="D101" t="n">
-        <v>1.734723475976807e-15</v>
+        <v>1.637578961322106e-15</v>
       </c>
       <c r="E101" t="n">
-        <v>1.387778780781446e-17</v>
+        <v>3.191891195797325e-16</v>
       </c>
       <c r="F101" t="n">
         <v>0</v>
       </c>
       <c r="G101" t="n">
-        <v>0</v>
+        <v>6.938893903907228e-17</v>
       </c>
       <c r="H101" t="n">
-        <v>0.9999999999999989</v>
+        <v>0.9999999999999991</v>
       </c>
       <c r="I101" t="n">
         <v>0</v>
       </c>
       <c r="J101" t="n">
-        <v>4.024558464266192e-16</v>
+        <v>6.661338147750939e-16</v>
       </c>
       <c r="K101" t="n">
         <v>0</v>
@@ -5321,13 +5321,13 @@
         <v>0.6154051621353303</v>
       </c>
       <c r="E2" t="n">
-        <v>0.7080158486523555</v>
+        <v>0.7080158486523553</v>
       </c>
       <c r="F2" t="n">
         <v>0.4457140877612871</v>
       </c>
       <c r="G2" t="n">
-        <v>0.4957871609401717</v>
+        <v>0.4957871609401718</v>
       </c>
       <c r="H2" t="n">
         <v>0.2875761766931065</v>
@@ -5352,19 +5352,19 @@
         <v>0.7019845897229843</v>
       </c>
       <c r="E3" t="n">
-        <v>0.6727182928307738</v>
+        <v>0.6727182928307739</v>
       </c>
       <c r="F3" t="n">
-        <v>0.4479860119557348</v>
+        <v>0.447986011955735</v>
       </c>
       <c r="G3" t="n">
         <v>0.4179338773472103</v>
       </c>
       <c r="H3" t="n">
-        <v>0.2154842554349414</v>
+        <v>0.2154842554349415</v>
       </c>
       <c r="I3" t="n">
-        <v>0.4611928159408281</v>
+        <v>0.4611928159408279</v>
       </c>
     </row>
     <row r="4">
@@ -5386,7 +5386,7 @@
         <v>0.8703787734388615</v>
       </c>
       <c r="F4" t="n">
-        <v>0.6415182470774795</v>
+        <v>0.6415182470774797</v>
       </c>
       <c r="G4" t="n">
         <v>0.5602009897339925</v>
@@ -5395,7 +5395,7 @@
         <v>0.2990536675378052</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6304140854381329</v>
+        <v>0.630414085438133</v>
       </c>
     </row>
     <row r="5">
@@ -5405,10 +5405,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.7080158486523555</v>
+        <v>0.7080158486523553</v>
       </c>
       <c r="C5" t="n">
-        <v>0.6727182928307738</v>
+        <v>0.6727182928307739</v>
       </c>
       <c r="D5" t="n">
         <v>0.8703787734388615</v>
@@ -5417,16 +5417,16 @@
         <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7451471429847806</v>
+        <v>0.7451471429847808</v>
       </c>
       <c r="G5" t="n">
         <v>0.6592595738247619</v>
       </c>
       <c r="H5" t="n">
-        <v>0.4107400072088258</v>
+        <v>0.4107400072088257</v>
       </c>
       <c r="I5" t="n">
-        <v>0.6689423984404478</v>
+        <v>0.6689423984404477</v>
       </c>
     </row>
     <row r="6">
@@ -5439,13 +5439,13 @@
         <v>0.4457140877612871</v>
       </c>
       <c r="C6" t="n">
-        <v>0.4479860119557348</v>
+        <v>0.447986011955735</v>
       </c>
       <c r="D6" t="n">
-        <v>0.6415182470774795</v>
+        <v>0.6415182470774797</v>
       </c>
       <c r="E6" t="n">
-        <v>0.7451471429847806</v>
+        <v>0.7451471429847808</v>
       </c>
       <c r="F6" t="n">
         <v>1</v>
@@ -5454,7 +5454,7 @@
         <v>0.5265685538144041</v>
       </c>
       <c r="H6" t="n">
-        <v>0.3306651094032382</v>
+        <v>0.3306651094032383</v>
       </c>
       <c r="I6" t="n">
         <v>0.5531937350398379</v>
@@ -5467,7 +5467,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.4957871609401717</v>
+        <v>0.4957871609401718</v>
       </c>
       <c r="C7" t="n">
         <v>0.4179338773472103</v>
@@ -5488,7 +5488,7 @@
         <v>0.6255080489684137</v>
       </c>
       <c r="I7" t="n">
-        <v>0.6850436303922661</v>
+        <v>0.6850436303922663</v>
       </c>
     </row>
     <row r="8">
@@ -5501,16 +5501,16 @@
         <v>0.2875761766931065</v>
       </c>
       <c r="C8" t="n">
-        <v>0.2154842554349414</v>
+        <v>0.2154842554349415</v>
       </c>
       <c r="D8" t="n">
         <v>0.2990536675378052</v>
       </c>
       <c r="E8" t="n">
-        <v>0.4107400072088258</v>
+        <v>0.4107400072088257</v>
       </c>
       <c r="F8" t="n">
-        <v>0.3306651094032382</v>
+        <v>0.3306651094032383</v>
       </c>
       <c r="G8" t="n">
         <v>0.6255080489684137</v>
@@ -5519,7 +5519,7 @@
         <v>1</v>
       </c>
       <c r="I8" t="n">
-        <v>0.4104610785140765</v>
+        <v>0.4104610785140766</v>
       </c>
     </row>
     <row r="9">
@@ -5532,22 +5532,22 @@
         <v>0.5204386167756581</v>
       </c>
       <c r="C9" t="n">
-        <v>0.4611928159408281</v>
+        <v>0.4611928159408279</v>
       </c>
       <c r="D9" t="n">
-        <v>0.6304140854381329</v>
+        <v>0.630414085438133</v>
       </c>
       <c r="E9" t="n">
-        <v>0.6689423984404478</v>
+        <v>0.6689423984404477</v>
       </c>
       <c r="F9" t="n">
         <v>0.5531937350398379</v>
       </c>
       <c r="G9" t="n">
-        <v>0.6850436303922661</v>
+        <v>0.6850436303922663</v>
       </c>
       <c r="H9" t="n">
-        <v>0.4104610785140765</v>
+        <v>0.4104610785140766</v>
       </c>
       <c r="I9" t="n">
         <v>1</v>
@@ -5604,13 +5604,13 @@
         <v>0.4902260525509582</v>
       </c>
       <c r="C2" t="n">
-        <v>0.5007454006413341</v>
+        <v>0.500745400641334</v>
       </c>
       <c r="D2" t="n">
         <v>0.4609393448218127</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.0398060558195214</v>
+        <v>-0.03980605581952129</v>
       </c>
     </row>
     <row r="3">
@@ -5639,7 +5639,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.7080158486523555</v>
+        <v>0.7080158486523553</v>
       </c>
       <c r="C4" t="n">
         <v>0.7614833758022684</v>
@@ -5677,16 +5677,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.4957871609401717</v>
+        <v>0.4957871609401718</v>
       </c>
       <c r="C6" t="n">
-        <v>0.5187401319918179</v>
+        <v>0.518740131991818</v>
       </c>
       <c r="D6" t="n">
-        <v>0.4120295869101725</v>
+        <v>0.4120295869101724</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.1067105450816454</v>
+        <v>-0.1067105450816456</v>
       </c>
     </row>
     <row r="7">
@@ -5718,10 +5718,10 @@
         <v>0.5204386167756581</v>
       </c>
       <c r="C8" t="n">
-        <v>0.5716776228704172</v>
+        <v>0.5716776228704171</v>
       </c>
       <c r="D8" t="n">
-        <v>0.3472883864356235</v>
+        <v>0.3472883864356234</v>
       </c>
       <c r="E8" t="n">
         <v>-0.2243892364347937</v>
@@ -5734,16 +5734,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.5090233007869811</v>
+        <v>0.509023300786981</v>
       </c>
       <c r="C9" t="n">
-        <v>0.5486283832502574</v>
+        <v>0.5486283832502575</v>
       </c>
       <c r="D9" t="n">
         <v>0.3927084394723381</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.1559199437779193</v>
+        <v>-0.1559199437779195</v>
       </c>
     </row>
   </sheetData>
@@ -5832,7 +5832,7 @@
         <v>0.01038787912675922</v>
       </c>
       <c r="H2" t="n">
-        <v>0.007172550081213879</v>
+        <v>0.007172550081213882</v>
       </c>
       <c r="I2" t="n">
         <v>0.01252286124322956</v>
@@ -5851,7 +5851,7 @@
         <v>0.07000489645434713</v>
       </c>
       <c r="D3" t="n">
-        <v>0.03452163019589029</v>
+        <v>0.03452163019589028</v>
       </c>
       <c r="E3" t="n">
         <v>0.03135659096199024</v>
@@ -5879,13 +5879,13 @@
         <v>0.02028152029713371</v>
       </c>
       <c r="C4" t="n">
-        <v>0.03452163019589029</v>
+        <v>0.03452163019589028</v>
       </c>
       <c r="D4" t="n">
         <v>0.03454609934243165</v>
       </c>
       <c r="E4" t="n">
-        <v>0.02849962820785289</v>
+        <v>0.0284996282078529</v>
       </c>
       <c r="F4" t="n">
         <v>0.02112796236936711</v>
@@ -5913,7 +5913,7 @@
         <v>0.03135659096199024</v>
       </c>
       <c r="D5" t="n">
-        <v>0.02849962820785289</v>
+        <v>0.0284996282078529</v>
       </c>
       <c r="E5" t="n">
         <v>0.03103578890532283</v>
@@ -5956,7 +5956,7 @@
         <v>0.01102543569925791</v>
       </c>
       <c r="H6" t="n">
-        <v>0.008241728147407286</v>
+        <v>0.008241728147407288</v>
       </c>
       <c r="I6" t="n">
         <v>0.01330211006359534</v>
@@ -6000,7 +6000,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.007172550081213879</v>
+        <v>0.007172550081213882</v>
       </c>
       <c r="C8" t="n">
         <v>0.00801974525574441</v>
@@ -6012,7 +6012,7 @@
         <v>0.01017839315344844</v>
       </c>
       <c r="F8" t="n">
-        <v>0.008241728147407286</v>
+        <v>0.008241728147407288</v>
       </c>
       <c r="G8" t="n">
         <v>0.0103969384342186</v>
@@ -6159,28 +6159,28 @@
         <v>0.1093469788601253</v>
       </c>
       <c r="F2" t="n">
-        <v>0.08556527673367774</v>
+        <v>0.08556527673367778</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>8.429036616364356e-18</v>
       </c>
       <c r="H2" t="n">
-        <v>3.687864785652252e-18</v>
+        <v>1.179323972462162e-17</v>
       </c>
       <c r="I2" t="n">
-        <v>1.962937338412056e-18</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>0.04567811908672142</v>
+        <v>0.04567811908672137</v>
       </c>
       <c r="K2" t="n">
-        <v>0.3948433721197893</v>
+        <v>0.3948433721197898</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2634291742973692</v>
+        <v>0.2634291742973693</v>
       </c>
       <c r="M2" t="n">
-        <v>0.2104840577624423</v>
+        <v>0.2104840577624419</v>
       </c>
     </row>
     <row r="3">
@@ -6198,25 +6198,25 @@
         <v>0.1533775093404843</v>
       </c>
       <c r="F3" t="n">
-        <v>0.3465774705782325</v>
+        <v>0.3465774705782329</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>1.808712818820481e-17</v>
+        <v>1.074064360563279e-17</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>0.6534225294217673</v>
+        <v>0.653422529421767</v>
       </c>
       <c r="K3" t="n">
-        <v>6.133598722773533e-17</v>
+        <v>8.139034572895418e-17</v>
       </c>
       <c r="L3" t="n">
-        <v>4.305584546556521e-16</v>
+        <v>1.919535265408507e-16</v>
       </c>
       <c r="M3" t="n">
         <v>0</v>
@@ -6244,25 +6244,25 @@
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>7.996388485281367e-18</v>
+        <v>8.838788804598624e-19</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>7.432264542410003e-18</v>
+        <v>1.586492710207305e-18</v>
       </c>
       <c r="J4" t="n">
-        <v>0.06212631032178041</v>
+        <v>0.06212631032178031</v>
       </c>
       <c r="K4" t="n">
-        <v>0.4300000516322494</v>
+        <v>0.4300000516322492</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2636692920157067</v>
+        <v>0.2636692920157068</v>
       </c>
       <c r="M4" t="n">
-        <v>0.2442043460302636</v>
+        <v>0.2442043460302637</v>
       </c>
     </row>
     <row r="5">
@@ -6286,22 +6286,22 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>2.586028459749451e-17</v>
+        <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>6.770811803143688e-17</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>0.8692115045337068</v>
+        <v>0.8692115045337057</v>
       </c>
       <c r="K5" t="n">
-        <v>8.521680137282358e-18</v>
+        <v>1.734723475976807e-18</v>
       </c>
       <c r="L5" t="n">
-        <v>0.04516639008307528</v>
+        <v>0.04516639008307516</v>
       </c>
       <c r="M5" t="n">
-        <v>0.08562210538321799</v>
+        <v>0.08562210538321922</v>
       </c>
     </row>
     <row r="6">
@@ -6327,28 +6327,28 @@
         <v>0.1067563288585438</v>
       </c>
       <c r="F6" t="n">
-        <v>0.05540182866451901</v>
+        <v>0.05540182866451893</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>2.168404344971009e-19</v>
       </c>
       <c r="H6" t="n">
-        <v>9.17123909487703e-19</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>4.18614284042478e-18</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>0.05609019744355018</v>
+        <v>0.05609019744355079</v>
       </c>
       <c r="K6" t="n">
-        <v>0.3175974304376356</v>
+        <v>0.3175974304376353</v>
       </c>
       <c r="L6" t="n">
         <v>0.34342078196175</v>
       </c>
       <c r="M6" t="n">
-        <v>0.2274897614925453</v>
+        <v>0.2274897614925449</v>
       </c>
     </row>
     <row r="7">
@@ -6366,22 +6366,22 @@
         <v>0.1504476024987286</v>
       </c>
       <c r="F7" t="n">
-        <v>0.4025461561604331</v>
+        <v>0.4025461561604337</v>
       </c>
       <c r="G7" t="n">
-        <v>9.925202306393247e-17</v>
+        <v>6.496474504117939e-17</v>
       </c>
       <c r="H7" t="n">
-        <v>1.393070427474296e-16</v>
+        <v>5.345599695110914e-17</v>
       </c>
       <c r="I7" t="n">
-        <v>2.220460394304046e-16</v>
+        <v>1.163729879948893e-16</v>
       </c>
       <c r="J7" t="n">
-        <v>0.5974538438395668</v>
+        <v>0.5974538438395665</v>
       </c>
       <c r="K7" t="n">
-        <v>1.01776876116429e-17</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -6412,25 +6412,25 @@
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>2.56589215659788e-18</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>1.123736081645859e-18</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>2.471030624981074e-18</v>
+        <v>2.901934877293233e-18</v>
       </c>
       <c r="J8" t="n">
-        <v>0.07361026433028858</v>
+        <v>0.07361026433028842</v>
       </c>
       <c r="K8" t="n">
-        <v>0.3363305860138766</v>
+        <v>0.3363305860138776</v>
       </c>
       <c r="L8" t="n">
-        <v>0.340281021157545</v>
+        <v>0.3402810211575445</v>
       </c>
       <c r="M8" t="n">
-        <v>0.24977812849829</v>
+        <v>0.2497781284982894</v>
       </c>
     </row>
     <row r="9">
@@ -6445,31 +6445,31 @@
         <v>0.1810966956098033</v>
       </c>
       <c r="E9" t="n">
-        <v>0.1541715894857803</v>
+        <v>0.1541715894857802</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>3.916685657686329e-17</v>
+        <v>1.387778780781446e-17</v>
       </c>
       <c r="H9" t="n">
-        <v>7.386132609639943e-17</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>3.469446951953614e-18</v>
       </c>
       <c r="J9" t="n">
-        <v>0.8863307991279518</v>
+        <v>0.8863307991279513</v>
       </c>
       <c r="K9" t="n">
-        <v>1.566224931342011e-17</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>0.1136692008720484</v>
+        <v>0.1136692008720488</v>
       </c>
     </row>
     <row r="10">
@@ -6492,31 +6492,31 @@
         <v>0.07496781225164267</v>
       </c>
       <c r="E10" t="n">
-        <v>0.1113583569727966</v>
+        <v>0.1113583569727967</v>
       </c>
       <c r="F10" t="n">
-        <v>0.2214304253984209</v>
+        <v>0.2214304253984211</v>
       </c>
       <c r="G10" t="n">
-        <v>9.154179701933422e-18</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>5.514161490226473e-18</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>2.322281108715372e-18</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>0.08120951631889428</v>
+        <v>0.08120951631889435</v>
       </c>
       <c r="K10" t="n">
-        <v>0.4927219905189312</v>
+        <v>0.4927219905189315</v>
       </c>
       <c r="L10" t="n">
-        <v>0.01043557493966056</v>
+        <v>0.0104355749396604</v>
       </c>
       <c r="M10" t="n">
-        <v>0.1942024928240929</v>
+        <v>0.1942024928240928</v>
       </c>
     </row>
     <row r="11">
@@ -6534,28 +6534,28 @@
         <v>0.1721636278425112</v>
       </c>
       <c r="F11" t="n">
-        <v>0.2221693546039033</v>
+        <v>0.2221693546039032</v>
       </c>
       <c r="G11" t="n">
-        <v>0.07993134246149998</v>
+        <v>0.07993134246150027</v>
       </c>
       <c r="H11" t="n">
-        <v>6.74815586966716e-18</v>
+        <v>4.959530626478106e-18</v>
       </c>
       <c r="I11" t="n">
-        <v>1.280732249299352e-17</v>
+        <v>3.60494444964577e-17</v>
       </c>
       <c r="J11" t="n">
-        <v>0.6978993029345968</v>
+        <v>0.6978993029345967</v>
       </c>
       <c r="K11" t="n">
-        <v>2.735985220860997e-17</v>
+        <v>6.277428668144968e-18</v>
       </c>
       <c r="L11" t="n">
-        <v>3.318994919662097e-18</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>1.929796067553098e-17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -6571,7 +6571,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.06827491568687617</v>
+        <v>0.0682749156868762</v>
       </c>
       <c r="E12" t="n">
         <v>0.1163795120288083</v>
@@ -6580,22 +6580,22 @@
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>3.228889594933393e-18</v>
       </c>
       <c r="H12" t="n">
-        <v>3.440100278867604e-18</v>
+        <v>1.140106347004288e-18</v>
       </c>
       <c r="I12" t="n">
-        <v>4.114368027917515e-18</v>
+        <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>0.08165132750285274</v>
+        <v>0.08165132750285288</v>
       </c>
       <c r="K12" t="n">
-        <v>0.6003671464488618</v>
+        <v>0.6003671464488619</v>
       </c>
       <c r="L12" t="n">
-        <v>0.07475257078037467</v>
+        <v>0.07475257078037457</v>
       </c>
       <c r="M12" t="n">
         <v>0.2432289552679107</v>
@@ -6619,25 +6619,25 @@
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>0.1576130232278464</v>
+        <v>0.157613023227846</v>
       </c>
       <c r="H13" t="n">
-        <v>3.040572499202851e-17</v>
+        <v>4.042258540243613e-17</v>
       </c>
       <c r="I13" t="n">
-        <v>0.01304206278550509</v>
+        <v>0.01304206278550639</v>
       </c>
       <c r="J13" t="n">
-        <v>0.7348352533246159</v>
+        <v>0.7348352533246154</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>0.0945096606620327</v>
+        <v>0.09450966066203217</v>
       </c>
       <c r="M13" t="n">
-        <v>1.0921633283152e-17</v>
+        <v>1.248182054523118e-17</v>
       </c>
     </row>
   </sheetData>
@@ -6709,7 +6709,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.08556527673367774</v>
+        <v>0.08556527673367778</v>
       </c>
       <c r="C2" t="n">
         <v>0.1093469788601253</v>
@@ -6718,13 +6718,13 @@
         <v>0.1100594843273342</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0007125054672088849</v>
+        <v>0.000712505467208871</v>
       </c>
       <c r="F2" t="n">
-        <v>0.006338185634588038</v>
+        <v>0.006338185634588002</v>
       </c>
       <c r="G2" t="n">
-        <v>0.01037188581130459</v>
+        <v>0.01037188581130447</v>
       </c>
     </row>
     <row r="3">
@@ -6734,7 +6734,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.05540182866451901</v>
+        <v>0.05540182866451893</v>
       </c>
       <c r="C3" t="n">
         <v>0.1067563288585438</v>
@@ -6743,10 +6743,10 @@
         <v>0.1070394347523071</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0002831058937633052</v>
+        <v>0.0002831058937632913</v>
       </c>
       <c r="F3" t="n">
-        <v>0.006075804774036059</v>
+        <v>0.006075804774036055</v>
       </c>
       <c r="G3" t="n">
         <v>0.008064474009896544</v>
@@ -6759,22 +6759,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.2214304253984209</v>
+        <v>0.2214304253984211</v>
       </c>
       <c r="C4" t="n">
-        <v>0.1113583569727966</v>
+        <v>0.1113583569727967</v>
       </c>
       <c r="D4" t="n">
         <v>0.1163795120288083</v>
       </c>
       <c r="E4" t="n">
-        <v>0.005021155056011695</v>
+        <v>0.005021155056011667</v>
       </c>
       <c r="F4" t="n">
-        <v>0.006996611231066884</v>
+        <v>0.00699661123106689</v>
       </c>
       <c r="G4" t="n">
-        <v>0.03289161870301872</v>
+        <v>0.03289161870301859</v>
       </c>
     </row>
   </sheetData>
@@ -6815,13 +6815,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.1937588930478913</v>
+        <v>0.1937588930478917</v>
       </c>
       <c r="C2" t="n">
-        <v>0.4279360145518208</v>
+        <v>0.4279360145518211</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>3.031497883446051e-17</v>
       </c>
     </row>
     <row r="3">
@@ -6831,13 +6831,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.3465774705782325</v>
+        <v>0.3465774705782329</v>
       </c>
       <c r="C3" t="n">
-        <v>0.4025461561604331</v>
+        <v>0.4025461561604337</v>
       </c>
       <c r="D3" t="n">
-        <v>0.2221693546039033</v>
+        <v>0.2221693546039032</v>
       </c>
     </row>
     <row r="4">
@@ -6847,13 +6847,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.3384510282616056</v>
+        <v>0.3384510282616053</v>
       </c>
       <c r="C4" t="n">
         <v>0.3391483660024529</v>
       </c>
       <c r="D4" t="n">
-        <v>0.3159012209564501</v>
+        <v>0.31590122095645</v>
       </c>
     </row>
     <row r="5">
@@ -6863,13 +6863,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.2854919704249195</v>
+        <v>0.2854919704249194</v>
       </c>
       <c r="C5" t="n">
-        <v>0.274398870332317</v>
+        <v>0.2743988703323169</v>
       </c>
       <c r="D5" t="n">
-        <v>0.3288283943947342</v>
+        <v>0.3288283943947343</v>
       </c>
     </row>
     <row r="6">
@@ -6882,10 +6882,10 @@
         <v>0.2537136369278277</v>
       </c>
       <c r="C6" t="n">
-        <v>0.2355487583306577</v>
+        <v>0.2355487583306576</v>
       </c>
       <c r="D6" t="n">
-        <v>0.327632154804668</v>
+        <v>0.3276321548046678</v>
       </c>
     </row>
     <row r="7">
@@ -6895,13 +6895,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.08556527673367774</v>
+        <v>0.08556527673367778</v>
       </c>
       <c r="C7" t="n">
-        <v>0.05540182866451901</v>
+        <v>0.05540182866451893</v>
       </c>
       <c r="D7" t="n">
-        <v>0.2214304253984209</v>
+        <v>0.2214304253984211</v>
       </c>
     </row>
   </sheetData>
